--- a/journal_new/journal_list.xlsx
+++ b/journal_new/journal_list.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R86c947fac6db4790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="R70cb4c10f91f490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Re4e5a39a91444fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Rd3bf13f768ba4d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="Rc5fdd745095a404d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,12 +23,6 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:color rgb="1F4E79"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -42,7 +35,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F4E79"/>
+        <x:fgColor rgb="1E5B8C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -53,7 +46,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -72,13 +65,18 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -87,7 +85,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalsTable" displayName="JournalsTable" ref="A1:F198" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalTable" displayName="JournalTable" ref="A1:F198" headerRowCount="1">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Order"/>
@@ -249,3248 +247,3248 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="62" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="10" t="str">
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Order</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Journal</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Extra Links (label|url; ...)</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B2" t="n">
+      <x:c r="A2" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C2" s="11" t="str">
         <x:v>Applied Soft Computing</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D2" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing</x:v>
       </x:c>
-      <x:c r="E2"/>
-      <x:c r="F2"/>
+      <x:c r="E2" s="11" t="str"/>
+      <x:c r="F2" s="11" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B3" t="n">
+      <x:c r="A3" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C3" s="11" t="str">
         <x:v>Computers &amp; Industrial Engineering</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D3" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering</x:v>
       </x:c>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
+      <x:c r="E3" s="11" t="str"/>
+      <x:c r="F3" s="11" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B4" t="n">
+      <x:c r="A4" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>Computers &amp; Operations Research</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research</x:v>
       </x:c>
-      <x:c r="E4"/>
-      <x:c r="F4"/>
+      <x:c r="E4" s="11" t="str"/>
+      <x:c r="F4" s="11" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B5" t="n">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C5" s="11" t="str">
         <x:v>Decision Support Systems</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D5" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems</x:v>
       </x:c>
-      <x:c r="E5"/>
-      <x:c r="F5"/>
+      <x:c r="E5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B6" t="n">
+      <x:c r="A6" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>European J of Operational Research</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="C6" s="11" t="str">
+        <x:v>European Journal of Operational Research</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-j-of-operational-research</x:v>
       </x:c>
-      <x:c r="E6"/>
-      <x:c r="F6"/>
+      <x:c r="E6" s="11" t="str"/>
+      <x:c r="F6" s="11" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B7" t="n">
+      <x:c r="A7" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="11" t="str">
         <x:v>Expert Systems with Applications</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D7" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications</x:v>
       </x:c>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
+      <x:c r="E7" s="11" t="str"/>
+      <x:c r="F7" s="11" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B8" t="n">
+      <x:c r="A8" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="11" t="str">
         <x:v>Fuzzy Sets and Systems</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="D8" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems</x:v>
       </x:c>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
+      <x:c r="E8" s="11" t="str"/>
+      <x:c r="F8" s="11" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B9" t="n">
+      <x:c r="A9" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C9" s="11" t="str">
         <x:v>Information Fusion</x:v>
       </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="D9" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion</x:v>
       </x:c>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
+      <x:c r="E9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B10" t="n">
+      <x:c r="A10" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>Information Sciences</x:v>
       </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences</x:v>
       </x:c>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B11" t="n">
+      <x:c r="A11" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Int J of Approximate Reasoning</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="C11" s="11" t="str">
+        <x:v>International Journal of Approximate Reasoning</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-approximate-reasoning</x:v>
       </x:c>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B12" t="n">
+      <x:c r="A12" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Int J of Production Economics</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="C12" s="11" t="str">
+        <x:v>International Journal of Production Economics</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-production-economics</x:v>
       </x:c>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
+      <x:c r="E12" s="11" t="str"/>
+      <x:c r="F12" s="11" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B13" t="n">
+      <x:c r="A13" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="11" t="str">
         <x:v>Knowledge-Based Systems</x:v>
       </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="D13" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems</x:v>
       </x:c>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B14" t="n">
+      <x:c r="A14" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C14" s="11" t="str">
         <x:v>Omega</x:v>
       </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="D14" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega</x:v>
       </x:c>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="11" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B15" t="n">
+      <x:c r="A15" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C15" s="11" t="str">
         <x:v>Engineering Applications of Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="D15" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
+      <x:c r="E15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B16" t="n">
+      <x:c r="A16" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="11" t="str">
         <x:v>Journal of Management Science and Engineering</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D16" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering</x:v>
       </x:c>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
+      <x:c r="E16" s="11" t="str"/>
+      <x:c r="F16" s="11" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B17" t="n">
+      <x:c r="A17" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C17" s="11" t="str">
         <x:v>Electronic Commerce Research and Applications</x:v>
       </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="D17" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications</x:v>
       </x:c>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
+      <x:c r="E17" s="11" t="str"/>
+      <x:c r="F17" s="11" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B18" t="n">
+      <x:c r="A18" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C18" s="11" t="str">
         <x:v>International Journal of Forecasting</x:v>
       </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="D18" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting</x:v>
       </x:c>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
+      <x:c r="E18" s="11" t="str"/>
+      <x:c r="F18" s="11" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B19" t="n">
+      <x:c r="A19" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C19" s="11" t="str">
         <x:v>Information &amp; Management</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D19" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management</x:v>
       </x:c>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B20" t="n">
+      <x:c r="A20" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C20" s="11" t="str">
         <x:v>Information Systems</x:v>
       </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="D20" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems</x:v>
       </x:c>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
+      <x:c r="E20" s="11" t="str"/>
+      <x:c r="F20" s="11" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B21" t="n">
+      <x:c r="A21" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C21" s="11" t="str">
         <x:v>Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="D21" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
+      <x:c r="E21" s="11" t="str"/>
+      <x:c r="F21" s="11" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B22" t="n">
+      <x:c r="A22" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C22" s="11" t="str">
         <x:v>Pattern Recognition</x:v>
       </x:c>
-      <x:c r="D22" t="str">
+      <x:c r="D22" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition</x:v>
       </x:c>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
+      <x:c r="E22" s="11" t="str"/>
+      <x:c r="F22" s="11" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B23" t="n">
+      <x:c r="A23" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C23" t="str">
+      <x:c r="C23" s="11" t="str">
         <x:v>Pattern Recognition Letters</x:v>
       </x:c>
-      <x:c r="D23" t="str">
+      <x:c r="D23" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters</x:v>
       </x:c>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
+      <x:c r="E23" s="11" t="str"/>
+      <x:c r="F23" s="11" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B24" t="n">
+      <x:c r="A24" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C24" s="11" t="str">
         <x:v>Neurocomputing</x:v>
       </x:c>
-      <x:c r="D24" t="str">
+      <x:c r="D24" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing</x:v>
       </x:c>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
+      <x:c r="E24" s="11" t="str"/>
+      <x:c r="F24" s="11" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B25" t="n">
+      <x:c r="A25" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C25" t="str">
-        <x:v>Physica A</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
+      <x:c r="C25" s="11" t="str">
+        <x:v>Physica A: Statistical Mechanics and its Applications</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a</x:v>
       </x:c>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
+      <x:c r="E25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B26" t="n">
+      <x:c r="A26" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C26" s="11" t="str">
         <x:v>Journal of Cleaner Production</x:v>
       </x:c>
-      <x:c r="D26" t="str">
+      <x:c r="D26" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-cleaner-production</x:v>
       </x:c>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
+      <x:c r="E26" s="11" t="str"/>
+      <x:c r="F26" s="11" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B27" t="n">
+      <x:c r="A27" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C27" s="11" t="str">
         <x:v>Energy</x:v>
       </x:c>
-      <x:c r="D27" t="str">
+      <x:c r="D27" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/energy</x:v>
       </x:c>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
+      <x:c r="E27" s="11" t="str"/>
+      <x:c r="F27" s="11" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B28" t="n">
+      <x:c r="A28" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C28" t="str">
+      <x:c r="C28" s="11" t="str">
         <x:v>Reliability Engineering &amp; System Safety</x:v>
       </x:c>
-      <x:c r="D28" t="str">
+      <x:c r="D28" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety</x:v>
       </x:c>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
+      <x:c r="E28" s="11" t="str"/>
+      <x:c r="F28" s="11" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B29" t="n">
+      <x:c r="A29" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C29" s="11" t="str">
         <x:v>Journal of Biomedical Informatics</x:v>
       </x:c>
-      <x:c r="D29" t="str">
+      <x:c r="D29" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics</x:v>
       </x:c>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
+      <x:c r="E29" s="11" t="str"/>
+      <x:c r="F29" s="11" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B30" t="n">
+      <x:c r="A30" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C30" s="11" t="str">
         <x:v>AI Open</x:v>
       </x:c>
-      <x:c r="D30" t="str">
+      <x:c r="D30" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open</x:v>
       </x:c>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
+      <x:c r="E30" s="11" t="str"/>
+      <x:c r="F30" s="11" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B31" t="n">
+      <x:c r="A31" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C31" t="str">
+      <x:c r="C31" s="11" t="str">
         <x:v>Neural Networks</x:v>
       </x:c>
-      <x:c r="D31" t="str">
+      <x:c r="D31" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks</x:v>
       </x:c>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
+      <x:c r="E31" s="11" t="str"/>
+      <x:c r="F31" s="11" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B32" t="n">
+      <x:c r="A32" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C32" s="11" t="str">
         <x:v>Advanced Engineering Informatics</x:v>
       </x:c>
-      <x:c r="D32" t="str">
+      <x:c r="D32" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
+      <x:c r="E32" s="11" t="str"/>
+      <x:c r="F32" s="11" t="str"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B33" t="n">
+      <x:c r="A33" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C33" t="str">
+      <x:c r="C33" s="11" t="str">
         <x:v>Computers in Industry</x:v>
       </x:c>
-      <x:c r="D33" t="str">
+      <x:c r="D33" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry</x:v>
       </x:c>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
+      <x:c r="E33" s="11" t="str"/>
+      <x:c r="F33" s="11" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B34" t="n">
+      <x:c r="A34" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C34" t="str">
+      <x:c r="C34" s="11" t="str">
         <x:v>Chaos, Solitons &amp; Fractals</x:v>
       </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="D34" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/chaos-solitons-and-fractals</x:v>
       </x:c>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
+      <x:c r="E34" s="11" t="str"/>
+      <x:c r="F34" s="11" t="str"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B35" t="n">
+      <x:c r="A35" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C35" t="str">
+      <x:c r="C35" s="11" t="str">
         <x:v>Safety Science</x:v>
       </x:c>
-      <x:c r="D35" t="str">
+      <x:c r="D35" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/safety-science</x:v>
       </x:c>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
+      <x:c r="E35" s="11" t="str"/>
+      <x:c r="F35" s="11" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B36" t="n">
+      <x:c r="A36" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C36" t="str">
+      <x:c r="C36" s="11" t="str">
         <x:v>Technological Forecasting and Social Change</x:v>
       </x:c>
-      <x:c r="D36" t="str">
+      <x:c r="D36" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change</x:v>
       </x:c>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
+      <x:c r="E36" s="11" t="str"/>
+      <x:c r="F36" s="11" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B37" t="n">
+      <x:c r="A37" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C37" t="str">
+      <x:c r="C37" s="11" t="str">
         <x:v>Automation in Construction</x:v>
       </x:c>
-      <x:c r="D37" t="str">
+      <x:c r="D37" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/automation-in-construction</x:v>
       </x:c>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
+      <x:c r="E37" s="11" t="str"/>
+      <x:c r="F37" s="11" t="str"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B38" t="n">
+      <x:c r="A38" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C38" t="str">
+      <x:c r="C38" s="11" t="str">
         <x:v>Annual Reviews in Control</x:v>
       </x:c>
-      <x:c r="D38" t="str">
+      <x:c r="D38" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/annual-reviews-in-control</x:v>
       </x:c>
-      <x:c r="E38"/>
-      <x:c r="F38"/>
+      <x:c r="E38" s="11" t="str"/>
+      <x:c r="F38" s="11" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B39" t="n">
+      <x:c r="A39" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C39" t="str">
+      <x:c r="C39" s="11" t="str">
         <x:v>Journal of Environmental Economics and Management</x:v>
       </x:c>
-      <x:c r="D39" t="str">
+      <x:c r="D39" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-environmental-economics-and-management</x:v>
       </x:c>
-      <x:c r="E39"/>
-      <x:c r="F39"/>
+      <x:c r="E39" s="11" t="str"/>
+      <x:c r="F39" s="11" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B40" t="n">
+      <x:c r="A40" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C40" t="str">
+      <x:c r="C40" s="11" t="str">
         <x:v>Journal of Retailing and Consumer Services</x:v>
       </x:c>
-      <x:c r="D40" t="str">
+      <x:c r="D40" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services</x:v>
       </x:c>
-      <x:c r="E40"/>
-      <x:c r="F40"/>
+      <x:c r="E40" s="11" t="str"/>
+      <x:c r="F40" s="11" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B41" t="n">
+      <x:c r="A41" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C41" t="str">
-        <x:v>Transportation Research, Series B: Methodological</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
+      <x:c r="C41" s="11" t="str">
+        <x:v>Transportation Research Part B: Methodological</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-series-b-methodological</x:v>
       </x:c>
-      <x:c r="E41"/>
-      <x:c r="F41"/>
+      <x:c r="E41" s="11" t="str"/>
+      <x:c r="F41" s="11" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B42" t="n">
+      <x:c r="A42" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C42" t="str">
+      <x:c r="C42" s="11" t="str">
         <x:v>Transportation Research, Part D: Transport and Environment</x:v>
       </x:c>
-      <x:c r="D42" t="str">
+      <x:c r="D42" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
-      <x:c r="E42"/>
-      <x:c r="F42"/>
+      <x:c r="E42" s="11" t="str"/>
+      <x:c r="F42" s="11" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B43" t="n">
+      <x:c r="A43" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C43" t="str">
+      <x:c r="C43" s="11" t="str">
         <x:v>Transportation Research, Part E: Logistics and Transportation Review</x:v>
       </x:c>
-      <x:c r="D43" t="str">
+      <x:c r="D43" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
-      <x:c r="E43"/>
-      <x:c r="F43"/>
+      <x:c r="E43" s="11" t="str"/>
+      <x:c r="F43" s="11" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B44" t="n">
+      <x:c r="A44" s="11" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C44" t="str">
+      <x:c r="C44" s="11" t="str">
         <x:v>EURO Journal on Decision Processes</x:v>
       </x:c>
-      <x:c r="D44" t="str">
+      <x:c r="D44" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes</x:v>
       </x:c>
-      <x:c r="E44"/>
-      <x:c r="F44"/>
+      <x:c r="E44" s="11" t="str"/>
+      <x:c r="F44" s="11" t="str"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" t="str">
+      <x:c r="A45" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B45" t="n">
+      <x:c r="B45" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C45" t="str">
+      <x:c r="C45" s="11" t="str">
         <x:v>Tourism Management</x:v>
       </x:c>
-      <x:c r="D45" t="str">
+      <x:c r="D45" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management</x:v>
       </x:c>
-      <x:c r="E45"/>
-      <x:c r="F45"/>
+      <x:c r="E45" s="11" t="str"/>
+      <x:c r="F45" s="11" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="str">
+      <x:c r="A46" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B46" t="n">
+      <x:c r="B46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C46" t="str">
+      <x:c r="C46" s="11" t="str">
         <x:v>Annals of Tourism Research</x:v>
       </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="D46" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research</x:v>
       </x:c>
-      <x:c r="E46"/>
-      <x:c r="F46"/>
+      <x:c r="E46" s="11" t="str"/>
+      <x:c r="F46" s="11" t="str"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="str">
+      <x:c r="A47" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B47" t="n">
+      <x:c r="B47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C47" t="str">
+      <x:c r="C47" s="11" t="str">
         <x:v>Journal of Travel Research</x:v>
       </x:c>
-      <x:c r="D47" t="str">
+      <x:c r="D47" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Travel%20Research</x:v>
       </x:c>
-      <x:c r="E47"/>
-      <x:c r="F47"/>
+      <x:c r="E47" s="11" t="str"/>
+      <x:c r="F47" s="11" t="str"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="str">
+      <x:c r="A48" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B48" t="n">
+      <x:c r="B48" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C48" t="str">
+      <x:c r="C48" s="11" t="str">
         <x:v>Journal of Service Research</x:v>
       </x:c>
-      <x:c r="D48" t="str">
+      <x:c r="D48" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Service%20Research</x:v>
       </x:c>
-      <x:c r="E48"/>
-      <x:c r="F48"/>
+      <x:c r="E48" s="11" t="str"/>
+      <x:c r="F48" s="11" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" t="str">
+      <x:c r="A49" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B49" t="n">
+      <x:c r="B49" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C49" t="str">
+      <x:c r="C49" s="11" t="str">
         <x:v>International Journal of Hospitality Management</x:v>
       </x:c>
-      <x:c r="D49" t="str">
+      <x:c r="D49" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-hospitality-management</x:v>
       </x:c>
-      <x:c r="E49"/>
-      <x:c r="F49"/>
+      <x:c r="E49" s="11" t="str"/>
+      <x:c r="F49" s="11" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" t="str">
+      <x:c r="A50" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B50" t="n">
+      <x:c r="B50" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C50" t="str">
+      <x:c r="C50" s="11" t="str">
         <x:v>International Journal of Contemporary Hospitality Management</x:v>
       </x:c>
-      <x:c r="D50" t="str">
+      <x:c r="D50" s="11" t="str">
         <x:v>https://www.emerald.com/insight/search?q=International%20Journal%20of%20Contemporary%20Hospitality%20Management</x:v>
       </x:c>
-      <x:c r="E50"/>
-      <x:c r="F50"/>
+      <x:c r="E50" s="11" t="str"/>
+      <x:c r="F50" s="11" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" t="str">
+      <x:c r="A51" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B51" t="n">
+      <x:c r="B51" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C51" t="str">
+      <x:c r="C51" s="11" t="str">
         <x:v>Journal of Sustainable Tourism</x:v>
       </x:c>
-      <x:c r="D51" t="str">
+      <x:c r="D51" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Sustainable%20Tourism</x:v>
       </x:c>
-      <x:c r="E51"/>
-      <x:c r="F51"/>
+      <x:c r="E51" s="11" t="str"/>
+      <x:c r="F51" s="11" t="str"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" t="str">
+      <x:c r="A52" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B52" t="n">
+      <x:c r="B52" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C52" t="str">
+      <x:c r="C52" s="11" t="str">
         <x:v>Tourism Management Perspectives</x:v>
       </x:c>
-      <x:c r="D52" t="str">
+      <x:c r="D52" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management-perspectives</x:v>
       </x:c>
-      <x:c r="E52"/>
-      <x:c r="F52"/>
+      <x:c r="E52" s="11" t="str"/>
+      <x:c r="F52" s="11" t="str"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" t="str">
+      <x:c r="A53" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B53" t="n">
+      <x:c r="B53" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C53" t="str">
+      <x:c r="C53" s="11" t="str">
         <x:v>Current Issues in Tourism</x:v>
       </x:c>
-      <x:c r="D53" t="str">
+      <x:c r="D53" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Current%20Issues%20in%20Tourism</x:v>
       </x:c>
-      <x:c r="E53"/>
-      <x:c r="F53"/>
+      <x:c r="E53" s="11" t="str"/>
+      <x:c r="F53" s="11" t="str"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" t="str">
+      <x:c r="A54" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B54" t="n">
+      <x:c r="B54" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C54" t="str">
+      <x:c r="C54" s="11" t="str">
         <x:v>International Journal of Tourism Research</x:v>
       </x:c>
-      <x:c r="D54" t="str">
+      <x:c r="D54" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E54"/>
-      <x:c r="F54"/>
+      <x:c r="E54" s="11" t="str"/>
+      <x:c r="F54" s="11" t="str"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" t="str">
+      <x:c r="A55" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B55" t="n">
+      <x:c r="B55" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C55" t="str">
+      <x:c r="C55" s="11" t="str">
         <x:v>Tourism Planning and Development</x:v>
       </x:c>
-      <x:c r="D55" t="str">
+      <x:c r="D55" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Tourism%20Planning%20and%20Development</x:v>
       </x:c>
-      <x:c r="E55"/>
-      <x:c r="F55"/>
+      <x:c r="E55" s="11" t="str"/>
+      <x:c r="F55" s="11" t="str"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" t="str">
+      <x:c r="A56" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B56" t="n">
+      <x:c r="B56" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C56" t="str">
+      <x:c r="C56" s="11" t="str">
         <x:v>Journal of Hospitality &amp; Tourism Research</x:v>
       </x:c>
-      <x:c r="D56" t="str">
+      <x:c r="D56" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Hospitality%20%26%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E56"/>
-      <x:c r="F56"/>
+      <x:c r="E56" s="11" t="str"/>
+      <x:c r="F56" s="11" t="str"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" t="str">
+      <x:c r="A57" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B57" t="n">
+      <x:c r="B57" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C57" t="str">
+      <x:c r="C57" s="11" t="str">
         <x:v>Tourism Economics</x:v>
       </x:c>
-      <x:c r="D57" t="str">
+      <x:c r="D57" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20Economics</x:v>
       </x:c>
-      <x:c r="E57"/>
-      <x:c r="F57"/>
+      <x:c r="E57" s="11" t="str"/>
+      <x:c r="F57" s="11" t="str"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" t="str">
+      <x:c r="A58" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B58" t="n">
+      <x:c r="B58" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C58" t="str">
+      <x:c r="C58" s="11" t="str">
         <x:v>Journal of Hospitality and Tourism Management</x:v>
       </x:c>
-      <x:c r="D58" t="str">
+      <x:c r="D58" s="11" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-hospitality-and-tourism-management</x:v>
       </x:c>
-      <x:c r="E58"/>
-      <x:c r="F58"/>
+      <x:c r="E58" s="11" t="str"/>
+      <x:c r="F58" s="11" t="str"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" t="str">
+      <x:c r="A59" s="11" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B59" t="n">
+      <x:c r="B59" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C59" t="str">
+      <x:c r="C59" s="11" t="str">
         <x:v>Tourism and Hospitality Research</x:v>
       </x:c>
-      <x:c r="D59" t="str">
+      <x:c r="D59" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20and%20Hospitality%20Research</x:v>
       </x:c>
-      <x:c r="E59"/>
-      <x:c r="F59"/>
+      <x:c r="E59" s="11" t="str"/>
+      <x:c r="F59" s="11" t="str"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B60" t="n">
+      <x:c r="A60" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B60" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C60" t="str">
+      <x:c r="C60" s="11" t="str">
         <x:v>Annals of Operations Research</x:v>
       </x:c>
-      <x:c r="D60" t="str">
+      <x:c r="D60" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E60"/>
-      <x:c r="F60"/>
+      <x:c r="E60" s="11" t="str"/>
+      <x:c r="F60" s="11" t="str"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B61" t="n">
+      <x:c r="A61" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C61" t="str">
+      <x:c r="C61" s="11" t="str">
         <x:v>Fuzzy Optimization and Decision Making</x:v>
       </x:c>
-      <x:c r="D61" t="str">
+      <x:c r="D61" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Fuzzy%20Optimization%20and%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E61"/>
-      <x:c r="F61"/>
+      <x:c r="E61" s="11" t="str"/>
+      <x:c r="F61" s="11" t="str"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B62" t="n">
+      <x:c r="A62" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C62" t="str">
+      <x:c r="C62" s="11" t="str">
         <x:v>Group Decision and Negotiation</x:v>
       </x:c>
-      <x:c r="D62" t="str">
+      <x:c r="D62" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Group%20Decision%20and%20Negotiation</x:v>
       </x:c>
-      <x:c r="E62"/>
-      <x:c r="F62"/>
+      <x:c r="E62" s="11" t="str"/>
+      <x:c r="F62" s="11" t="str"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B63" t="n">
+      <x:c r="A63" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C63" t="str">
+      <x:c r="C63" s="11" t="str">
         <x:v>Soft Computing</x:v>
       </x:c>
-      <x:c r="D63" t="str">
+      <x:c r="D63" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Soft%20Computing</x:v>
       </x:c>
-      <x:c r="E63"/>
-      <x:c r="F63"/>
+      <x:c r="E63" s="11" t="str"/>
+      <x:c r="F63" s="11" t="str"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B64" t="n">
+      <x:c r="A64" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B64" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C64" t="str">
+      <x:c r="C64" s="11" t="str">
         <x:v>International Journal of Machine Learning and Cybernetics</x:v>
       </x:c>
-      <x:c r="D64" t="str">
+      <x:c r="D64" s="11" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Machine%20Learning%20and%20Cybernetics</x:v>
       </x:c>
-      <x:c r="E64"/>
-      <x:c r="F64"/>
+      <x:c r="E64" s="11" t="str"/>
+      <x:c r="F64" s="11" t="str"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B65" t="n">
+      <x:c r="A65" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C65" t="str">
+      <x:c r="C65" s="11" t="str">
         <x:v>Knowledge and Information Systems</x:v>
       </x:c>
-      <x:c r="D65" t="str">
+      <x:c r="D65" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Knowledge%20and%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E65"/>
-      <x:c r="F65"/>
+      <x:c r="E65" s="11" t="str"/>
+      <x:c r="F65" s="11" t="str"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B66" t="n">
+      <x:c r="A66" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B66" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C66" t="str">
+      <x:c r="C66" s="11" t="str">
         <x:v>Neural Computing and Applications</x:v>
       </x:c>
-      <x:c r="D66" t="str">
+      <x:c r="D66" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Neural%20Computing%20and%20Applications</x:v>
       </x:c>
-      <x:c r="E66"/>
-      <x:c r="F66"/>
+      <x:c r="E66" s="11" t="str"/>
+      <x:c r="F66" s="11" t="str"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B67" t="n">
+      <x:c r="A67" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C67" t="str">
+      <x:c r="C67" s="11" t="str">
         <x:v>Applied Intelligence</x:v>
       </x:c>
-      <x:c r="D67" t="str">
+      <x:c r="D67" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Applied%20Intelligence</x:v>
       </x:c>
-      <x:c r="E67"/>
-      <x:c r="F67"/>
+      <x:c r="E67" s="11" t="str"/>
+      <x:c r="F67" s="11" t="str"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B68" t="n">
+      <x:c r="A68" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B68" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C68" t="str">
+      <x:c r="C68" s="11" t="str">
         <x:v>Cognitive Computation</x:v>
       </x:c>
-      <x:c r="D68" t="str">
+      <x:c r="D68" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Cognitive%20Computation</x:v>
       </x:c>
-      <x:c r="E68"/>
-      <x:c r="F68"/>
+      <x:c r="E68" s="11" t="str"/>
+      <x:c r="F68" s="11" t="str"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B69" t="n">
+      <x:c r="A69" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C69" t="str">
+      <x:c r="C69" s="11" t="str">
         <x:v>Complex &amp; Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D69" t="str">
+      <x:c r="D69" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Complex%20%26%20Intelligent%20Systems</x:v>
       </x:c>
-      <x:c r="E69"/>
-      <x:c r="F69"/>
+      <x:c r="E69" s="11" t="str"/>
+      <x:c r="F69" s="11" t="str"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B70" t="n">
+      <x:c r="A70" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B70" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C70" t="str">
+      <x:c r="C70" s="11" t="str">
         <x:v>International Journal of Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D70" t="str">
+      <x:c r="D70" s="11" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Fuzzy%20Systems</x:v>
       </x:c>
-      <x:c r="E70"/>
-      <x:c r="F70"/>
+      <x:c r="E70" s="11" t="str"/>
+      <x:c r="F70" s="11" t="str"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B71" t="n">
+      <x:c r="A71" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C71" t="str">
+      <x:c r="C71" s="11" t="str">
         <x:v>OR Spectrum</x:v>
       </x:c>
-      <x:c r="D71" t="str">
+      <x:c r="D71" s="11" t="str">
         <x:v>https://link.springer.com/search?query=OR%20Spectrum</x:v>
       </x:c>
-      <x:c r="E71"/>
-      <x:c r="F71"/>
+      <x:c r="E71" s="11" t="str"/>
+      <x:c r="F71" s="11" t="str"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B72" t="n">
+      <x:c r="A72" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C72" t="str">
+      <x:c r="C72" s="11" t="str">
         <x:v>Artificial Intelligence Review</x:v>
       </x:c>
-      <x:c r="D72" t="str">
+      <x:c r="D72" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Artificial%20Intelligence%20Review</x:v>
       </x:c>
-      <x:c r="E72"/>
-      <x:c r="F72"/>
+      <x:c r="E72" s="11" t="str"/>
+      <x:c r="F72" s="11" t="str"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B73" t="n">
+      <x:c r="A73" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C73" t="str">
+      <x:c r="C73" s="11" t="str">
         <x:v>Journal of Ambient Intelligence and Humanized Computing</x:v>
       </x:c>
-      <x:c r="D73" t="str">
+      <x:c r="D73" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Ambient%20Intelligence%20and%20Humanized%20Computing</x:v>
       </x:c>
-      <x:c r="E73"/>
-      <x:c r="F73"/>
+      <x:c r="E73" s="11" t="str"/>
+      <x:c r="F73" s="11" t="str"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B74" t="n">
+      <x:c r="A74" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B74" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C74" t="str">
+      <x:c r="C74" s="11" t="str">
         <x:v>Frontiers of Engineering Management</x:v>
       </x:c>
-      <x:c r="D74" t="str">
+      <x:c r="D74" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Frontiers%20of%20Engineering%20Management</x:v>
       </x:c>
-      <x:c r="E74"/>
-      <x:c r="F74"/>
+      <x:c r="E74" s="11" t="str"/>
+      <x:c r="F74" s="11" t="str"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B75" t="n">
+      <x:c r="A75" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B75" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C75" t="str">
+      <x:c r="C75" s="11" t="str">
         <x:v>Journal of Data, Information and Management</x:v>
       </x:c>
-      <x:c r="D75" t="str">
+      <x:c r="D75" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Data%2C%20Information%20and%20Management</x:v>
       </x:c>
-      <x:c r="E75"/>
-      <x:c r="F75"/>
+      <x:c r="E75" s="11" t="str"/>
+      <x:c r="F75" s="11" t="str"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B76" t="n">
+      <x:c r="A76" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B76" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C76" t="str">
+      <x:c r="C76" s="11" t="str">
         <x:v>Journal of Systems Science and Systems Engineering</x:v>
       </x:c>
-      <x:c r="D76" t="str">
+      <x:c r="D76" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Systems%20Engineering</x:v>
       </x:c>
-      <x:c r="E76"/>
-      <x:c r="F76"/>
+      <x:c r="E76" s="11" t="str"/>
+      <x:c r="F76" s="11" t="str"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B77" t="n">
+      <x:c r="A77" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B77" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C77" t="str">
+      <x:c r="C77" s="11" t="str">
         <x:v>Journal of Systems Science and Complexity</x:v>
       </x:c>
-      <x:c r="D77" t="str">
+      <x:c r="D77" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Complexity</x:v>
       </x:c>
-      <x:c r="E77"/>
-      <x:c r="F77"/>
+      <x:c r="E77" s="11" t="str"/>
+      <x:c r="F77" s="11" t="str"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B78" t="n">
+      <x:c r="A78" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B78" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C78" t="str">
+      <x:c r="C78" s="11" t="str">
         <x:v>Data Mining &amp; Knowledge Discovery</x:v>
       </x:c>
-      <x:c r="D78" t="str">
+      <x:c r="D78" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Data%20Mining%20%26%20Knowledge%20Discovery</x:v>
       </x:c>
-      <x:c r="E78"/>
-      <x:c r="F78"/>
+      <x:c r="E78" s="11" t="str"/>
+      <x:c r="F78" s="11" t="str"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B79" t="n">
+      <x:c r="A79" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B79" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C79" t="str">
+      <x:c r="C79" s="11" t="str">
         <x:v>Social Network Analysis and Mining</x:v>
       </x:c>
-      <x:c r="D79" t="str">
+      <x:c r="D79" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Social%20Network%20Analysis%20and%20Mining</x:v>
       </x:c>
-      <x:c r="E79"/>
-      <x:c r="F79"/>
+      <x:c r="E79" s="11" t="str"/>
+      <x:c r="F79" s="11" t="str"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B80" t="n">
+      <x:c r="A80" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B80" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C80" t="str">
+      <x:c r="C80" s="11" t="str">
         <x:v>Health Care Management Science</x:v>
       </x:c>
-      <x:c r="D80" t="str">
+      <x:c r="D80" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Health%20Care%20Management%20Science</x:v>
       </x:c>
-      <x:c r="E80"/>
-      <x:c r="F80"/>
+      <x:c r="E80" s="11" t="str"/>
+      <x:c r="F80" s="11" t="str"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B81" t="n">
+      <x:c r="A81" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C81" t="str">
+      <x:c r="C81" s="11" t="str">
         <x:v>Electronic Commerce Research</x:v>
       </x:c>
-      <x:c r="D81" t="str">
+      <x:c r="D81" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Electronic%20Commerce%20Research</x:v>
       </x:c>
-      <x:c r="E81"/>
-      <x:c r="F81"/>
+      <x:c r="E81" s="11" t="str"/>
+      <x:c r="F81" s="11" t="str"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B82" t="n">
+      <x:c r="A82" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B82" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C82" t="str">
+      <x:c r="C82" s="11" t="str">
         <x:v>Operational Research</x:v>
       </x:c>
-      <x:c r="D82" t="str">
+      <x:c r="D82" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Operational%20Research</x:v>
       </x:c>
-      <x:c r="E82"/>
-      <x:c r="F82"/>
+      <x:c r="E82" s="11" t="str"/>
+      <x:c r="F82" s="11" t="str"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B83" t="n">
+      <x:c r="A83" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C83" t="str">
+      <x:c r="C83" s="11" t="str">
         <x:v>Information Technology &amp; Tourism</x:v>
       </x:c>
-      <x:c r="D83" t="str">
+      <x:c r="D83" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Information%20Technology%20%26%20Tourism</x:v>
       </x:c>
-      <x:c r="E83"/>
-      <x:c r="F83"/>
+      <x:c r="E83" s="11" t="str"/>
+      <x:c r="F83" s="11" t="str"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B84" t="n">
+      <x:c r="A84" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C84" t="str">
+      <x:c r="C84" s="11" t="str">
         <x:v>TOP</x:v>
       </x:c>
-      <x:c r="D84" t="str">
+      <x:c r="D84" s="11" t="str">
         <x:v>https://link.springer.com/search?query=TOP</x:v>
       </x:c>
-      <x:c r="E84"/>
-      <x:c r="F84"/>
+      <x:c r="E84" s="11" t="str"/>
+      <x:c r="F84" s="11" t="str"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B85" t="n">
+      <x:c r="A85" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C85" t="str">
+      <x:c r="C85" s="11" t="str">
         <x:v>Theory and Decision</x:v>
       </x:c>
-      <x:c r="D85" t="str">
+      <x:c r="D85" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Theory%20and%20Decision</x:v>
       </x:c>
-      <x:c r="E85"/>
-      <x:c r="F85"/>
+      <x:c r="E85" s="11" t="str"/>
+      <x:c r="F85" s="11" t="str"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B86" t="n">
+      <x:c r="A86" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B86" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C86" t="str">
+      <x:c r="C86" s="11" t="str">
         <x:v>Annals of Data Science</x:v>
       </x:c>
-      <x:c r="D86" t="str">
+      <x:c r="D86" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E86"/>
-      <x:c r="F86"/>
+      <x:c r="E86" s="11" t="str"/>
+      <x:c r="F86" s="11" t="str"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B87" t="n">
+      <x:c r="A87" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C87" t="str">
+      <x:c r="C87" s="11" t="str">
         <x:v>Central European Journal of Operations Research</x:v>
       </x:c>
-      <x:c r="D87" t="str">
+      <x:c r="D87" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Central%20European%20Journal%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E87"/>
-      <x:c r="F87"/>
+      <x:c r="E87" s="11" t="str"/>
+      <x:c r="F87" s="11" t="str"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B88" t="n">
+      <x:c r="A88" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B88" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C88" t="str">
-        <x:v>SCIENCE CHINA Information Sciences</x:v>
-      </x:c>
-      <x:c r="D88" t="str">
+      <x:c r="C88" s="11" t="str">
+        <x:v>Science China Information Sciences</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="str">
         <x:v>https://www.sciengine.com</x:v>
       </x:c>
-      <x:c r="E88"/>
-      <x:c r="F88"/>
+      <x:c r="E88" s="11" t="str"/>
+      <x:c r="F88" s="11" t="str"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B89" t="n">
+      <x:c r="A89" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C89" t="str">
+      <x:c r="C89" s="11" t="str">
         <x:v>Progress in Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D89" t="str">
+      <x:c r="D89" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Progress%20in%20Artificial%20Intelligence</x:v>
       </x:c>
-      <x:c r="E89"/>
-      <x:c r="F89"/>
+      <x:c r="E89" s="11" t="str"/>
+      <x:c r="F89" s="11" t="str"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B90" t="n">
+      <x:c r="A90" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B90" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C90" t="str">
+      <x:c r="C90" s="11" t="str">
         <x:v>Granular Computing</x:v>
       </x:c>
-      <x:c r="D90" t="str">
+      <x:c r="D90" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Granular%20Computing</x:v>
       </x:c>
-      <x:c r="E90"/>
-      <x:c r="F90"/>
+      <x:c r="E90" s="11" t="str"/>
+      <x:c r="F90" s="11" t="str"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B91" t="n">
+      <x:c r="A91" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C91" t="str">
+      <x:c r="C91" s="11" t="str">
         <x:v>Journal of Intelligent Manufacturing</x:v>
       </x:c>
-      <x:c r="D91" t="str">
+      <x:c r="D91" s="11" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Intelligent%20Manufacturing</x:v>
       </x:c>
-      <x:c r="E91"/>
-      <x:c r="F91"/>
+      <x:c r="E91" s="11" t="str"/>
+      <x:c r="F91" s="11" t="str"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B92" t="n">
+      <x:c r="A92" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B92" s="11" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C92" t="str">
+      <x:c r="C92" s="11" t="str">
         <x:v>Nature Computational Science</x:v>
       </x:c>
-      <x:c r="D92" t="str">
+      <x:c r="D92" s="11" t="str">
         <x:v>https://www.nature.com</x:v>
       </x:c>
-      <x:c r="E92"/>
-      <x:c r="F92"/>
+      <x:c r="E92" s="11" t="str"/>
+      <x:c r="F92" s="11" t="str"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B93" t="n">
+      <x:c r="A93" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B93" s="11" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C93" t="str">
+      <x:c r="C93" s="11" t="str">
         <x:v>Nature Machine Intelligence</x:v>
       </x:c>
-      <x:c r="D93" t="str">
+      <x:c r="D93" s="11" t="str">
         <x:v>https://www.nature.com</x:v>
       </x:c>
-      <x:c r="E93"/>
-      <x:c r="F93"/>
+      <x:c r="E93" s="11" t="str"/>
+      <x:c r="F93" s="11" t="str"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B94" t="n">
+      <x:c r="A94" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B94" s="11" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C94" t="str">
+      <x:c r="C94" s="11" t="str">
         <x:v>npj Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D94" t="str">
+      <x:c r="D94" s="11" t="str">
         <x:v>https://www.nature.com</x:v>
       </x:c>
-      <x:c r="E94"/>
-      <x:c r="F94"/>
+      <x:c r="E94" s="11" t="str"/>
+      <x:c r="F94" s="11" t="str"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" t="str">
-        <x:v>Springer</x:v>
-      </x:c>
-      <x:c r="B95" t="n">
+      <x:c r="A95" s="11" t="str">
+        <x:v>Springer</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C95" t="str">
+      <x:c r="C95" s="11" t="str">
         <x:v>Nature Communications</x:v>
       </x:c>
-      <x:c r="D95" t="str">
+      <x:c r="D95" s="11" t="str">
         <x:v>https://www.nature.com</x:v>
       </x:c>
-      <x:c r="E95"/>
-      <x:c r="F95"/>
+      <x:c r="E95" s="11" t="str"/>
+      <x:c r="F95" s="11" t="str"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B96" t="n">
+      <x:c r="A96" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B96" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C96" t="str">
+      <x:c r="C96" s="11" t="str">
         <x:v>IEEE Transactions on Systems, Man, and Cybernetics: Systems</x:v>
       </x:c>
-      <x:c r="D96" t="str">
+      <x:c r="D96" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E96"/>
-      <x:c r="F96"/>
+      <x:c r="E96" s="11" t="str"/>
+      <x:c r="F96" s="11" t="str"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B97" t="n">
+      <x:c r="A97" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B97" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C97" t="str">
+      <x:c r="C97" s="11" t="str">
         <x:v>IEEE Transactions on Cybernetics</x:v>
       </x:c>
-      <x:c r="D97" t="str">
+      <x:c r="D97" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E97"/>
-      <x:c r="F97"/>
+      <x:c r="E97" s="11" t="str"/>
+      <x:c r="F97" s="11" t="str"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B98" t="n">
+      <x:c r="A98" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B98" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C98" t="str">
+      <x:c r="C98" s="11" t="str">
         <x:v>IEEE Transactions on Computational Social Systems</x:v>
       </x:c>
-      <x:c r="D98" t="str">
+      <x:c r="D98" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E98"/>
-      <x:c r="F98"/>
+      <x:c r="E98" s="11" t="str"/>
+      <x:c r="F98" s="11" t="str"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B99" t="n">
+      <x:c r="A99" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C99" t="str">
+      <x:c r="C99" s="11" t="str">
         <x:v>IEEE Transactions on Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D99" t="str">
+      <x:c r="D99" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E99"/>
-      <x:c r="F99"/>
+      <x:c r="E99" s="11" t="str"/>
+      <x:c r="F99" s="11" t="str"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B100" t="n">
+      <x:c r="A100" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B100" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C100" t="str">
+      <x:c r="C100" s="11" t="str">
         <x:v>IEEE Transactions on Reliability</x:v>
       </x:c>
-      <x:c r="D100" t="str">
+      <x:c r="D100" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E100"/>
-      <x:c r="F100"/>
+      <x:c r="E100" s="11" t="str"/>
+      <x:c r="F100" s="11" t="str"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B101" t="n">
+      <x:c r="A101" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C101" t="str">
+      <x:c r="C101" s="11" t="str">
         <x:v>IEEE Transactions on Engineering Management</x:v>
       </x:c>
-      <x:c r="D101" t="str">
+      <x:c r="D101" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E101"/>
-      <x:c r="F101"/>
+      <x:c r="E101" s="11" t="str"/>
+      <x:c r="F101" s="11" t="str"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B102" t="n">
+      <x:c r="A102" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B102" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C102" t="str">
+      <x:c r="C102" s="11" t="str">
         <x:v>IEEE Transactions on Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D102" t="str">
+      <x:c r="D102" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E102"/>
-      <x:c r="F102"/>
+      <x:c r="E102" s="11" t="str"/>
+      <x:c r="F102" s="11" t="str"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B103" t="n">
+      <x:c r="A103" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B103" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C103" t="str">
+      <x:c r="C103" s="11" t="str">
         <x:v>IEEE Transactions on Knowledge and Data Engineering</x:v>
       </x:c>
-      <x:c r="D103" t="str">
+      <x:c r="D103" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E103"/>
-      <x:c r="F103"/>
+      <x:c r="E103" s="11" t="str"/>
+      <x:c r="F103" s="11" t="str"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B104" t="n">
+      <x:c r="A104" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B104" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C104" t="str">
+      <x:c r="C104" s="11" t="str">
         <x:v>IEEE Transactions on Evolutionary Computation</x:v>
       </x:c>
-      <x:c r="D104" t="str">
+      <x:c r="D104" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E104"/>
-      <x:c r="F104"/>
+      <x:c r="E104" s="11" t="str"/>
+      <x:c r="F104" s="11" t="str"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B105" t="n">
+      <x:c r="A105" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B105" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C105" t="str">
+      <x:c r="C105" s="11" t="str">
         <x:v>IEEE Transactions on Neural Networks and Learning Systems</x:v>
       </x:c>
-      <x:c r="D105" t="str">
+      <x:c r="D105" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E105"/>
-      <x:c r="F105"/>
+      <x:c r="E105" s="11" t="str"/>
+      <x:c r="F105" s="11" t="str"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B106" t="n">
+      <x:c r="A106" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B106" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C106" t="str">
+      <x:c r="C106" s="11" t="str">
         <x:v>IEEE Transactions on Pattern Analysis and Machine Intelligence</x:v>
       </x:c>
-      <x:c r="D106" t="str">
+      <x:c r="D106" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E106"/>
-      <x:c r="F106"/>
+      <x:c r="E106" s="11" t="str"/>
+      <x:c r="F106" s="11" t="str"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B107" t="n">
+      <x:c r="A107" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B107" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C107" t="str">
+      <x:c r="C107" s="11" t="str">
         <x:v>IEEE Transactions on Big Data</x:v>
       </x:c>
-      <x:c r="D107" t="str">
+      <x:c r="D107" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E107"/>
-      <x:c r="F107"/>
+      <x:c r="E107" s="11" t="str"/>
+      <x:c r="F107" s="11" t="str"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B108" t="n">
+      <x:c r="A108" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B108" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C108" t="str">
+      <x:c r="C108" s="11" t="str">
         <x:v>IEEE Transactions on Network Science and Engineering</x:v>
       </x:c>
-      <x:c r="D108" t="str">
+      <x:c r="D108" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E108"/>
-      <x:c r="F108"/>
+      <x:c r="E108" s="11" t="str"/>
+      <x:c r="F108" s="11" t="str"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B109" t="n">
+      <x:c r="A109" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C109" t="str">
+      <x:c r="C109" s="11" t="str">
         <x:v>IEEE/CAA Journal of Automatica Sinica</x:v>
       </x:c>
-      <x:c r="D109" t="str">
+      <x:c r="D109" s="11" t="str">
         <x:v>https://www.ieee-jas.net</x:v>
       </x:c>
-      <x:c r="E109"/>
-      <x:c r="F109"/>
+      <x:c r="E109" s="11" t="str"/>
+      <x:c r="F109" s="11" t="str"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B110" t="n">
+      <x:c r="A110" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B110" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C110" t="str">
+      <x:c r="C110" s="11" t="str">
         <x:v>IEEE Transactions on Cognitive and Developmental Systems</x:v>
       </x:c>
-      <x:c r="D110" t="str">
+      <x:c r="D110" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E110"/>
-      <x:c r="F110"/>
+      <x:c r="E110" s="11" t="str"/>
+      <x:c r="F110" s="11" t="str"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B111" t="n">
+      <x:c r="A111" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B111" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C111" t="str">
+      <x:c r="C111" s="11" t="str">
         <x:v>IEEE Transactions on Emerging Topics in Computational Intelligence</x:v>
       </x:c>
-      <x:c r="D111" t="str">
+      <x:c r="D111" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E111"/>
-      <x:c r="F111"/>
+      <x:c r="E111" s="11" t="str"/>
+      <x:c r="F111" s="11" t="str"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B112" t="n">
+      <x:c r="A112" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B112" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C112" t="str">
+      <x:c r="C112" s="11" t="str">
         <x:v>IEEE Systems Journal</x:v>
       </x:c>
-      <x:c r="D112" t="str">
+      <x:c r="D112" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E112"/>
-      <x:c r="F112"/>
+      <x:c r="E112" s="11" t="str"/>
+      <x:c r="F112" s="11" t="str"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B113" t="n">
+      <x:c r="A113" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B113" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C113" t="str">
+      <x:c r="C113" s="11" t="str">
         <x:v>IEEE Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D113" t="str">
+      <x:c r="D113" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E113"/>
-      <x:c r="F113"/>
+      <x:c r="E113" s="11" t="str"/>
+      <x:c r="F113" s="11" t="str"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B114" t="n">
+      <x:c r="A114" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B114" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C114" t="str">
+      <x:c r="C114" s="11" t="str">
         <x:v>Journal of Systems Engineering and Electronics</x:v>
       </x:c>
-      <x:c r="D114" t="str">
+      <x:c r="D114" s="11" t="str">
         <x:v>https://www.jseepub.com</x:v>
       </x:c>
-      <x:c r="E114"/>
-      <x:c r="F114"/>
+      <x:c r="E114" s="11" t="str"/>
+      <x:c r="F114" s="11" t="str"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B115" t="n">
+      <x:c r="A115" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B115" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C115" t="str">
+      <x:c r="C115" s="11" t="str">
         <x:v>IEEE Transactions on Automation Science and Engineering</x:v>
       </x:c>
-      <x:c r="D115" t="str">
+      <x:c r="D115" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E115"/>
-      <x:c r="F115"/>
+      <x:c r="E115" s="11" t="str"/>
+      <x:c r="F115" s="11" t="str"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B116" t="n">
+      <x:c r="A116" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B116" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C116" t="str">
+      <x:c r="C116" s="11" t="str">
         <x:v>IEEE Transactions on Automatic Control</x:v>
       </x:c>
-      <x:c r="D116" t="str">
+      <x:c r="D116" s="11" t="str">
         <x:v>https://ieeexplore.ieee.org</x:v>
       </x:c>
-      <x:c r="E116"/>
-      <x:c r="F116"/>
+      <x:c r="E116" s="11" t="str"/>
+      <x:c r="F116" s="11" t="str"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B117" t="n">
+      <x:c r="A117" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B117" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C117" t="str">
+      <x:c r="C117" s="11" t="str">
         <x:v>Management Science</x:v>
       </x:c>
-      <x:c r="D117" t="str">
+      <x:c r="D117" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Management%20Science</x:v>
       </x:c>
-      <x:c r="E117"/>
-      <x:c r="F117"/>
+      <x:c r="E117" s="11" t="str"/>
+      <x:c r="F117" s="11" t="str"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B118" t="n">
+      <x:c r="A118" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B118" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C118" t="str">
+      <x:c r="C118" s="11" t="str">
         <x:v>Operations Research</x:v>
       </x:c>
-      <x:c r="D118" t="str">
+      <x:c r="D118" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Operations%20Research</x:v>
       </x:c>
-      <x:c r="E118"/>
-      <x:c r="F118"/>
+      <x:c r="E118" s="11" t="str"/>
+      <x:c r="F118" s="11" t="str"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B119" t="n">
+      <x:c r="A119" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B119" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C119" t="str">
+      <x:c r="C119" s="11" t="str">
         <x:v>INFORMS Journal on Computing</x:v>
       </x:c>
-      <x:c r="D119" t="str">
+      <x:c r="D119" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Computing</x:v>
       </x:c>
-      <x:c r="E119"/>
-      <x:c r="F119"/>
+      <x:c r="E119" s="11" t="str"/>
+      <x:c r="F119" s="11" t="str"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B120" t="n">
+      <x:c r="A120" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B120" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C120" t="str">
+      <x:c r="C120" s="11" t="str">
         <x:v>Information Systems Research</x:v>
       </x:c>
-      <x:c r="D120" t="str">
+      <x:c r="D120" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Information%20Systems%20Research</x:v>
       </x:c>
-      <x:c r="E120"/>
-      <x:c r="F120"/>
+      <x:c r="E120" s="11" t="str"/>
+      <x:c r="F120" s="11" t="str"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B121" t="n">
+      <x:c r="A121" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B121" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C121" t="str">
+      <x:c r="C121" s="11" t="str">
         <x:v>Manufacturing &amp; Service Operations Management</x:v>
       </x:c>
-      <x:c r="D121" t="str">
+      <x:c r="D121" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Manufacturing%20%26%20Service%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E121"/>
-      <x:c r="F121"/>
+      <x:c r="E121" s="11" t="str"/>
+      <x:c r="F121" s="11" t="str"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B122" t="n">
+      <x:c r="A122" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B122" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C122" t="str">
+      <x:c r="C122" s="11" t="str">
         <x:v>Decision Analysis</x:v>
       </x:c>
-      <x:c r="D122" t="str">
+      <x:c r="D122" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E122"/>
-      <x:c r="F122"/>
+      <x:c r="E122" s="11" t="str"/>
+      <x:c r="F122" s="11" t="str"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B123" t="n">
+      <x:c r="A123" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B123" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C123" t="str">
+      <x:c r="C123" s="11" t="str">
         <x:v>Production and Operations Management</x:v>
       </x:c>
-      <x:c r="D123" t="str">
+      <x:c r="D123" s="11" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Production%20and%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E123"/>
-      <x:c r="F123"/>
+      <x:c r="E123" s="11" t="str"/>
+      <x:c r="F123" s="11" t="str"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B124" t="n">
+      <x:c r="A124" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B124" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C124" t="str">
+      <x:c r="C124" s="11" t="str">
         <x:v>INFORMS Journal on Data Science</x:v>
       </x:c>
-      <x:c r="D124" t="str">
+      <x:c r="D124" s="11" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E124"/>
-      <x:c r="F124"/>
+      <x:c r="E124" s="11" t="str"/>
+      <x:c r="F124" s="11" t="str"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B125" t="n">
+      <x:c r="A125" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B125" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C125" t="str">
+      <x:c r="C125" s="11" t="str">
         <x:v>ACM Computing Surveys</x:v>
       </x:c>
-      <x:c r="D125" t="str">
+      <x:c r="D125" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Computing%20Surveys</x:v>
       </x:c>
-      <x:c r="E125"/>
-      <x:c r="F125"/>
+      <x:c r="E125" s="11" t="str"/>
+      <x:c r="F125" s="11" t="str"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B126" t="n">
+      <x:c r="A126" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B126" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C126" t="str">
+      <x:c r="C126" s="11" t="str">
         <x:v>ACM Transactions on Intelligent Systems and Technology</x:v>
       </x:c>
-      <x:c r="D126" t="str">
+      <x:c r="D126" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Intelligent%20Systems%20and%20Technology</x:v>
       </x:c>
-      <x:c r="E126"/>
-      <x:c r="F126"/>
+      <x:c r="E126" s="11" t="str"/>
+      <x:c r="F126" s="11" t="str"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B127" t="n">
+      <x:c r="A127" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B127" s="11" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C127" t="str">
+      <x:c r="C127" s="11" t="str">
         <x:v>ACM Transactions on Knowledge Discovery from Data</x:v>
       </x:c>
-      <x:c r="D127" t="str">
+      <x:c r="D127" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Knowledge%20Discovery%20from%20Data</x:v>
       </x:c>
-      <x:c r="E127"/>
-      <x:c r="F127"/>
+      <x:c r="E127" s="11" t="str"/>
+      <x:c r="F127" s="11" t="str"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B128" t="n">
+      <x:c r="A128" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B128" s="11" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C128" t="str">
+      <x:c r="C128" s="11" t="str">
         <x:v>ACM Transactions on Management Information Systems</x:v>
       </x:c>
-      <x:c r="D128" t="str">
+      <x:c r="D128" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Management%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E128"/>
-      <x:c r="F128"/>
+      <x:c r="E128" s="11" t="str"/>
+      <x:c r="F128" s="11" t="str"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B129" t="n">
+      <x:c r="A129" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B129" s="11" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C129" t="str">
+      <x:c r="C129" s="11" t="str">
         <x:v>ACM Transactions on Information Systems</x:v>
       </x:c>
-      <x:c r="D129" t="str">
+      <x:c r="D129" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E129"/>
-      <x:c r="F129"/>
+      <x:c r="E129" s="11" t="str"/>
+      <x:c r="F129" s="11" t="str"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B130" t="n">
+      <x:c r="A130" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B130" s="11" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C130" t="str">
+      <x:c r="C130" s="11" t="str">
         <x:v>ACM Transactions on Internet Technology</x:v>
       </x:c>
-      <x:c r="D130" t="str">
+      <x:c r="D130" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Internet%20Technology</x:v>
       </x:c>
-      <x:c r="E130"/>
-      <x:c r="F130"/>
+      <x:c r="E130" s="11" t="str"/>
+      <x:c r="F130" s="11" t="str"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B131" t="n">
+      <x:c r="A131" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B131" s="11" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C131" t="str">
+      <x:c r="C131" s="11" t="str">
         <x:v>ACM Transactions on Modeling and Computer Simulation</x:v>
       </x:c>
-      <x:c r="D131" t="str">
+      <x:c r="D131" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Modeling%20and%20Computer%20Simulation</x:v>
       </x:c>
-      <x:c r="E131"/>
-      <x:c r="F131"/>
+      <x:c r="E131" s="11" t="str"/>
+      <x:c r="F131" s="11" t="str"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B132" t="n">
+      <x:c r="A132" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B132" s="11" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C132" t="str">
+      <x:c r="C132" s="11" t="str">
         <x:v>ACM Transactions on Social Computing</x:v>
       </x:c>
-      <x:c r="D132" t="str">
+      <x:c r="D132" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Social%20Computing</x:v>
       </x:c>
-      <x:c r="E132"/>
-      <x:c r="F132"/>
+      <x:c r="E132" s="11" t="str"/>
+      <x:c r="F132" s="11" t="str"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B133" t="n">
+      <x:c r="A133" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B133" s="11" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C133" t="str">
+      <x:c r="C133" s="11" t="str">
         <x:v>ACM Transactions on the Web</x:v>
       </x:c>
-      <x:c r="D133" t="str">
+      <x:c r="D133" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20the%20Web</x:v>
       </x:c>
-      <x:c r="E133"/>
-      <x:c r="F133"/>
+      <x:c r="E133" s="11" t="str"/>
+      <x:c r="F133" s="11" t="str"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B134" t="n">
+      <x:c r="A134" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B134" s="11" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C134" t="str">
+      <x:c r="C134" s="11" t="str">
         <x:v>ACM Transactions on Recommender Systems</x:v>
       </x:c>
-      <x:c r="D134" t="str">
+      <x:c r="D134" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Recommender%20Systems</x:v>
       </x:c>
-      <x:c r="E134"/>
-      <x:c r="F134"/>
+      <x:c r="E134" s="11" t="str"/>
+      <x:c r="F134" s="11" t="str"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B135" t="n">
+      <x:c r="A135" s="11" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B135" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C135" t="str">
+      <x:c r="C135" s="11" t="str">
         <x:v>ACM/IMS Transactions on Data Science</x:v>
       </x:c>
-      <x:c r="D135" t="str">
+      <x:c r="D135" s="11" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM/IMS%20Transactions%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E135"/>
-      <x:c r="F135"/>
+      <x:c r="E135" s="11" t="str"/>
+      <x:c r="F135" s="11" t="str"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" t="str">
+      <x:c r="A136" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B136" t="n">
+      <x:c r="B136" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C136" t="str">
+      <x:c r="C136" s="11" t="str">
         <x:v>Journal of Forecasting</x:v>
       </x:c>
-      <x:c r="D136" t="str">
+      <x:c r="D136" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Forecasting</x:v>
       </x:c>
-      <x:c r="E136"/>
-      <x:c r="F136"/>
+      <x:c r="E136" s="11" t="str"/>
+      <x:c r="F136" s="11" t="str"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" t="str">
+      <x:c r="A137" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B137" t="n">
+      <x:c r="B137" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C137" t="str">
+      <x:c r="C137" s="11" t="str">
         <x:v>International Journal of Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D137" t="str">
+      <x:c r="D137" s="11" t="str">
         <x:v>https://www.hindawi.com</x:v>
       </x:c>
-      <x:c r="E137"/>
-      <x:c r="F137"/>
+      <x:c r="E137" s="11" t="str"/>
+      <x:c r="F137" s="11" t="str"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" t="str">
+      <x:c r="A138" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B138" t="n">
+      <x:c r="B138" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C138" t="str">
+      <x:c r="C138" s="11" t="str">
         <x:v>Expert Systems</x:v>
       </x:c>
-      <x:c r="D138" t="str">
+      <x:c r="D138" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Expert%20Systems</x:v>
       </x:c>
-      <x:c r="E138"/>
-      <x:c r="F138"/>
+      <x:c r="E138" s="11" t="str"/>
+      <x:c r="F138" s="11" t="str"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" t="str">
+      <x:c r="A139" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B139" t="n">
+      <x:c r="B139" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C139" t="str">
+      <x:c r="C139" s="11" t="str">
         <x:v>International Transactions in Operational Research</x:v>
       </x:c>
-      <x:c r="D139" t="str">
+      <x:c r="D139" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Transactions%20in%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E139"/>
-      <x:c r="F139"/>
+      <x:c r="E139" s="11" t="str"/>
+      <x:c r="F139" s="11" t="str"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" t="str">
+      <x:c r="A140" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B140" t="n">
+      <x:c r="B140" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C140" t="str">
+      <x:c r="C140" s="11" t="str">
         <x:v>Journal of Multi-Criteria Decision Analysis</x:v>
       </x:c>
-      <x:c r="D140" t="str">
+      <x:c r="D140" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Multi-Criteria%20Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E140"/>
-      <x:c r="F140"/>
+      <x:c r="E140" s="11" t="str"/>
+      <x:c r="F140" s="11" t="str"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" t="str">
+      <x:c r="A141" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B141" t="n">
+      <x:c r="B141" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C141" t="str">
+      <x:c r="C141" s="11" t="str">
         <x:v>Decision Sciences Journal</x:v>
       </x:c>
-      <x:c r="D141" t="str">
+      <x:c r="D141" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Decision%20Sciences%20Journal</x:v>
       </x:c>
-      <x:c r="E141"/>
-      <x:c r="F141"/>
+      <x:c r="E141" s="11" t="str"/>
+      <x:c r="F141" s="11" t="str"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" t="str">
+      <x:c r="A142" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B142" t="n">
+      <x:c r="B142" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C142" t="str">
+      <x:c r="C142" s="11" t="str">
         <x:v>Risk Analysis</x:v>
       </x:c>
-      <x:c r="D142" t="str">
+      <x:c r="D142" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Risk%20Analysis</x:v>
       </x:c>
-      <x:c r="E142"/>
-      <x:c r="F142"/>
+      <x:c r="E142" s="11" t="str"/>
+      <x:c r="F142" s="11" t="str"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" t="str">
+      <x:c r="A143" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B143" t="n">
+      <x:c r="B143" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C143" t="str">
+      <x:c r="C143" s="11" t="str">
         <x:v>International Journal of Finance &amp; Economics</x:v>
       </x:c>
-      <x:c r="D143" t="str">
+      <x:c r="D143" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Finance%20%26%20Economics</x:v>
       </x:c>
-      <x:c r="E143"/>
-      <x:c r="F143"/>
+      <x:c r="E143" s="11" t="str"/>
+      <x:c r="F143" s="11" t="str"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" t="str">
+      <x:c r="A144" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B144" t="n">
+      <x:c r="B144" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C144" t="str">
+      <x:c r="C144" s="11" t="str">
         <x:v>Quality and Reliability Engineering International</x:v>
       </x:c>
-      <x:c r="D144" t="str">
+      <x:c r="D144" s="11" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Quality%20and%20Reliability%20Engineering%20International</x:v>
       </x:c>
-      <x:c r="E144"/>
-      <x:c r="F144"/>
+      <x:c r="E144" s="11" t="str"/>
+      <x:c r="F144" s="11" t="str"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" t="str">
+      <x:c r="A145" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B145" t="n">
+      <x:c r="B145" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C145" t="str">
+      <x:c r="C145" s="11" t="str">
         <x:v>IISE Transactions</x:v>
       </x:c>
-      <x:c r="D145" t="str">
+      <x:c r="D145" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=IISE%20Transactions</x:v>
       </x:c>
-      <x:c r="E145"/>
-      <x:c r="F145"/>
+      <x:c r="E145" s="11" t="str"/>
+      <x:c r="F145" s="11" t="str"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" t="str">
+      <x:c r="A146" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B146" t="n">
+      <x:c r="B146" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C146" t="str">
+      <x:c r="C146" s="11" t="str">
         <x:v>Journal of the Operational Research Society</x:v>
       </x:c>
-      <x:c r="D146" t="str">
+      <x:c r="D146" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20the%20Operational%20Research%20Society</x:v>
       </x:c>
-      <x:c r="E146"/>
-      <x:c r="F146"/>
+      <x:c r="E146" s="11" t="str"/>
+      <x:c r="F146" s="11" t="str"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" t="str">
+      <x:c r="A147" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B147" t="n">
+      <x:c r="B147" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C147" t="str">
+      <x:c r="C147" s="11" t="str">
         <x:v>International Journal of Production Research</x:v>
       </x:c>
-      <x:c r="D147" t="str">
+      <x:c r="D147" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Production%20Research</x:v>
       </x:c>
-      <x:c r="E147"/>
-      <x:c r="F147"/>
+      <x:c r="E147" s="11" t="str"/>
+      <x:c r="F147" s="11" t="str"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" t="str">
+      <x:c r="A148" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B148" t="n">
+      <x:c r="B148" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C148" t="str">
+      <x:c r="C148" s="11" t="str">
         <x:v>International Journal of Systems Science</x:v>
       </x:c>
-      <x:c r="D148" t="str">
+      <x:c r="D148" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Systems%20Science</x:v>
       </x:c>
-      <x:c r="E148"/>
-      <x:c r="F148"/>
+      <x:c r="E148" s="11" t="str"/>
+      <x:c r="F148" s="11" t="str"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" t="str">
+      <x:c r="A149" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B149" t="n">
+      <x:c r="B149" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C149" t="str">
+      <x:c r="C149" s="11" t="str">
         <x:v>International Journal of General Systems</x:v>
       </x:c>
-      <x:c r="D149" t="str">
+      <x:c r="D149" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20General%20Systems</x:v>
       </x:c>
-      <x:c r="E149"/>
-      <x:c r="F149"/>
+      <x:c r="E149" s="11" t="str"/>
+      <x:c r="F149" s="11" t="str"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" t="str">
+      <x:c r="A150" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B150" t="n">
+      <x:c r="B150" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C150" t="str">
+      <x:c r="C150" s="11" t="str">
         <x:v>International Journal of Information Technology &amp; Decision Making</x:v>
       </x:c>
-      <x:c r="D150" t="str">
+      <x:c r="D150" s="11" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Information%20Technology%20%26%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E150"/>
-      <x:c r="F150"/>
+      <x:c r="E150" s="11" t="str"/>
+      <x:c r="F150" s="11" t="str"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" t="str">
+      <x:c r="A151" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B151" t="n">
+      <x:c r="B151" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C151" t="str">
+      <x:c r="C151" s="11" t="str">
         <x:v>International Journal of Uncertainty, Fuzziness and Knowledge-Based Systems</x:v>
       </x:c>
-      <x:c r="D151" t="str">
+      <x:c r="D151" s="11" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Uncertainty%2C%20Fuzziness%20and%20Knowledge-Based%20Systems</x:v>
       </x:c>
-      <x:c r="E151"/>
-      <x:c r="F151"/>
+      <x:c r="E151" s="11" t="str"/>
+      <x:c r="F151" s="11" t="str"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" t="str">
+      <x:c r="A152" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B152" t="n">
+      <x:c r="B152" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C152" t="str">
+      <x:c r="C152" s="11" t="str">
         <x:v>Asia-Pacific Journal of Operational Research</x:v>
       </x:c>
-      <x:c r="D152" t="str">
+      <x:c r="D152" s="11" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=Asia-Pacific%20Journal%20of%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E152"/>
-      <x:c r="F152"/>
+      <x:c r="E152" s="11" t="str"/>
+      <x:c r="F152" s="11" t="str"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" t="str">
+      <x:c r="A153" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B153" t="n">
+      <x:c r="B153" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C153" t="str">
+      <x:c r="C153" s="11" t="str">
         <x:v>Economic Research</x:v>
       </x:c>
-      <x:c r="D153" t="str">
+      <x:c r="D153" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Economic%20Research</x:v>
       </x:c>
-      <x:c r="E153"/>
-      <x:c r="F153"/>
+      <x:c r="E153" s="11" t="str"/>
+      <x:c r="F153" s="11" t="str"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" t="str">
+      <x:c r="A154" s="11" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B154" t="n">
+      <x:c r="B154" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C154" t="str">
+      <x:c r="C154" s="11" t="str">
         <x:v>Journal of Management Analytics</x:v>
       </x:c>
-      <x:c r="D154" t="str">
+      <x:c r="D154" s="11" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Management%20Analytics</x:v>
       </x:c>
-      <x:c r="E154"/>
-      <x:c r="F154"/>
+      <x:c r="E154" s="11" t="str"/>
+      <x:c r="F154" s="11" t="str"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" t="str">
+      <x:c r="A155" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B155" t="n">
+      <x:c r="B155" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C155" t="str">
+      <x:c r="C155" s="11" t="str">
         <x:v>International Journal of Computational Intelligence Systems</x:v>
       </x:c>
-      <x:c r="D155" t="str">
+      <x:c r="D155" s="11" t="str">
         <x:v>https://www.springer.com/search?query=International%20Journal%20of%20Computational%20Intelligence%20Systems</x:v>
       </x:c>
-      <x:c r="E155"/>
-      <x:c r="F155"/>
+      <x:c r="E155" s="11" t="str"/>
+      <x:c r="F155" s="11" t="str"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" t="str">
+      <x:c r="A156" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B156" t="n">
+      <x:c r="B156" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C156" t="str">
+      <x:c r="C156" s="11" t="str">
         <x:v>Technological and Economic Development of Economy</x:v>
       </x:c>
-      <x:c r="D156" t="str">
+      <x:c r="D156" s="11" t="str">
         <x:v>https://journals.vgtu.lt</x:v>
       </x:c>
-      <x:c r="E156"/>
-      <x:c r="F156"/>
+      <x:c r="E156" s="11" t="str"/>
+      <x:c r="F156" s="11" t="str"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" t="str">
+      <x:c r="A157" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B157" t="n">
+      <x:c r="B157" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C157" t="str">
+      <x:c r="C157" s="11" t="str">
         <x:v>INFORMATICA</x:v>
       </x:c>
-      <x:c r="D157" t="str">
+      <x:c r="D157" s="11" t="str">
         <x:v>https://informatica.vu.lt</x:v>
       </x:c>
-      <x:c r="E157"/>
-      <x:c r="F157"/>
+      <x:c r="E157" s="11" t="str"/>
+      <x:c r="F157" s="11" t="str"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" t="str">
+      <x:c r="A158" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B158" t="n">
+      <x:c r="B158" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C158" t="str">
+      <x:c r="C158" s="11" t="str">
         <x:v>International Journal of Computers Communications &amp; Control</x:v>
       </x:c>
-      <x:c r="D158" t="str">
+      <x:c r="D158" s="11" t="str">
         <x:v>https://univagora.ro</x:v>
       </x:c>
-      <x:c r="E158"/>
-      <x:c r="F158"/>
+      <x:c r="E158" s="11" t="str"/>
+      <x:c r="F158" s="11" t="str"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" t="str">
+      <x:c r="A159" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B159" t="n">
+      <x:c r="B159" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C159" t="str">
+      <x:c r="C159" s="11" t="str">
         <x:v>International Journal of Strategic Property Management</x:v>
       </x:c>
-      <x:c r="D159" t="str">
+      <x:c r="D159" s="11" t="str">
         <x:v>https://journals.vgtu.lt</x:v>
       </x:c>
-      <x:c r="E159"/>
-      <x:c r="F159"/>
+      <x:c r="E159" s="11" t="str"/>
+      <x:c r="F159" s="11" t="str"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" t="str">
+      <x:c r="A160" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B160" t="n">
+      <x:c r="B160" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C160" t="str">
+      <x:c r="C160" s="11" t="str">
         <x:v>Transport</x:v>
       </x:c>
-      <x:c r="D160" t="str">
+      <x:c r="D160" s="11" t="str">
         <x:v>https://journals.vgtu.lt</x:v>
       </x:c>
-      <x:c r="E160"/>
-      <x:c r="F160"/>
+      <x:c r="E160" s="11" t="str"/>
+      <x:c r="F160" s="11" t="str"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" t="str">
+      <x:c r="A161" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B161" t="n">
+      <x:c r="B161" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C161" t="str">
+      <x:c r="C161" s="11" t="str">
         <x:v>Transformations in Business &amp; Economics</x:v>
       </x:c>
-      <x:c r="D161" t="str">
+      <x:c r="D161" s="11" t="str">
         <x:v>https://www.transformations.knf.vu.lt</x:v>
       </x:c>
-      <x:c r="E161"/>
-      <x:c r="F161"/>
+      <x:c r="E161" s="11" t="str"/>
+      <x:c r="F161" s="11" t="str"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" t="str">
+      <x:c r="A162" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B162" t="n">
+      <x:c r="B162" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C162" t="str">
+      <x:c r="C162" s="11" t="str">
         <x:v>Scientia Iranica</x:v>
       </x:c>
-      <x:c r="D162" t="str">
+      <x:c r="D162" s="11" t="str">
         <x:v>https://scientiairanica.sharif.edu</x:v>
       </x:c>
-      <x:c r="E162"/>
-      <x:c r="F162"/>
+      <x:c r="E162" s="11" t="str"/>
+      <x:c r="F162" s="11" t="str"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" t="str">
+      <x:c r="A163" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B163" t="n">
+      <x:c r="B163" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C163" t="str">
+      <x:c r="C163" s="11" t="str">
         <x:v>Iranian Journal of Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D163" t="str">
+      <x:c r="D163" s="11" t="str">
         <x:v>https://ijfs.usb.ac.ir</x:v>
       </x:c>
-      <x:c r="E163"/>
-      <x:c r="F163"/>
+      <x:c r="E163" s="11" t="str"/>
+      <x:c r="F163" s="11" t="str"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" t="str">
+      <x:c r="A164" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B164" t="n">
+      <x:c r="B164" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C164" t="str">
+      <x:c r="C164" s="11" t="str">
         <x:v>Kybernetes</x:v>
       </x:c>
-      <x:c r="D164" t="str">
+      <x:c r="D164" s="11" t="str">
         <x:v>https://www.emerald.com/insight/search?q=Kybernetes</x:v>
       </x:c>
-      <x:c r="E164"/>
-      <x:c r="F164"/>
+      <x:c r="E164" s="11" t="str"/>
+      <x:c r="F164" s="11" t="str"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" t="str">
+      <x:c r="A165" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B165" t="n">
+      <x:c r="B165" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C165" t="str">
+      <x:c r="C165" s="11" t="str">
         <x:v>Intelligent Decision Technologies</x:v>
       </x:c>
-      <x:c r="D165" t="str">
+      <x:c r="D165" s="11" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Decision%20Technologies</x:v>
       </x:c>
-      <x:c r="E165"/>
-      <x:c r="F165"/>
+      <x:c r="E165" s="11" t="str"/>
+      <x:c r="F165" s="11" t="str"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" t="str">
+      <x:c r="A166" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B166" t="n">
+      <x:c r="B166" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C166" t="str">
+      <x:c r="C166" s="11" t="str">
         <x:v>Fundamenta Informaticae</x:v>
       </x:c>
-      <x:c r="D166" t="str">
+      <x:c r="D166" s="11" t="str">
         <x:v>https://content.iospress.com/search?q=Fundamenta%20Informaticae</x:v>
       </x:c>
-      <x:c r="E166"/>
-      <x:c r="F166"/>
+      <x:c r="E166" s="11" t="str"/>
+      <x:c r="F166" s="11" t="str"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" t="str">
+      <x:c r="A167" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B167" t="n">
+      <x:c r="B167" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C167" t="str">
+      <x:c r="C167" s="11" t="str">
         <x:v>Intelligent Data Analysis</x:v>
       </x:c>
-      <x:c r="D167" t="str">
+      <x:c r="D167" s="11" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Data%20Analysis</x:v>
       </x:c>
-      <x:c r="E167"/>
-      <x:c r="F167"/>
+      <x:c r="E167" s="11" t="str"/>
+      <x:c r="F167" s="11" t="str"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" t="str">
+      <x:c r="A168" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B168" t="n">
+      <x:c r="B168" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C168" t="str">
+      <x:c r="C168" s="11" t="str">
         <x:v>Journal of Smart Environments and Green Computing</x:v>
       </x:c>
-      <x:c r="D168" t="str">
+      <x:c r="D168" s="11" t="str">
         <x:v>https://segcjournal.com</x:v>
       </x:c>
-      <x:c r="E168"/>
-      <x:c r="F168"/>
+      <x:c r="E168" s="11" t="str"/>
+      <x:c r="F168" s="11" t="str"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" t="str">
+      <x:c r="A169" s="11" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B169" t="n">
+      <x:c r="B169" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C169" t="str">
+      <x:c r="C169" s="11" t="str">
         <x:v>Journal of Civil Engineering and Management</x:v>
       </x:c>
-      <x:c r="D169" t="str">
+      <x:c r="D169" s="11" t="str">
         <x:v>https://journals.vgtu.lt</x:v>
       </x:c>
-      <x:c r="E169"/>
-      <x:c r="F169"/>
+      <x:c r="E169" s="11" t="str"/>
+      <x:c r="F169" s="11" t="str"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" t="str">
+      <x:c r="A170" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B170" t="n">
+      <x:c r="B170" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C170" t="str">
+      <x:c r="C170" s="11" t="str">
         <x:v>管理科学学报</x:v>
       </x:c>
-      <x:c r="D170" t="str">
+      <x:c r="D170" s="11" t="str">
         <x:v>http://jmsc.tju.edu.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E170" t="str">
+      <x:c r="E170" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8LJ05z2WKBaal83R1aZsKHhDdcfMpx3UBz-GfhJW-s7MsP1nXNGVxV1DUmvt3bqyaob8lhOefEDtskNzOE_2EpC2gCrA_8RJXiGWDTI_iUNA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F170"/>
+      <x:c r="F170" s="11" t="str"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" t="str">
+      <x:c r="A171" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B171" t="n">
+      <x:c r="B171" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C171" t="str">
+      <x:c r="C171" s="11" t="str">
         <x:v>系统工程理论与实践</x:v>
       </x:c>
-      <x:c r="D171" t="str">
+      <x:c r="D171" s="11" t="str">
         <x:v>http://www.sysengi.com/</x:v>
       </x:c>
-      <x:c r="E171" t="str">
+      <x:c r="E171" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=i3PX7_dq32X2Zk0vdxkR-ODkxN-nI3yF4njbEspRx73Nm7WAR7J-vcwM0_OoNx8FEvxGLJCXasn3KAcQ0RARebKAq4xD1pgviZ0U7vSuBvfNMhDxzEeSoA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F171"/>
+      <x:c r="F171" s="11" t="str"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" t="str">
+      <x:c r="A172" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B172" t="n">
+      <x:c r="B172" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C172" t="str">
+      <x:c r="C172" s="11" t="str">
         <x:v>管理世界</x:v>
       </x:c>
-      <x:c r="D172" t="str">
+      <x:c r="D172" s="11" t="str">
         <x:v>http://www.mwm.net.cn/web/</x:v>
       </x:c>
-      <x:c r="E172" t="str">
+      <x:c r="E172" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9bPeMF52gorOhVMoCTm_bP4JUtgupb_E88sMy-gsXzFr1P8lBB8uHZukD4Te4RdLMKnj45i1j1MNnPQo45WRUOuqkrMgwUszODdbOWIRUqkg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F172"/>
+      <x:c r="F172" s="11" t="str"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" t="str">
+      <x:c r="A173" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B173" t="n">
+      <x:c r="B173" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C173" t="str">
+      <x:c r="C173" s="11" t="str">
         <x:v>中国管理科学</x:v>
       </x:c>
-      <x:c r="D173" t="str">
+      <x:c r="D173" s="11" t="str">
         <x:v>http://www.zgglkx.com</x:v>
       </x:c>
-      <x:c r="E173" t="str">
+      <x:c r="E173" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-JU_du0-bK0lg27F1Oi8b1cNGusZwUOwac7P02Y1arLcSfkZu0L8ZB1IJhn7Fj80XDx2f9_sQ5r3G6IQgpyTe3Y_JDssEju9qAhMsGw3X0qw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F173"/>
+      <x:c r="F173" s="11" t="str"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" t="str">
+      <x:c r="A174" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B174" t="n">
+      <x:c r="B174" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C174" t="str">
+      <x:c r="C174" s="11" t="str">
         <x:v>系统工程学报</x:v>
       </x:c>
-      <x:c r="D174" t="str">
+      <x:c r="D174" s="11" t="str">
         <x:v>http://jse.tju.edu.cn</x:v>
       </x:c>
-      <x:c r="E174" t="str">
+      <x:c r="E174" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-NWam7tarWG4WxmWSs2_tcqdiLEz4i3KVdQbtnKLITej4vXhwHRR3aDau0yw8d_IavznXlO9dN3zYuKL_de5S7p2u36GqLdzMfHA3Wg9Wx0w==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F174"/>
+      <x:c r="F174" s="11" t="str"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" t="str">
+      <x:c r="A175" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B175" t="n">
+      <x:c r="B175" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C175" t="str">
+      <x:c r="C175" s="11" t="str">
         <x:v>系统管理学报</x:v>
       </x:c>
-      <x:c r="D175" t="str">
+      <x:c r="D175" s="11" t="str">
         <x:v>http://xtglxb.sjtu.edu.cn/</x:v>
       </x:c>
-      <x:c r="E175" t="str">
+      <x:c r="E175" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9URZHjnjpZNx894uUc8hEV_8y-XaWbYy_QQKZwrmUaOuHU_Ulmiyfu5w84oSoQ8OSwjHPBK4vEcFxdVksfIHxNuv4CL8S5HTYziOHdCIpK2w==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F175"/>
+      <x:c r="F175" s="11" t="str"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" t="str">
+      <x:c r="A176" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B176" t="n">
+      <x:c r="B176" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C176" t="str">
+      <x:c r="C176" s="11" t="str">
         <x:v>管理科学</x:v>
       </x:c>
-      <x:c r="D176" t="str">
+      <x:c r="D176" s="11" t="str">
         <x:v>http://glkx.hit.edu.cn/glkxcn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E176" t="str">
+      <x:c r="E176" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_ZE6E2FOt_BwppB5uBeXQErN0I5kVHOud5T_DbHM98apuHBLYdN4agXMpq5m9CZr4pnZE4hFnsyANk-8DWJ3fFUdWzB2oij7TzlVIKAxfF6A==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F176"/>
+      <x:c r="F176" s="11" t="str"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" t="str">
+      <x:c r="A177" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B177" t="n">
+      <x:c r="B177" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C177" t="str">
+      <x:c r="C177" s="11" t="str">
         <x:v>管理评论</x:v>
       </x:c>
-      <x:c r="D177" t="str">
+      <x:c r="D177" s="11" t="str">
         <x:v>http://www.glplzz.com/</x:v>
       </x:c>
-      <x:c r="E177" t="str">
+      <x:c r="E177" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-TCsOxvxdXdlSvw79gRfLC3Qs4Zx8pWINWUiL6dgoj_PFvNjjxeJ-IodjHg3dspx0OB_4yj_j_2YdtzhxiYvBKymQM3Mm052AZyEPIfen2cA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F177"/>
+      <x:c r="F177" s="11" t="str"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" t="str">
+      <x:c r="A178" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B178" t="n">
+      <x:c r="B178" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C178" t="str">
+      <x:c r="C178" s="11" t="str">
         <x:v>管理工程学报</x:v>
       </x:c>
-      <x:c r="D178" t="str">
+      <x:c r="D178" s="11" t="str">
         <x:v>http://glgcxb.zju.edu.cn/</x:v>
       </x:c>
-      <x:c r="E178" t="str">
-        <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; 万方|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</x:v>
-      </x:c>
-      <x:c r="F178"/>
+      <x:c r="E178" s="11" t="str">
+        <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</x:v>
+      </x:c>
+      <x:c r="F178" s="11" t="str"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" t="str">
+      <x:c r="A179" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B179" t="n">
+      <x:c r="B179" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C179" t="str">
+      <x:c r="C179" s="11" t="str">
         <x:v>南开管理评论</x:v>
       </x:c>
-      <x:c r="D179" t="str">
+      <x:c r="D179" s="11" t="str">
         <x:v>http://www.nbronline.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E179" t="str">
+      <x:c r="E179" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F179"/>
+      <x:c r="F179" s="11" t="str"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" t="str">
+      <x:c r="A180" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B180" t="n">
+      <x:c r="B180" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C180" t="str">
+      <x:c r="C180" s="11" t="str">
         <x:v>科研管理</x:v>
       </x:c>
-      <x:c r="D180" t="str">
+      <x:c r="D180" s="11" t="str">
         <x:v>http://www.kygl.net.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E180" t="str">
+      <x:c r="E180" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F180"/>
+      <x:c r="F180" s="11" t="str"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" t="str">
+      <x:c r="A181" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B181" t="n">
+      <x:c r="B181" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C181" t="str">
+      <x:c r="C181" s="11" t="str">
         <x:v>情报学报</x:v>
       </x:c>
-      <x:c r="D181" t="str">
+      <x:c r="D181" s="11" t="str">
         <x:v>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</x:v>
       </x:c>
-      <x:c r="E181" t="str">
+      <x:c r="E181" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F181"/>
+      <x:c r="F181" s="11" t="str"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" t="str">
+      <x:c r="A182" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B182" t="n">
+      <x:c r="B182" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C182" t="str">
+      <x:c r="C182" s="11" t="str">
         <x:v>工程管理科技前沿</x:v>
       </x:c>
-      <x:c r="D182" t="str">
+      <x:c r="D182" s="11" t="str">
         <x:v>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="E182" t="str">
+      <x:c r="E182" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F182"/>
+      <x:c r="F182" s="11" t="str"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" t="str">
+      <x:c r="A183" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B183" t="n">
+      <x:c r="B183" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C183" t="str">
+      <x:c r="C183" s="11" t="str">
         <x:v>运筹与管理</x:v>
       </x:c>
-      <x:c r="D183" t="str">
+      <x:c r="D183" s="11" t="str">
         <x:v>http://www.jorms.net/CN/1007-3221/home.shtml</x:v>
       </x:c>
-      <x:c r="E183" t="str">
-        <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; 万方|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</x:v>
-      </x:c>
-      <x:c r="F183"/>
+      <x:c r="E183" s="11" t="str">
+        <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</x:v>
+      </x:c>
+      <x:c r="F183" s="11" t="str"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" t="str">
+      <x:c r="A184" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B184" t="n">
+      <x:c r="B184" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C184" t="str">
+      <x:c r="C184" s="11" t="str">
         <x:v>管理学报</x:v>
       </x:c>
-      <x:c r="D184" t="str">
+      <x:c r="D184" s="11" t="str">
         <x:v>http://manu68.magtech.com.cn/Jwk_glxb/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E184" t="str">
+      <x:c r="E184" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8PCnUrD8saRufeUaB7vvWh8ImJB4HeHNeLqW0ePwzGyEPNRCnQsHlbFXGOlO-wcTfqZgKY4hDwsLs-3Tn89zOBbGtw1AAMZyEw5PPM6laErQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F184"/>
+      <x:c r="F184" s="11" t="str"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" t="str">
+      <x:c r="A185" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B185" t="n">
+      <x:c r="B185" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C185" t="str">
+      <x:c r="C185" s="11" t="str">
         <x:v>工业工程与管理</x:v>
       </x:c>
-      <x:c r="D185" t="str">
+      <x:c r="D185" s="11" t="str">
         <x:v>https://gygc.cbpt.cnki.net/WKB2/WebPublication/index.aspx?mid=gygc</x:v>
       </x:c>
-      <x:c r="E185" t="str">
+      <x:c r="E185" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8br7MgEIcFYMQt_ZJBi4Gq5howJvAAN2q5Uw-jRJpkwA6seBfU1WclQ4xGDeYNZADI68ojMDuwRNLC-W9Dialui-wgcg5tuYIT8ESNZSpaSQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F185"/>
+      <x:c r="F185" s="11" t="str"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" t="str">
+      <x:c r="A186" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B186" t="n">
+      <x:c r="B186" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C186" t="str">
+      <x:c r="C186" s="11" t="str">
         <x:v>系统工程</x:v>
       </x:c>
-      <x:c r="D186" t="str">
+      <x:c r="D186" s="11" t="str">
         <x:v>http://www.xitonggongcheng.cn/</x:v>
       </x:c>
-      <x:c r="E186" t="str">
+      <x:c r="E186" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ521dERQpzlafVK7qGUOU45RpQBLI3a7dqVm6V_hSwqA5HQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F186"/>
+      <x:c r="F186" s="11" t="str"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" t="str">
+      <x:c r="A187" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B187" t="n">
+      <x:c r="B187" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C187" t="str">
+      <x:c r="C187" s="11" t="str">
         <x:v>控制与决策</x:v>
       </x:c>
-      <x:c r="D187" t="str">
+      <x:c r="D187" s="11" t="str">
         <x:v>http://kzyjc.alljournals.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E187" t="str">
+      <x:c r="E187" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9VMm0YxN4tX5yL-EVnsT6PAjZVl9XwIKssVo1NvBga91FGUvekhWuNlMQI0JER059BEkpPkSf2yKf-gU-zpBPmAP0aZmcjFXxTBOO3l4T0hA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F187"/>
+      <x:c r="F187" s="11" t="str"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" t="str">
+      <x:c r="A188" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B188" t="n">
+      <x:c r="B188" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C188" t="str">
+      <x:c r="C188" s="11" t="str">
         <x:v>系统工程与电子技术</x:v>
       </x:c>
-      <x:c r="D188" t="str">
+      <x:c r="D188" s="11" t="str">
         <x:v>http://www.sys-ele.com/CN/1001-506X/home.shtml</x:v>
       </x:c>
-      <x:c r="E188" t="str">
+      <x:c r="E188" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ522XKppJFMLpkDt0YeID7jzeew3YqHq1UltKzV8MACc98A==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F188"/>
+      <x:c r="F188" s="11" t="str"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" t="str">
+      <x:c r="A189" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B189" t="n">
+      <x:c r="B189" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C189" t="str">
+      <x:c r="C189" s="11" t="str">
         <x:v>中国软科学</x:v>
       </x:c>
-      <x:c r="D189" t="str">
+      <x:c r="D189" s="11" t="str">
         <x:v>http://www.cssm.com.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E189" t="str">
+      <x:c r="E189" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8jySLJU_283KXns0m8yNk0Ce8rmtobTme-1MViCCKsbzSynAlfsvvxkGahZxy_URE-jKLwH5grOgRQ7kKV0KBnSC88LYojIfsOG5GxO7NKdg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F189"/>
+      <x:c r="F189" s="11" t="str"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" t="str">
+      <x:c r="A190" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B190" t="n">
+      <x:c r="B190" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C190" t="str">
+      <x:c r="C190" s="11" t="str">
         <x:v>系统科学与数学</x:v>
       </x:c>
-      <x:c r="D190" t="str">
+      <x:c r="D190" s="11" t="str">
         <x:v>http://sysmath.com/jweb_xtkxysx</x:v>
       </x:c>
-      <x:c r="E190" t="str">
+      <x:c r="E190" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-E-p5hVM-T-2-bewhhYzlPKidJWYOorDi1B-PITMAbOL0S7cekgijFCS0nSXq4XQNKt1GbaW3S6VWjdbpFqoGY_EIIuekH5mr8rxzI_HrR7g==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F190"/>
+      <x:c r="F190" s="11" t="str"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" t="str">
+      <x:c r="A191" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B191" t="n">
+      <x:c r="B191" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C191" t="str">
+      <x:c r="C191" s="11" t="str">
         <x:v>计量经济学报</x:v>
       </x:c>
-      <x:c r="D191" t="str">
+      <x:c r="D191" s="11" t="str">
         <x:v>http://www.cjoe.ac.cn/CN/2096-9732/home.shtml</x:v>
       </x:c>
-      <x:c r="E191" t="str">
+      <x:c r="E191" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9O7KTOAqVcVsRDT7MmQLR8XCOwVreqgSqoJ_mGw8hFdrvny_-zVG3nRwmEQnA8E_SpxQeLOkYd7CxfbKQuxDeda_UEYUS14oC9RQJGSD6dYg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F191"/>
+      <x:c r="F191" s="11" t="str"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" t="str">
+      <x:c r="A192" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B192" t="n">
+      <x:c r="B192" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C192" t="str">
+      <x:c r="C192" s="11" t="str">
         <x:v>自动化学报</x:v>
       </x:c>
-      <x:c r="D192" t="str">
+      <x:c r="D192" s="11" t="str">
         <x:v>http://www.aas.net.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E192" t="str">
+      <x:c r="E192" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_KyFB5Et1OillJwmuopCWBj5pdqWDmDRaudYAq4j6C1SQ8RskmxnZJipOZnXxhDK_wNDwDjzo_dILEkzq7JyCDiG26p2JrBu__1dKfqF0Hug==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F192"/>
+      <x:c r="F192" s="11" t="str"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" t="str">
+      <x:c r="A193" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B193" t="n">
+      <x:c r="B193" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C193" t="str">
+      <x:c r="C193" s="11" t="str">
         <x:v>计算机学报</x:v>
       </x:c>
-      <x:c r="D193" t="str">
+      <x:c r="D193" s="11" t="str">
         <x:v>http://cjc.ict.ac.cn/</x:v>
       </x:c>
-      <x:c r="E193" t="str">
+      <x:c r="E193" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9_vxQO77UEmThRI7mhs7_u-tPwE_PVKzc0Y8BhMYBHTzr98uiHz_J7VQEcj0zQgQD69gziJmOh-Y7_MS0eWzVrjAi2cxJHj4AyA5FLhECB7Q==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F193"/>
+      <x:c r="F193" s="11" t="str"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" t="str">
+      <x:c r="A194" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B194" t="n">
+      <x:c r="B194" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C194" t="str">
+      <x:c r="C194" s="11" t="str">
         <x:v>计算机研究与发展</x:v>
       </x:c>
-      <x:c r="D194" t="str">
+      <x:c r="D194" s="11" t="str">
         <x:v>http://crad.ict.ac.cn/</x:v>
       </x:c>
-      <x:c r="E194" t="str">
+      <x:c r="E194" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8lGm60BT1S32qMmgQriP9uZ2ShOTZe4_8yW-QQYDij87AjrNp9M_13YGgNGlrNwq-vJCQhJ1KyL0VCjz5laN36JY4u-_EtYQc2NFnjQlP6wg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F194"/>
+      <x:c r="F194" s="11" t="str"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" t="str">
+      <x:c r="A195" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B195" t="n">
+      <x:c r="B195" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C195" t="str">
+      <x:c r="C195" s="11" t="str">
         <x:v>电子学报</x:v>
       </x:c>
-      <x:c r="D195" t="str">
+      <x:c r="D195" s="11" t="str">
         <x:v>http://www.ejournal.org.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E195" t="str">
+      <x:c r="E195" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/journals/DZXU/detail?uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F195"/>
+      <x:c r="F195" s="11" t="str"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" t="str">
+      <x:c r="A196" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B196" t="n">
+      <x:c r="B196" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C196" t="str">
+      <x:c r="C196" s="11" t="str">
         <x:v>软件学报</x:v>
       </x:c>
-      <x:c r="D196" t="str">
+      <x:c r="D196" s="11" t="str">
         <x:v>http://www.jos.org.cn/</x:v>
       </x:c>
-      <x:c r="E196" t="str">
+      <x:c r="E196" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-eSDBBKMj0vAeZF-smiUXPlDeISBrKFJZZ9arNvuLVDlcERM2YiZPI_j0aeLQpFlrUVoLG0JBQXMun-myIj8mt0fvZymwFzAizMqubrnbCDg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F196"/>
+      <x:c r="F196" s="11" t="str"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" t="str">
+      <x:c r="A197" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B197" t="n">
+      <x:c r="B197" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C197" t="str">
+      <x:c r="C197" s="11" t="str">
         <x:v>中国科学: 信息科学</x:v>
       </x:c>
-      <x:c r="D197" t="str">
+      <x:c r="D197" s="11" t="str">
         <x:v>https://www.sciengine.com/publisher/scp/journal/SSI?slug=firstpublish</x:v>
       </x:c>
-      <x:c r="E197" t="str">
+      <x:c r="E197" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_wGZ_mUleWCYCON5LbBM4MWv3xigAWN4kttzDDJAGVBd7SeAnjCYVkCmhMZnWmK8p7oIeobAw_ntBHWA0d52ws1dPal6Yqvk_voRKDk5MihA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F197"/>
+      <x:c r="F197" s="11" t="str"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" t="str">
+      <x:c r="A198" s="11" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B198" t="n">
+      <x:c r="B198" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C198" t="str">
+      <x:c r="C198" s="11" t="str">
         <x:v>数据分析与知识发现</x:v>
       </x:c>
-      <x:c r="D198" t="str">
+      <x:c r="D198" s="11" t="str">
         <x:v>https://manu44.magtech.com.cn/Jwk_infotech_wk3/CN/2096-3467/home.shtml</x:v>
       </x:c>
-      <x:c r="E198" t="str">
+      <x:c r="E198" s="11" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/journals/XDTQ/detail</x:v>
       </x:c>
-      <x:c r="F198"/>
+      <x:c r="F198" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64ddde3161c34ee2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e0fd1e74182431d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3499,11 +3497,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="3" t="str">
         <x:v>Category</x:v>
       </x:c>
     </x:row>
@@ -3540,48 +3538,6 @@
     <x:row r="8">
       <x:c r="A8" t="str">
         <x:v>中文期刊</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="95" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="12" t="str">
-        <x:v>How to update</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>1. Edit journal_list.xlsx. Keep the columns unchanged.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>2. Run update_journals.bat to regenerate journals.json.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>3. Open index.html in a browser, or upload all files to the same folder on GitHub Pages.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>Extra Links format: Label|URL; Label2|URL2.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>The webpage displays only journal names; journal title links use the URL column.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/journal_new/journal_list.xlsx
+++ b/journal_new/journal_list.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Rd3bf13f768ba4d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="Rc5fdd745095a404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Raf7068f8a086440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="R8dafbf87a6d24777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1558fbe28ad948c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +36,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1E5B8C"/>
+        <x:fgColor rgb="245F9F"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -46,36 +47,24 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -85,7 +74,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalTable" displayName="JournalTable" ref="A1:F198" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalsTable" displayName="JournalsTable" ref="A1:F198" headerRowCount="1">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Order"/>
@@ -249,3246 +238,3304 @@
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="64" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>Order</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>Journal</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>Extra Links (label|url; ...)</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="n">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="str">
+      <x:c r="C2" s="8" t="str">
         <x:v>Applied Soft Computing</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="str">
+      <x:c r="D2" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="str"/>
-      <x:c r="F2" s="11" t="str"/>
+      <x:c r="E2" s="8" t="str"/>
+      <x:c r="F2" s="8" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="n">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>Computers &amp; Industrial Engineering</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="str">
+      <x:c r="D3" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering</x:v>
       </x:c>
-      <x:c r="E3" s="11" t="str"/>
-      <x:c r="F3" s="11" t="str"/>
+      <x:c r="E3" s="8" t="str"/>
+      <x:c r="F3" s="8" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="n">
+      <x:c r="A4" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="str">
+      <x:c r="C4" s="8" t="str">
         <x:v>Computers &amp; Operations Research</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
+      <x:c r="D4" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="str"/>
-      <x:c r="F4" s="11" t="str"/>
+      <x:c r="E4" s="8" t="str"/>
+      <x:c r="F4" s="8" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="n">
+      <x:c r="A5" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
+      <x:c r="C5" s="8" t="str">
         <x:v>Decision Support Systems</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
+      <x:c r="D5" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="str"/>
-      <x:c r="F5" s="11" t="str"/>
+      <x:c r="E5" s="8" t="str"/>
+      <x:c r="F5" s="8" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="A6" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="str">
+      <x:c r="C6" s="8" t="str">
         <x:v>European Journal of Operational Research</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
+      <x:c r="D6" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-j-of-operational-research</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str"/>
-      <x:c r="F6" s="11" t="str"/>
+      <x:c r="E6" s="8" t="str"/>
+      <x:c r="F6" s="8" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="A7" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str">
+      <x:c r="C7" s="8" t="str">
         <x:v>Expert Systems with Applications</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
+      <x:c r="D7" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str"/>
-      <x:c r="F7" s="11" t="str"/>
+      <x:c r="E7" s="8" t="str"/>
+      <x:c r="F7" s="8" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="n">
+      <x:c r="A8" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
+      <x:c r="C8" s="8" t="str">
         <x:v>Fuzzy Sets and Systems</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
+      <x:c r="D8" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str"/>
-      <x:c r="F8" s="11" t="str"/>
+      <x:c r="E8" s="8" t="str"/>
+      <x:c r="F8" s="8" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="n">
+      <x:c r="A9" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="str">
+      <x:c r="C9" s="8" t="str">
         <x:v>Information Fusion</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="str">
+      <x:c r="D9" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="str"/>
-      <x:c r="F9" s="11" t="str"/>
+      <x:c r="E9" s="8" t="str"/>
+      <x:c r="F9" s="8" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="n">
+      <x:c r="A10" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="str">
+      <x:c r="C10" s="8" t="str">
         <x:v>Information Sciences</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="str">
+      <x:c r="D10" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str"/>
-      <x:c r="F10" s="11" t="str"/>
+      <x:c r="E10" s="8" t="str"/>
+      <x:c r="F10" s="8" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="n">
+      <x:c r="A11" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="str">
+      <x:c r="C11" s="8" t="str">
         <x:v>International Journal of Approximate Reasoning</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="str">
+      <x:c r="D11" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-approximate-reasoning</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="str"/>
-      <x:c r="F11" s="11" t="str"/>
+      <x:c r="E11" s="8" t="str"/>
+      <x:c r="F11" s="8" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="n">
+      <x:c r="A12" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="str">
+      <x:c r="C12" s="8" t="str">
         <x:v>International Journal of Production Economics</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="str">
+      <x:c r="D12" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-production-economics</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="str"/>
-      <x:c r="F12" s="11" t="str"/>
+      <x:c r="E12" s="8" t="str"/>
+      <x:c r="F12" s="8" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="n">
+      <x:c r="A13" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="str">
+      <x:c r="C13" s="8" t="str">
         <x:v>Knowledge-Based Systems</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="str">
+      <x:c r="D13" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str"/>
-      <x:c r="F13" s="11" t="str"/>
+      <x:c r="E13" s="8" t="str"/>
+      <x:c r="F13" s="8" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="n">
+      <x:c r="A14" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="str">
+      <x:c r="C14" s="8" t="str">
         <x:v>Omega</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="str">
+      <x:c r="D14" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="str"/>
-      <x:c r="F14" s="11" t="str"/>
+      <x:c r="E14" s="8" t="str"/>
+      <x:c r="F14" s="8" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="n">
+      <x:c r="A15" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="str">
+      <x:c r="C15" s="8" t="str">
         <x:v>Engineering Applications of Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="str">
+      <x:c r="D15" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="str"/>
-      <x:c r="F15" s="11" t="str"/>
+      <x:c r="E15" s="8" t="str"/>
+      <x:c r="F15" s="8" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="n">
+      <x:c r="A16" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="str">
+      <x:c r="C16" s="8" t="str">
         <x:v>Journal of Management Science and Engineering</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="str">
+      <x:c r="D16" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="str"/>
-      <x:c r="F16" s="11" t="str"/>
+      <x:c r="E16" s="8" t="str"/>
+      <x:c r="F16" s="8" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="n">
+      <x:c r="A17" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="str">
+      <x:c r="C17" s="8" t="str">
         <x:v>Electronic Commerce Research and Applications</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="str">
+      <x:c r="D17" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="str"/>
-      <x:c r="F17" s="11" t="str"/>
+      <x:c r="E17" s="8" t="str"/>
+      <x:c r="F17" s="8" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B18" s="11" t="n">
+      <x:c r="A18" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="str">
+      <x:c r="C18" s="8" t="str">
         <x:v>International Journal of Forecasting</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="str">
+      <x:c r="D18" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="str"/>
-      <x:c r="F18" s="11" t="str"/>
+      <x:c r="E18" s="8" t="str"/>
+      <x:c r="F18" s="8" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="n">
+      <x:c r="A19" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="str">
+      <x:c r="C19" s="8" t="str">
         <x:v>Information &amp; Management</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="str">
+      <x:c r="D19" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="str"/>
-      <x:c r="F19" s="11" t="str"/>
+      <x:c r="E19" s="8" t="str"/>
+      <x:c r="F19" s="8" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="n">
+      <x:c r="A20" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="str">
+      <x:c r="C20" s="8" t="str">
         <x:v>Information Systems</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="str">
+      <x:c r="D20" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="str"/>
-      <x:c r="F20" s="11" t="str"/>
+      <x:c r="E20" s="8" t="str"/>
+      <x:c r="F20" s="8" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="n">
+      <x:c r="A21" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="str">
+      <x:c r="C21" s="8" t="str">
         <x:v>Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="str">
+      <x:c r="D21" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="str"/>
-      <x:c r="F21" s="11" t="str"/>
+      <x:c r="E21" s="8" t="str"/>
+      <x:c r="F21" s="8" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B22" s="11" t="n">
+      <x:c r="A22" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="str">
+      <x:c r="C22" s="8" t="str">
         <x:v>Pattern Recognition</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="str">
+      <x:c r="D22" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="str"/>
-      <x:c r="F22" s="11" t="str"/>
+      <x:c r="E22" s="8" t="str"/>
+      <x:c r="F22" s="8" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="n">
+      <x:c r="A23" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="str">
+      <x:c r="C23" s="8" t="str">
         <x:v>Pattern Recognition Letters</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="str">
+      <x:c r="D23" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="str"/>
-      <x:c r="F23" s="11" t="str"/>
+      <x:c r="E23" s="8" t="str"/>
+      <x:c r="F23" s="8" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B24" s="11" t="n">
+      <x:c r="A24" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="str">
+      <x:c r="C24" s="8" t="str">
         <x:v>Neurocomputing</x:v>
       </x:c>
-      <x:c r="D24" s="11" t="str">
+      <x:c r="D24" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="str"/>
-      <x:c r="F24" s="11" t="str"/>
+      <x:c r="E24" s="8" t="str"/>
+      <x:c r="F24" s="8" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="n">
+      <x:c r="A25" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="str">
+      <x:c r="C25" s="8" t="str">
         <x:v>Physica A: Statistical Mechanics and its Applications</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="str">
+      <x:c r="D25" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="str"/>
-      <x:c r="F25" s="11" t="str"/>
+      <x:c r="E25" s="8" t="str"/>
+      <x:c r="F25" s="8" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="n">
+      <x:c r="A26" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="str">
+      <x:c r="C26" s="8" t="str">
         <x:v>Journal of Cleaner Production</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="str">
+      <x:c r="D26" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-cleaner-production</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="str"/>
-      <x:c r="F26" s="11" t="str"/>
+      <x:c r="E26" s="8" t="str"/>
+      <x:c r="F26" s="8" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="n">
+      <x:c r="A27" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="str">
+      <x:c r="C27" s="8" t="str">
         <x:v>Energy</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="str">
+      <x:c r="D27" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/energy</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="str"/>
-      <x:c r="F27" s="11" t="str"/>
+      <x:c r="E27" s="8" t="str"/>
+      <x:c r="F27" s="8" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="n">
+      <x:c r="A28" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="str">
+      <x:c r="C28" s="8" t="str">
         <x:v>Reliability Engineering &amp; System Safety</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="str">
+      <x:c r="D28" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="str"/>
-      <x:c r="F28" s="11" t="str"/>
+      <x:c r="E28" s="8" t="str"/>
+      <x:c r="F28" s="8" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B29" s="11" t="n">
+      <x:c r="A29" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="str">
+      <x:c r="C29" s="8" t="str">
         <x:v>Journal of Biomedical Informatics</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="str">
+      <x:c r="D29" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="str"/>
-      <x:c r="F29" s="11" t="str"/>
+      <x:c r="E29" s="8" t="str"/>
+      <x:c r="F29" s="8" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="n">
+      <x:c r="A30" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="str">
+      <x:c r="C30" s="8" t="str">
         <x:v>AI Open</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="str">
+      <x:c r="D30" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="str"/>
-      <x:c r="F30" s="11" t="str"/>
+      <x:c r="E30" s="8" t="str"/>
+      <x:c r="F30" s="8" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B31" s="11" t="n">
+      <x:c r="A31" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="str">
+      <x:c r="C31" s="8" t="str">
         <x:v>Neural Networks</x:v>
       </x:c>
-      <x:c r="D31" s="11" t="str">
+      <x:c r="D31" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="str"/>
-      <x:c r="F31" s="11" t="str"/>
+      <x:c r="E31" s="8" t="str"/>
+      <x:c r="F31" s="8" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="n">
+      <x:c r="A32" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="str">
+      <x:c r="C32" s="8" t="str">
         <x:v>Advanced Engineering Informatics</x:v>
       </x:c>
-      <x:c r="D32" s="11" t="str">
+      <x:c r="D32" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="str"/>
-      <x:c r="F32" s="11" t="str"/>
+      <x:c r="E32" s="8" t="str"/>
+      <x:c r="F32" s="8" t="str"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B33" s="11" t="n">
+      <x:c r="A33" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="str">
+      <x:c r="C33" s="8" t="str">
         <x:v>Computers in Industry</x:v>
       </x:c>
-      <x:c r="D33" s="11" t="str">
+      <x:c r="D33" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="str"/>
-      <x:c r="F33" s="11" t="str"/>
+      <x:c r="E33" s="8" t="str"/>
+      <x:c r="F33" s="8" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="n">
+      <x:c r="A34" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="str">
+      <x:c r="C34" s="8" t="str">
         <x:v>Chaos, Solitons &amp; Fractals</x:v>
       </x:c>
-      <x:c r="D34" s="11" t="str">
+      <x:c r="D34" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/chaos-solitons-and-fractals</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="str"/>
-      <x:c r="F34" s="11" t="str"/>
+      <x:c r="E34" s="8" t="str"/>
+      <x:c r="F34" s="8" t="str"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="n">
+      <x:c r="A35" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="str">
+      <x:c r="C35" s="8" t="str">
         <x:v>Safety Science</x:v>
       </x:c>
-      <x:c r="D35" s="11" t="str">
+      <x:c r="D35" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/safety-science</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="str"/>
-      <x:c r="F35" s="11" t="str"/>
+      <x:c r="E35" s="8" t="str"/>
+      <x:c r="F35" s="8" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B36" s="11" t="n">
+      <x:c r="A36" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="str">
+      <x:c r="C36" s="8" t="str">
         <x:v>Technological Forecasting and Social Change</x:v>
       </x:c>
-      <x:c r="D36" s="11" t="str">
+      <x:c r="D36" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="str"/>
-      <x:c r="F36" s="11" t="str"/>
+      <x:c r="E36" s="8" t="str"/>
+      <x:c r="F36" s="8" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B37" s="11" t="n">
+      <x:c r="A37" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C37" s="11" t="str">
+      <x:c r="C37" s="8" t="str">
         <x:v>Automation in Construction</x:v>
       </x:c>
-      <x:c r="D37" s="11" t="str">
+      <x:c r="D37" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/automation-in-construction</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="str"/>
-      <x:c r="F37" s="11" t="str"/>
+      <x:c r="E37" s="8" t="str"/>
+      <x:c r="F37" s="8" t="str"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B38" s="11" t="n">
+      <x:c r="A38" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C38" s="11" t="str">
+      <x:c r="C38" s="8" t="str">
         <x:v>Annual Reviews in Control</x:v>
       </x:c>
-      <x:c r="D38" s="11" t="str">
+      <x:c r="D38" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/annual-reviews-in-control</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="str"/>
-      <x:c r="F38" s="11" t="str"/>
+      <x:c r="E38" s="8" t="str"/>
+      <x:c r="F38" s="8" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B39" s="11" t="n">
+      <x:c r="A39" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C39" s="11" t="str">
+      <x:c r="C39" s="8" t="str">
         <x:v>Journal of Environmental Economics and Management</x:v>
       </x:c>
-      <x:c r="D39" s="11" t="str">
+      <x:c r="D39" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-environmental-economics-and-management</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="str"/>
-      <x:c r="F39" s="11" t="str"/>
+      <x:c r="E39" s="8" t="str"/>
+      <x:c r="F39" s="8" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B40" s="11" t="n">
+      <x:c r="A40" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C40" s="11" t="str">
+      <x:c r="C40" s="8" t="str">
         <x:v>Journal of Retailing and Consumer Services</x:v>
       </x:c>
-      <x:c r="D40" s="11" t="str">
+      <x:c r="D40" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services</x:v>
       </x:c>
-      <x:c r="E40" s="11" t="str"/>
-      <x:c r="F40" s="11" t="str"/>
+      <x:c r="E40" s="8" t="str"/>
+      <x:c r="F40" s="8" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B41" s="11" t="n">
+      <x:c r="A41" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C41" s="11" t="str">
-        <x:v>Transportation Research Part B: Methodological</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
+      <x:c r="C41" s="8" t="str">
+        <x:v>Transportation Research, Series B: Methodological</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-series-b-methodological</x:v>
       </x:c>
-      <x:c r="E41" s="11" t="str"/>
-      <x:c r="F41" s="11" t="str"/>
+      <x:c r="E41" s="8" t="str"/>
+      <x:c r="F41" s="8" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B42" s="11" t="n">
+      <x:c r="A42" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C42" s="11" t="str">
+      <x:c r="C42" s="8" t="str">
         <x:v>Transportation Research, Part D: Transport and Environment</x:v>
       </x:c>
-      <x:c r="D42" s="11" t="str">
+      <x:c r="D42" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
-      <x:c r="E42" s="11" t="str"/>
-      <x:c r="F42" s="11" t="str"/>
+      <x:c r="E42" s="8" t="str"/>
+      <x:c r="F42" s="8" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B43" s="11" t="n">
+      <x:c r="A43" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C43" s="11" t="str">
+      <x:c r="C43" s="8" t="str">
         <x:v>Transportation Research, Part E: Logistics and Transportation Review</x:v>
       </x:c>
-      <x:c r="D43" s="11" t="str">
+      <x:c r="D43" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
-      <x:c r="E43" s="11" t="str"/>
-      <x:c r="F43" s="11" t="str"/>
+      <x:c r="E43" s="8" t="str"/>
+      <x:c r="F43" s="8" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="11" t="str">
-        <x:v>Elsevier</x:v>
-      </x:c>
-      <x:c r="B44" s="11" t="n">
+      <x:c r="A44" s="8" t="str">
+        <x:v>Elsevier</x:v>
+      </x:c>
+      <x:c r="B44" s="8" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C44" s="11" t="str">
+      <x:c r="C44" s="8" t="str">
         <x:v>EURO Journal on Decision Processes</x:v>
       </x:c>
-      <x:c r="D44" s="11" t="str">
+      <x:c r="D44" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes</x:v>
       </x:c>
-      <x:c r="E44" s="11" t="str"/>
-      <x:c r="F44" s="11" t="str"/>
+      <x:c r="E44" s="8" t="str"/>
+      <x:c r="F44" s="8" t="str"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="11" t="str">
+      <x:c r="A45" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B45" s="11" t="n">
+      <x:c r="B45" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C45" s="11" t="str">
+      <x:c r="C45" s="8" t="str">
         <x:v>Tourism Management</x:v>
       </x:c>
-      <x:c r="D45" s="11" t="str">
+      <x:c r="D45" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management</x:v>
       </x:c>
-      <x:c r="E45" s="11" t="str"/>
-      <x:c r="F45" s="11" t="str"/>
+      <x:c r="E45" s="8" t="str"/>
+      <x:c r="F45" s="8" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="11" t="str">
+      <x:c r="A46" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B46" s="11" t="n">
+      <x:c r="B46" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C46" s="11" t="str">
+      <x:c r="C46" s="8" t="str">
         <x:v>Annals of Tourism Research</x:v>
       </x:c>
-      <x:c r="D46" s="11" t="str">
+      <x:c r="D46" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research</x:v>
       </x:c>
-      <x:c r="E46" s="11" t="str"/>
-      <x:c r="F46" s="11" t="str"/>
+      <x:c r="E46" s="8" t="str"/>
+      <x:c r="F46" s="8" t="str"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="11" t="str">
+      <x:c r="A47" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B47" s="11" t="n">
+      <x:c r="B47" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C47" s="11" t="str">
+      <x:c r="C47" s="8" t="str">
         <x:v>Journal of Travel Research</x:v>
       </x:c>
-      <x:c r="D47" s="11" t="str">
+      <x:c r="D47" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Travel%20Research</x:v>
       </x:c>
-      <x:c r="E47" s="11" t="str"/>
-      <x:c r="F47" s="11" t="str"/>
+      <x:c r="E47" s="8" t="str"/>
+      <x:c r="F47" s="8" t="str"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="11" t="str">
+      <x:c r="A48" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B48" s="11" t="n">
+      <x:c r="B48" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C48" s="11" t="str">
+      <x:c r="C48" s="8" t="str">
         <x:v>Journal of Service Research</x:v>
       </x:c>
-      <x:c r="D48" s="11" t="str">
+      <x:c r="D48" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Service%20Research</x:v>
       </x:c>
-      <x:c r="E48" s="11" t="str"/>
-      <x:c r="F48" s="11" t="str"/>
+      <x:c r="E48" s="8" t="str"/>
+      <x:c r="F48" s="8" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="11" t="str">
+      <x:c r="A49" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B49" s="11" t="n">
+      <x:c r="B49" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C49" s="11" t="str">
+      <x:c r="C49" s="8" t="str">
         <x:v>International Journal of Hospitality Management</x:v>
       </x:c>
-      <x:c r="D49" s="11" t="str">
+      <x:c r="D49" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-hospitality-management</x:v>
       </x:c>
-      <x:c r="E49" s="11" t="str"/>
-      <x:c r="F49" s="11" t="str"/>
+      <x:c r="E49" s="8" t="str"/>
+      <x:c r="F49" s="8" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="11" t="str">
+      <x:c r="A50" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B50" s="11" t="n">
+      <x:c r="B50" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C50" s="11" t="str">
+      <x:c r="C50" s="8" t="str">
         <x:v>International Journal of Contemporary Hospitality Management</x:v>
       </x:c>
-      <x:c r="D50" s="11" t="str">
+      <x:c r="D50" s="8" t="str">
         <x:v>https://www.emerald.com/insight/search?q=International%20Journal%20of%20Contemporary%20Hospitality%20Management</x:v>
       </x:c>
-      <x:c r="E50" s="11" t="str"/>
-      <x:c r="F50" s="11" t="str"/>
+      <x:c r="E50" s="8" t="str"/>
+      <x:c r="F50" s="8" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="11" t="str">
+      <x:c r="A51" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B51" s="11" t="n">
+      <x:c r="B51" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C51" s="11" t="str">
+      <x:c r="C51" s="8" t="str">
         <x:v>Journal of Sustainable Tourism</x:v>
       </x:c>
-      <x:c r="D51" s="11" t="str">
+      <x:c r="D51" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Sustainable%20Tourism</x:v>
       </x:c>
-      <x:c r="E51" s="11" t="str"/>
-      <x:c r="F51" s="11" t="str"/>
+      <x:c r="E51" s="8" t="str"/>
+      <x:c r="F51" s="8" t="str"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="11" t="str">
+      <x:c r="A52" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B52" s="11" t="n">
+      <x:c r="B52" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C52" s="11" t="str">
+      <x:c r="C52" s="8" t="str">
         <x:v>Tourism Management Perspectives</x:v>
       </x:c>
-      <x:c r="D52" s="11" t="str">
+      <x:c r="D52" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management-perspectives</x:v>
       </x:c>
-      <x:c r="E52" s="11" t="str"/>
-      <x:c r="F52" s="11" t="str"/>
+      <x:c r="E52" s="8" t="str"/>
+      <x:c r="F52" s="8" t="str"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="11" t="str">
+      <x:c r="A53" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B53" s="11" t="n">
+      <x:c r="B53" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C53" s="11" t="str">
+      <x:c r="C53" s="8" t="str">
         <x:v>Current Issues in Tourism</x:v>
       </x:c>
-      <x:c r="D53" s="11" t="str">
+      <x:c r="D53" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Current%20Issues%20in%20Tourism</x:v>
       </x:c>
-      <x:c r="E53" s="11" t="str"/>
-      <x:c r="F53" s="11" t="str"/>
+      <x:c r="E53" s="8" t="str"/>
+      <x:c r="F53" s="8" t="str"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="11" t="str">
+      <x:c r="A54" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B54" s="11" t="n">
+      <x:c r="B54" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C54" s="11" t="str">
+      <x:c r="C54" s="8" t="str">
         <x:v>International Journal of Tourism Research</x:v>
       </x:c>
-      <x:c r="D54" s="11" t="str">
+      <x:c r="D54" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E54" s="11" t="str"/>
-      <x:c r="F54" s="11" t="str"/>
+      <x:c r="E54" s="8" t="str"/>
+      <x:c r="F54" s="8" t="str"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="11" t="str">
+      <x:c r="A55" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B55" s="11" t="n">
+      <x:c r="B55" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C55" s="11" t="str">
+      <x:c r="C55" s="8" t="str">
         <x:v>Tourism Planning and Development</x:v>
       </x:c>
-      <x:c r="D55" s="11" t="str">
+      <x:c r="D55" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Tourism%20Planning%20and%20Development</x:v>
       </x:c>
-      <x:c r="E55" s="11" t="str"/>
-      <x:c r="F55" s="11" t="str"/>
+      <x:c r="E55" s="8" t="str"/>
+      <x:c r="F55" s="8" t="str"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="11" t="str">
+      <x:c r="A56" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B56" s="11" t="n">
+      <x:c r="B56" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C56" s="11" t="str">
+      <x:c r="C56" s="8" t="str">
         <x:v>Journal of Hospitality &amp; Tourism Research</x:v>
       </x:c>
-      <x:c r="D56" s="11" t="str">
+      <x:c r="D56" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Hospitality%20%26%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E56" s="11" t="str"/>
-      <x:c r="F56" s="11" t="str"/>
+      <x:c r="E56" s="8" t="str"/>
+      <x:c r="F56" s="8" t="str"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="11" t="str">
+      <x:c r="A57" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B57" s="11" t="n">
+      <x:c r="B57" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C57" s="11" t="str">
+      <x:c r="C57" s="8" t="str">
         <x:v>Tourism Economics</x:v>
       </x:c>
-      <x:c r="D57" s="11" t="str">
+      <x:c r="D57" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20Economics</x:v>
       </x:c>
-      <x:c r="E57" s="11" t="str"/>
-      <x:c r="F57" s="11" t="str"/>
+      <x:c r="E57" s="8" t="str"/>
+      <x:c r="F57" s="8" t="str"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="11" t="str">
+      <x:c r="A58" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B58" s="11" t="n">
+      <x:c r="B58" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C58" s="11" t="str">
+      <x:c r="C58" s="8" t="str">
         <x:v>Journal of Hospitality and Tourism Management</x:v>
       </x:c>
-      <x:c r="D58" s="11" t="str">
+      <x:c r="D58" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-hospitality-and-tourism-management</x:v>
       </x:c>
-      <x:c r="E58" s="11" t="str"/>
-      <x:c r="F58" s="11" t="str"/>
+      <x:c r="E58" s="8" t="str"/>
+      <x:c r="F58" s="8" t="str"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="11" t="str">
+      <x:c r="A59" s="8" t="str">
         <x:v>Tourism Related</x:v>
       </x:c>
-      <x:c r="B59" s="11" t="n">
+      <x:c r="B59" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C59" s="11" t="str">
+      <x:c r="C59" s="8" t="str">
         <x:v>Tourism and Hospitality Research</x:v>
       </x:c>
-      <x:c r="D59" s="11" t="str">
+      <x:c r="D59" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20and%20Hospitality%20Research</x:v>
       </x:c>
-      <x:c r="E59" s="11" t="str"/>
-      <x:c r="F59" s="11" t="str"/>
+      <x:c r="E59" s="8" t="str"/>
+      <x:c r="F59" s="8" t="str"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="11" t="str">
+      <x:c r="A60" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B60" s="11" t="n">
+      <x:c r="B60" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C60" s="11" t="str">
+      <x:c r="C60" s="8" t="str">
         <x:v>Annals of Operations Research</x:v>
       </x:c>
-      <x:c r="D60" s="11" t="str">
+      <x:c r="D60" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E60" s="11" t="str"/>
-      <x:c r="F60" s="11" t="str"/>
+      <x:c r="E60" s="8" t="str"/>
+      <x:c r="F60" s="8" t="str"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="11" t="str">
+      <x:c r="A61" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B61" s="11" t="n">
+      <x:c r="B61" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C61" s="11" t="str">
+      <x:c r="C61" s="8" t="str">
         <x:v>Fuzzy Optimization and Decision Making</x:v>
       </x:c>
-      <x:c r="D61" s="11" t="str">
+      <x:c r="D61" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Fuzzy%20Optimization%20and%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E61" s="11" t="str"/>
-      <x:c r="F61" s="11" t="str"/>
+      <x:c r="E61" s="8" t="str"/>
+      <x:c r="F61" s="8" t="str"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="11" t="str">
+      <x:c r="A62" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B62" s="11" t="n">
+      <x:c r="B62" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C62" s="11" t="str">
+      <x:c r="C62" s="8" t="str">
         <x:v>Group Decision and Negotiation</x:v>
       </x:c>
-      <x:c r="D62" s="11" t="str">
+      <x:c r="D62" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Group%20Decision%20and%20Negotiation</x:v>
       </x:c>
-      <x:c r="E62" s="11" t="str"/>
-      <x:c r="F62" s="11" t="str"/>
+      <x:c r="E62" s="8" t="str"/>
+      <x:c r="F62" s="8" t="str"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="11" t="str">
+      <x:c r="A63" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B63" s="11" t="n">
+      <x:c r="B63" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C63" s="11" t="str">
+      <x:c r="C63" s="8" t="str">
         <x:v>Soft Computing</x:v>
       </x:c>
-      <x:c r="D63" s="11" t="str">
+      <x:c r="D63" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Soft%20Computing</x:v>
       </x:c>
-      <x:c r="E63" s="11" t="str"/>
-      <x:c r="F63" s="11" t="str"/>
+      <x:c r="E63" s="8" t="str"/>
+      <x:c r="F63" s="8" t="str"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="11" t="str">
+      <x:c r="A64" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B64" s="11" t="n">
+      <x:c r="B64" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C64" s="11" t="str">
+      <x:c r="C64" s="8" t="str">
         <x:v>International Journal of Machine Learning and Cybernetics</x:v>
       </x:c>
-      <x:c r="D64" s="11" t="str">
+      <x:c r="D64" s="8" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Machine%20Learning%20and%20Cybernetics</x:v>
       </x:c>
-      <x:c r="E64" s="11" t="str"/>
-      <x:c r="F64" s="11" t="str"/>
+      <x:c r="E64" s="8" t="str"/>
+      <x:c r="F64" s="8" t="str"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="11" t="str">
+      <x:c r="A65" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B65" s="11" t="n">
+      <x:c r="B65" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C65" s="11" t="str">
+      <x:c r="C65" s="8" t="str">
         <x:v>Knowledge and Information Systems</x:v>
       </x:c>
-      <x:c r="D65" s="11" t="str">
+      <x:c r="D65" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Knowledge%20and%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E65" s="11" t="str"/>
-      <x:c r="F65" s="11" t="str"/>
+      <x:c r="E65" s="8" t="str"/>
+      <x:c r="F65" s="8" t="str"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="11" t="str">
+      <x:c r="A66" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B66" s="11" t="n">
+      <x:c r="B66" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C66" s="11" t="str">
+      <x:c r="C66" s="8" t="str">
         <x:v>Neural Computing and Applications</x:v>
       </x:c>
-      <x:c r="D66" s="11" t="str">
+      <x:c r="D66" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Neural%20Computing%20and%20Applications</x:v>
       </x:c>
-      <x:c r="E66" s="11" t="str"/>
-      <x:c r="F66" s="11" t="str"/>
+      <x:c r="E66" s="8" t="str"/>
+      <x:c r="F66" s="8" t="str"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="11" t="str">
+      <x:c r="A67" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B67" s="11" t="n">
+      <x:c r="B67" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C67" s="11" t="str">
+      <x:c r="C67" s="8" t="str">
         <x:v>Applied Intelligence</x:v>
       </x:c>
-      <x:c r="D67" s="11" t="str">
+      <x:c r="D67" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Applied%20Intelligence</x:v>
       </x:c>
-      <x:c r="E67" s="11" t="str"/>
-      <x:c r="F67" s="11" t="str"/>
+      <x:c r="E67" s="8" t="str"/>
+      <x:c r="F67" s="8" t="str"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="11" t="str">
+      <x:c r="A68" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B68" s="11" t="n">
+      <x:c r="B68" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C68" s="11" t="str">
+      <x:c r="C68" s="8" t="str">
         <x:v>Cognitive Computation</x:v>
       </x:c>
-      <x:c r="D68" s="11" t="str">
+      <x:c r="D68" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Cognitive%20Computation</x:v>
       </x:c>
-      <x:c r="E68" s="11" t="str"/>
-      <x:c r="F68" s="11" t="str"/>
+      <x:c r="E68" s="8" t="str"/>
+      <x:c r="F68" s="8" t="str"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="11" t="str">
+      <x:c r="A69" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B69" s="11" t="n">
+      <x:c r="B69" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C69" s="11" t="str">
+      <x:c r="C69" s="8" t="str">
         <x:v>Complex &amp; Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D69" s="11" t="str">
+      <x:c r="D69" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Complex%20%26%20Intelligent%20Systems</x:v>
       </x:c>
-      <x:c r="E69" s="11" t="str"/>
-      <x:c r="F69" s="11" t="str"/>
+      <x:c r="E69" s="8" t="str"/>
+      <x:c r="F69" s="8" t="str"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="11" t="str">
+      <x:c r="A70" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B70" s="11" t="n">
+      <x:c r="B70" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C70" s="11" t="str">
+      <x:c r="C70" s="8" t="str">
         <x:v>International Journal of Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D70" s="11" t="str">
+      <x:c r="D70" s="8" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Fuzzy%20Systems</x:v>
       </x:c>
-      <x:c r="E70" s="11" t="str"/>
-      <x:c r="F70" s="11" t="str"/>
+      <x:c r="E70" s="8" t="str"/>
+      <x:c r="F70" s="8" t="str"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="11" t="str">
+      <x:c r="A71" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B71" s="11" t="n">
+      <x:c r="B71" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C71" s="11" t="str">
+      <x:c r="C71" s="8" t="str">
         <x:v>OR Spectrum</x:v>
       </x:c>
-      <x:c r="D71" s="11" t="str">
+      <x:c r="D71" s="8" t="str">
         <x:v>https://link.springer.com/search?query=OR%20Spectrum</x:v>
       </x:c>
-      <x:c r="E71" s="11" t="str"/>
-      <x:c r="F71" s="11" t="str"/>
+      <x:c r="E71" s="8" t="str"/>
+      <x:c r="F71" s="8" t="str"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="11" t="str">
+      <x:c r="A72" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B72" s="11" t="n">
+      <x:c r="B72" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C72" s="11" t="str">
+      <x:c r="C72" s="8" t="str">
         <x:v>Artificial Intelligence Review</x:v>
       </x:c>
-      <x:c r="D72" s="11" t="str">
+      <x:c r="D72" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Artificial%20Intelligence%20Review</x:v>
       </x:c>
-      <x:c r="E72" s="11" t="str"/>
-      <x:c r="F72" s="11" t="str"/>
+      <x:c r="E72" s="8" t="str"/>
+      <x:c r="F72" s="8" t="str"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="11" t="str">
+      <x:c r="A73" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B73" s="11" t="n">
+      <x:c r="B73" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C73" s="11" t="str">
+      <x:c r="C73" s="8" t="str">
         <x:v>Journal of Ambient Intelligence and Humanized Computing</x:v>
       </x:c>
-      <x:c r="D73" s="11" t="str">
+      <x:c r="D73" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Ambient%20Intelligence%20and%20Humanized%20Computing</x:v>
       </x:c>
-      <x:c r="E73" s="11" t="str"/>
-      <x:c r="F73" s="11" t="str"/>
+      <x:c r="E73" s="8" t="str"/>
+      <x:c r="F73" s="8" t="str"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="11" t="str">
+      <x:c r="A74" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B74" s="11" t="n">
+      <x:c r="B74" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C74" s="11" t="str">
+      <x:c r="C74" s="8" t="str">
         <x:v>Frontiers of Engineering Management</x:v>
       </x:c>
-      <x:c r="D74" s="11" t="str">
+      <x:c r="D74" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Frontiers%20of%20Engineering%20Management</x:v>
       </x:c>
-      <x:c r="E74" s="11" t="str"/>
-      <x:c r="F74" s="11" t="str"/>
+      <x:c r="E74" s="8" t="str"/>
+      <x:c r="F74" s="8" t="str"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="11" t="str">
+      <x:c r="A75" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B75" s="11" t="n">
+      <x:c r="B75" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C75" s="11" t="str">
+      <x:c r="C75" s="8" t="str">
         <x:v>Journal of Data, Information and Management</x:v>
       </x:c>
-      <x:c r="D75" s="11" t="str">
+      <x:c r="D75" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Data%2C%20Information%20and%20Management</x:v>
       </x:c>
-      <x:c r="E75" s="11" t="str"/>
-      <x:c r="F75" s="11" t="str"/>
+      <x:c r="E75" s="8" t="str"/>
+      <x:c r="F75" s="8" t="str"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="11" t="str">
+      <x:c r="A76" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B76" s="11" t="n">
+      <x:c r="B76" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C76" s="11" t="str">
+      <x:c r="C76" s="8" t="str">
         <x:v>Journal of Systems Science and Systems Engineering</x:v>
       </x:c>
-      <x:c r="D76" s="11" t="str">
+      <x:c r="D76" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Systems%20Engineering</x:v>
       </x:c>
-      <x:c r="E76" s="11" t="str"/>
-      <x:c r="F76" s="11" t="str"/>
+      <x:c r="E76" s="8" t="str"/>
+      <x:c r="F76" s="8" t="str"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="11" t="str">
+      <x:c r="A77" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B77" s="11" t="n">
+      <x:c r="B77" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C77" s="11" t="str">
+      <x:c r="C77" s="8" t="str">
         <x:v>Journal of Systems Science and Complexity</x:v>
       </x:c>
-      <x:c r="D77" s="11" t="str">
+      <x:c r="D77" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Complexity</x:v>
       </x:c>
-      <x:c r="E77" s="11" t="str"/>
-      <x:c r="F77" s="11" t="str"/>
+      <x:c r="E77" s="8" t="str"/>
+      <x:c r="F77" s="8" t="str"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="11" t="str">
+      <x:c r="A78" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B78" s="11" t="n">
+      <x:c r="B78" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C78" s="11" t="str">
+      <x:c r="C78" s="8" t="str">
         <x:v>Data Mining &amp; Knowledge Discovery</x:v>
       </x:c>
-      <x:c r="D78" s="11" t="str">
+      <x:c r="D78" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Data%20Mining%20%26%20Knowledge%20Discovery</x:v>
       </x:c>
-      <x:c r="E78" s="11" t="str"/>
-      <x:c r="F78" s="11" t="str"/>
+      <x:c r="E78" s="8" t="str"/>
+      <x:c r="F78" s="8" t="str"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="11" t="str">
+      <x:c r="A79" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B79" s="11" t="n">
+      <x:c r="B79" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C79" s="11" t="str">
+      <x:c r="C79" s="8" t="str">
         <x:v>Social Network Analysis and Mining</x:v>
       </x:c>
-      <x:c r="D79" s="11" t="str">
+      <x:c r="D79" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Social%20Network%20Analysis%20and%20Mining</x:v>
       </x:c>
-      <x:c r="E79" s="11" t="str"/>
-      <x:c r="F79" s="11" t="str"/>
+      <x:c r="E79" s="8" t="str"/>
+      <x:c r="F79" s="8" t="str"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="11" t="str">
+      <x:c r="A80" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B80" s="11" t="n">
+      <x:c r="B80" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C80" s="11" t="str">
+      <x:c r="C80" s="8" t="str">
         <x:v>Health Care Management Science</x:v>
       </x:c>
-      <x:c r="D80" s="11" t="str">
+      <x:c r="D80" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Health%20Care%20Management%20Science</x:v>
       </x:c>
-      <x:c r="E80" s="11" t="str"/>
-      <x:c r="F80" s="11" t="str"/>
+      <x:c r="E80" s="8" t="str"/>
+      <x:c r="F80" s="8" t="str"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="11" t="str">
+      <x:c r="A81" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B81" s="11" t="n">
+      <x:c r="B81" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C81" s="11" t="str">
+      <x:c r="C81" s="8" t="str">
         <x:v>Electronic Commerce Research</x:v>
       </x:c>
-      <x:c r="D81" s="11" t="str">
+      <x:c r="D81" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Electronic%20Commerce%20Research</x:v>
       </x:c>
-      <x:c r="E81" s="11" t="str"/>
-      <x:c r="F81" s="11" t="str"/>
+      <x:c r="E81" s="8" t="str"/>
+      <x:c r="F81" s="8" t="str"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="11" t="str">
+      <x:c r="A82" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B82" s="11" t="n">
+      <x:c r="B82" s="8" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C82" s="11" t="str">
+      <x:c r="C82" s="8" t="str">
         <x:v>Operational Research</x:v>
       </x:c>
-      <x:c r="D82" s="11" t="str">
+      <x:c r="D82" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Operational%20Research</x:v>
       </x:c>
-      <x:c r="E82" s="11" t="str"/>
-      <x:c r="F82" s="11" t="str"/>
+      <x:c r="E82" s="8" t="str"/>
+      <x:c r="F82" s="8" t="str"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="11" t="str">
+      <x:c r="A83" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B83" s="11" t="n">
+      <x:c r="B83" s="8" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C83" s="11" t="str">
+      <x:c r="C83" s="8" t="str">
         <x:v>Information Technology &amp; Tourism</x:v>
       </x:c>
-      <x:c r="D83" s="11" t="str">
+      <x:c r="D83" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Information%20Technology%20%26%20Tourism</x:v>
       </x:c>
-      <x:c r="E83" s="11" t="str"/>
-      <x:c r="F83" s="11" t="str"/>
+      <x:c r="E83" s="8" t="str"/>
+      <x:c r="F83" s="8" t="str"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="11" t="str">
+      <x:c r="A84" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B84" s="11" t="n">
+      <x:c r="B84" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C84" s="11" t="str">
+      <x:c r="C84" s="8" t="str">
         <x:v>TOP</x:v>
       </x:c>
-      <x:c r="D84" s="11" t="str">
+      <x:c r="D84" s="8" t="str">
         <x:v>https://link.springer.com/search?query=TOP</x:v>
       </x:c>
-      <x:c r="E84" s="11" t="str"/>
-      <x:c r="F84" s="11" t="str"/>
+      <x:c r="E84" s="8" t="str"/>
+      <x:c r="F84" s="8" t="str"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="11" t="str">
+      <x:c r="A85" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B85" s="11" t="n">
+      <x:c r="B85" s="8" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C85" s="11" t="str">
+      <x:c r="C85" s="8" t="str">
         <x:v>Theory and Decision</x:v>
       </x:c>
-      <x:c r="D85" s="11" t="str">
+      <x:c r="D85" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Theory%20and%20Decision</x:v>
       </x:c>
-      <x:c r="E85" s="11" t="str"/>
-      <x:c r="F85" s="11" t="str"/>
+      <x:c r="E85" s="8" t="str"/>
+      <x:c r="F85" s="8" t="str"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="11" t="str">
+      <x:c r="A86" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B86" s="11" t="n">
+      <x:c r="B86" s="8" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C86" s="11" t="str">
+      <x:c r="C86" s="8" t="str">
         <x:v>Annals of Data Science</x:v>
       </x:c>
-      <x:c r="D86" s="11" t="str">
+      <x:c r="D86" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E86" s="11" t="str"/>
-      <x:c r="F86" s="11" t="str"/>
+      <x:c r="E86" s="8" t="str"/>
+      <x:c r="F86" s="8" t="str"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="11" t="str">
+      <x:c r="A87" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B87" s="11" t="n">
+      <x:c r="B87" s="8" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C87" s="11" t="str">
+      <x:c r="C87" s="8" t="str">
         <x:v>Central European Journal of Operations Research</x:v>
       </x:c>
-      <x:c r="D87" s="11" t="str">
+      <x:c r="D87" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Central%20European%20Journal%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E87" s="11" t="str"/>
-      <x:c r="F87" s="11" t="str"/>
+      <x:c r="E87" s="8" t="str"/>
+      <x:c r="F87" s="8" t="str"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="11" t="str">
+      <x:c r="A88" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B88" s="11" t="n">
+      <x:c r="B88" s="8" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C88" s="11" t="str">
-        <x:v>Science China Information Sciences</x:v>
-      </x:c>
-      <x:c r="D88" s="11" t="str">
-        <x:v>https://www.sciengine.com</x:v>
-      </x:c>
-      <x:c r="E88" s="11" t="str"/>
-      <x:c r="F88" s="11" t="str"/>
+      <x:c r="C88" s="8" t="str">
+        <x:v>SCIENCE CHINA Information Sciences</x:v>
+      </x:c>
+      <x:c r="D88" s="8" t="str">
+        <x:v>https://www.sciengine.com/search?field=title&amp;query=SCIENCE%20CHINA%20Information%20Sciences</x:v>
+      </x:c>
+      <x:c r="E88" s="8" t="str">
+        <x:v>SciEngine|https://www.sciengine.com</x:v>
+      </x:c>
+      <x:c r="F88" s="8" t="str"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="11" t="str">
+      <x:c r="A89" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B89" s="11" t="n">
+      <x:c r="B89" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C89" s="11" t="str">
+      <x:c r="C89" s="8" t="str">
         <x:v>Progress in Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D89" s="11" t="str">
+      <x:c r="D89" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Progress%20in%20Artificial%20Intelligence</x:v>
       </x:c>
-      <x:c r="E89" s="11" t="str"/>
-      <x:c r="F89" s="11" t="str"/>
+      <x:c r="E89" s="8" t="str"/>
+      <x:c r="F89" s="8" t="str"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="11" t="str">
+      <x:c r="A90" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B90" s="11" t="n">
+      <x:c r="B90" s="8" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C90" s="11" t="str">
+      <x:c r="C90" s="8" t="str">
         <x:v>Granular Computing</x:v>
       </x:c>
-      <x:c r="D90" s="11" t="str">
+      <x:c r="D90" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Granular%20Computing</x:v>
       </x:c>
-      <x:c r="E90" s="11" t="str"/>
-      <x:c r="F90" s="11" t="str"/>
+      <x:c r="E90" s="8" t="str"/>
+      <x:c r="F90" s="8" t="str"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="11" t="str">
+      <x:c r="A91" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B91" s="11" t="n">
+      <x:c r="B91" s="8" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C91" s="11" t="str">
+      <x:c r="C91" s="8" t="str">
         <x:v>Journal of Intelligent Manufacturing</x:v>
       </x:c>
-      <x:c r="D91" s="11" t="str">
+      <x:c r="D91" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Intelligent%20Manufacturing</x:v>
       </x:c>
-      <x:c r="E91" s="11" t="str"/>
-      <x:c r="F91" s="11" t="str"/>
+      <x:c r="E91" s="8" t="str"/>
+      <x:c r="F91" s="8" t="str"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="11" t="str">
+      <x:c r="A92" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B92" s="11" t="n">
+      <x:c r="B92" s="8" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C92" s="11" t="str">
+      <x:c r="C92" s="8" t="str">
         <x:v>Nature Computational Science</x:v>
       </x:c>
-      <x:c r="D92" s="11" t="str">
-        <x:v>https://www.nature.com</x:v>
-      </x:c>
-      <x:c r="E92" s="11" t="str"/>
-      <x:c r="F92" s="11" t="str"/>
+      <x:c r="D92" s="8" t="str">
+        <x:v>https://www.nature.com/search?q=Nature%20Computational%20Science</x:v>
+      </x:c>
+      <x:c r="E92" s="8" t="str">
+        <x:v>Nature|https://www.nature.com</x:v>
+      </x:c>
+      <x:c r="F92" s="8" t="str"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="11" t="str">
+      <x:c r="A93" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B93" s="11" t="n">
+      <x:c r="B93" s="8" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C93" s="11" t="str">
+      <x:c r="C93" s="8" t="str">
         <x:v>Nature Machine Intelligence</x:v>
       </x:c>
-      <x:c r="D93" s="11" t="str">
-        <x:v>https://www.nature.com</x:v>
-      </x:c>
-      <x:c r="E93" s="11" t="str"/>
-      <x:c r="F93" s="11" t="str"/>
+      <x:c r="D93" s="8" t="str">
+        <x:v>https://www.nature.com/search?q=Nature%20Machine%20Intelligence</x:v>
+      </x:c>
+      <x:c r="E93" s="8" t="str">
+        <x:v>Nature|https://www.nature.com</x:v>
+      </x:c>
+      <x:c r="F93" s="8" t="str"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="11" t="str">
+      <x:c r="A94" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B94" s="11" t="n">
+      <x:c r="B94" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C94" s="11" t="str">
+      <x:c r="C94" s="8" t="str">
         <x:v>npj Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D94" s="11" t="str">
-        <x:v>https://www.nature.com</x:v>
-      </x:c>
-      <x:c r="E94" s="11" t="str"/>
-      <x:c r="F94" s="11" t="str"/>
+      <x:c r="D94" s="8" t="str">
+        <x:v>https://www.nature.com/search?q=npj%20Artificial%20Intelligence</x:v>
+      </x:c>
+      <x:c r="E94" s="8" t="str">
+        <x:v>Nature|https://www.nature.com</x:v>
+      </x:c>
+      <x:c r="F94" s="8" t="str"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="11" t="str">
+      <x:c r="A95" s="8" t="str">
         <x:v>Springer</x:v>
       </x:c>
-      <x:c r="B95" s="11" t="n">
+      <x:c r="B95" s="8" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C95" s="11" t="str">
+      <x:c r="C95" s="8" t="str">
         <x:v>Nature Communications</x:v>
       </x:c>
-      <x:c r="D95" s="11" t="str">
-        <x:v>https://www.nature.com</x:v>
-      </x:c>
-      <x:c r="E95" s="11" t="str"/>
-      <x:c r="F95" s="11" t="str"/>
+      <x:c r="D95" s="8" t="str">
+        <x:v>https://www.nature.com/search?q=Nature%20Communications</x:v>
+      </x:c>
+      <x:c r="E95" s="8" t="str">
+        <x:v>Nature|https://www.nature.com</x:v>
+      </x:c>
+      <x:c r="F95" s="8" t="str"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B96" s="11" t="n">
+      <x:c r="A96" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B96" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C96" s="11" t="str">
+      <x:c r="C96" s="8" t="str">
         <x:v>IEEE Transactions on Systems, Man, and Cybernetics: Systems</x:v>
       </x:c>
-      <x:c r="D96" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E96" s="11" t="str"/>
-      <x:c r="F96" s="11" t="str"/>
+      <x:c r="D96" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Systems%2C%20Man%2C%20and%20Cybernetics%3A%20Systems</x:v>
+      </x:c>
+      <x:c r="E96" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F96" s="8" t="str"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B97" s="11" t="n">
+      <x:c r="A97" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B97" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C97" s="11" t="str">
+      <x:c r="C97" s="8" t="str">
         <x:v>IEEE Transactions on Cybernetics</x:v>
       </x:c>
-      <x:c r="D97" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E97" s="11" t="str"/>
-      <x:c r="F97" s="11" t="str"/>
+      <x:c r="D97" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Cybernetics</x:v>
+      </x:c>
+      <x:c r="E97" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F97" s="8" t="str"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B98" s="11" t="n">
+      <x:c r="A98" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B98" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C98" s="11" t="str">
+      <x:c r="C98" s="8" t="str">
         <x:v>IEEE Transactions on Computational Social Systems</x:v>
       </x:c>
-      <x:c r="D98" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E98" s="11" t="str"/>
-      <x:c r="F98" s="11" t="str"/>
+      <x:c r="D98" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Computational%20Social%20Systems</x:v>
+      </x:c>
+      <x:c r="E98" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F98" s="8" t="str"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B99" s="11" t="n">
+      <x:c r="A99" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B99" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C99" s="11" t="str">
+      <x:c r="C99" s="8" t="str">
         <x:v>IEEE Transactions on Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D99" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E99" s="11" t="str"/>
-      <x:c r="F99" s="11" t="str"/>
+      <x:c r="D99" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Fuzzy%20Systems</x:v>
+      </x:c>
+      <x:c r="E99" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F99" s="8" t="str"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B100" s="11" t="n">
+      <x:c r="A100" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B100" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C100" s="11" t="str">
+      <x:c r="C100" s="8" t="str">
         <x:v>IEEE Transactions on Reliability</x:v>
       </x:c>
-      <x:c r="D100" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E100" s="11" t="str"/>
-      <x:c r="F100" s="11" t="str"/>
+      <x:c r="D100" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Reliability</x:v>
+      </x:c>
+      <x:c r="E100" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F100" s="8" t="str"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B101" s="11" t="n">
+      <x:c r="A101" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B101" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C101" s="11" t="str">
+      <x:c r="C101" s="8" t="str">
         <x:v>IEEE Transactions on Engineering Management</x:v>
       </x:c>
-      <x:c r="D101" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E101" s="11" t="str"/>
-      <x:c r="F101" s="11" t="str"/>
+      <x:c r="D101" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Engineering%20Management</x:v>
+      </x:c>
+      <x:c r="E101" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F101" s="8" t="str"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B102" s="11" t="n">
+      <x:c r="A102" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B102" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C102" s="11" t="str">
+      <x:c r="C102" s="8" t="str">
         <x:v>IEEE Transactions on Artificial Intelligence</x:v>
       </x:c>
-      <x:c r="D102" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E102" s="11" t="str"/>
-      <x:c r="F102" s="11" t="str"/>
+      <x:c r="D102" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Artificial%20Intelligence</x:v>
+      </x:c>
+      <x:c r="E102" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F102" s="8" t="str"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B103" s="11" t="n">
+      <x:c r="A103" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B103" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C103" s="11" t="str">
+      <x:c r="C103" s="8" t="str">
         <x:v>IEEE Transactions on Knowledge and Data Engineering</x:v>
       </x:c>
-      <x:c r="D103" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E103" s="11" t="str"/>
-      <x:c r="F103" s="11" t="str"/>
+      <x:c r="D103" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Knowledge%20and%20Data%20Engineering</x:v>
+      </x:c>
+      <x:c r="E103" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F103" s="8" t="str"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B104" s="11" t="n">
+      <x:c r="A104" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B104" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C104" s="11" t="str">
+      <x:c r="C104" s="8" t="str">
         <x:v>IEEE Transactions on Evolutionary Computation</x:v>
       </x:c>
-      <x:c r="D104" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E104" s="11" t="str"/>
-      <x:c r="F104" s="11" t="str"/>
+      <x:c r="D104" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Evolutionary%20Computation</x:v>
+      </x:c>
+      <x:c r="E104" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F104" s="8" t="str"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B105" s="11" t="n">
+      <x:c r="A105" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B105" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C105" s="11" t="str">
+      <x:c r="C105" s="8" t="str">
         <x:v>IEEE Transactions on Neural Networks and Learning Systems</x:v>
       </x:c>
-      <x:c r="D105" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E105" s="11" t="str"/>
-      <x:c r="F105" s="11" t="str"/>
+      <x:c r="D105" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Neural%20Networks%20and%20Learning%20Systems</x:v>
+      </x:c>
+      <x:c r="E105" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F105" s="8" t="str"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B106" s="11" t="n">
+      <x:c r="A106" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B106" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C106" s="11" t="str">
+      <x:c r="C106" s="8" t="str">
         <x:v>IEEE Transactions on Pattern Analysis and Machine Intelligence</x:v>
       </x:c>
-      <x:c r="D106" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E106" s="11" t="str"/>
-      <x:c r="F106" s="11" t="str"/>
+      <x:c r="D106" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Pattern%20Analysis%20and%20Machine%20Intelligence</x:v>
+      </x:c>
+      <x:c r="E106" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F106" s="8" t="str"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B107" s="11" t="n">
+      <x:c r="A107" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B107" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C107" s="11" t="str">
+      <x:c r="C107" s="8" t="str">
         <x:v>IEEE Transactions on Big Data</x:v>
       </x:c>
-      <x:c r="D107" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E107" s="11" t="str"/>
-      <x:c r="F107" s="11" t="str"/>
+      <x:c r="D107" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Big%20Data</x:v>
+      </x:c>
+      <x:c r="E107" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F107" s="8" t="str"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B108" s="11" t="n">
+      <x:c r="A108" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B108" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C108" s="11" t="str">
+      <x:c r="C108" s="8" t="str">
         <x:v>IEEE Transactions on Network Science and Engineering</x:v>
       </x:c>
-      <x:c r="D108" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E108" s="11" t="str"/>
-      <x:c r="F108" s="11" t="str"/>
+      <x:c r="D108" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Network%20Science%20and%20Engineering</x:v>
+      </x:c>
+      <x:c r="E108" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F108" s="8" t="str"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B109" s="11" t="n">
+      <x:c r="A109" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B109" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C109" s="11" t="str">
+      <x:c r="C109" s="8" t="str">
         <x:v>IEEE/CAA Journal of Automatica Sinica</x:v>
       </x:c>
-      <x:c r="D109" s="11" t="str">
+      <x:c r="D109" s="8" t="str">
         <x:v>https://www.ieee-jas.net</x:v>
       </x:c>
-      <x:c r="E109" s="11" t="str"/>
-      <x:c r="F109" s="11" t="str"/>
+      <x:c r="E109" s="8" t="str"/>
+      <x:c r="F109" s="8" t="str"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B110" s="11" t="n">
+      <x:c r="A110" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B110" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C110" s="11" t="str">
+      <x:c r="C110" s="8" t="str">
         <x:v>IEEE Transactions on Cognitive and Developmental Systems</x:v>
       </x:c>
-      <x:c r="D110" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E110" s="11" t="str"/>
-      <x:c r="F110" s="11" t="str"/>
+      <x:c r="D110" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Cognitive%20and%20Developmental%20Systems</x:v>
+      </x:c>
+      <x:c r="E110" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F110" s="8" t="str"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B111" s="11" t="n">
+      <x:c r="A111" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B111" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C111" s="11" t="str">
+      <x:c r="C111" s="8" t="str">
         <x:v>IEEE Transactions on Emerging Topics in Computational Intelligence</x:v>
       </x:c>
-      <x:c r="D111" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E111" s="11" t="str"/>
-      <x:c r="F111" s="11" t="str"/>
+      <x:c r="D111" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Emerging%20Topics%20in%20Computational%20Intelligence</x:v>
+      </x:c>
+      <x:c r="E111" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F111" s="8" t="str"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B112" s="11" t="n">
+      <x:c r="A112" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B112" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C112" s="11" t="str">
+      <x:c r="C112" s="8" t="str">
         <x:v>IEEE Systems Journal</x:v>
       </x:c>
-      <x:c r="D112" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E112" s="11" t="str"/>
-      <x:c r="F112" s="11" t="str"/>
+      <x:c r="D112" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Systems%20Journal</x:v>
+      </x:c>
+      <x:c r="E112" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F112" s="8" t="str"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B113" s="11" t="n">
+      <x:c r="A113" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B113" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C113" s="11" t="str">
+      <x:c r="C113" s="8" t="str">
         <x:v>IEEE Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D113" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E113" s="11" t="str"/>
-      <x:c r="F113" s="11" t="str"/>
+      <x:c r="D113" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Intelligent%20Systems</x:v>
+      </x:c>
+      <x:c r="E113" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F113" s="8" t="str"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B114" s="11" t="n">
+      <x:c r="A114" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B114" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C114" s="11" t="str">
+      <x:c r="C114" s="8" t="str">
         <x:v>Journal of Systems Engineering and Electronics</x:v>
       </x:c>
-      <x:c r="D114" s="11" t="str">
+      <x:c r="D114" s="8" t="str">
         <x:v>https://www.jseepub.com</x:v>
       </x:c>
-      <x:c r="E114" s="11" t="str"/>
-      <x:c r="F114" s="11" t="str"/>
+      <x:c r="E114" s="8" t="str"/>
+      <x:c r="F114" s="8" t="str"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B115" s="11" t="n">
+      <x:c r="A115" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B115" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C115" s="11" t="str">
+      <x:c r="C115" s="8" t="str">
         <x:v>IEEE Transactions on Automation Science and Engineering</x:v>
       </x:c>
-      <x:c r="D115" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E115" s="11" t="str"/>
-      <x:c r="F115" s="11" t="str"/>
+      <x:c r="D115" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Automation%20Science%20and%20Engineering</x:v>
+      </x:c>
+      <x:c r="E115" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F115" s="8" t="str"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B116" s="11" t="n">
+      <x:c r="A116" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B116" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C116" s="11" t="str">
+      <x:c r="C116" s="8" t="str">
         <x:v>IEEE Transactions on Automatic Control</x:v>
       </x:c>
-      <x:c r="D116" s="11" t="str">
-        <x:v>https://ieeexplore.ieee.org</x:v>
-      </x:c>
-      <x:c r="E116" s="11" t="str"/>
-      <x:c r="F116" s="11" t="str"/>
+      <x:c r="D116" s="8" t="str">
+        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Automatic%20Control</x:v>
+      </x:c>
+      <x:c r="E116" s="8" t="str">
+        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
+      </x:c>
+      <x:c r="F116" s="8" t="str"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B117" s="11" t="n">
+      <x:c r="A117" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B117" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C117" s="11" t="str">
+      <x:c r="C117" s="8" t="str">
         <x:v>Management Science</x:v>
       </x:c>
-      <x:c r="D117" s="11" t="str">
+      <x:c r="D117" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Management%20Science</x:v>
       </x:c>
-      <x:c r="E117" s="11" t="str"/>
-      <x:c r="F117" s="11" t="str"/>
+      <x:c r="E117" s="8" t="str"/>
+      <x:c r="F117" s="8" t="str"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B118" s="11" t="n">
+      <x:c r="A118" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B118" s="8" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C118" s="11" t="str">
+      <x:c r="C118" s="8" t="str">
         <x:v>Operations Research</x:v>
       </x:c>
-      <x:c r="D118" s="11" t="str">
+      <x:c r="D118" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Operations%20Research</x:v>
       </x:c>
-      <x:c r="E118" s="11" t="str"/>
-      <x:c r="F118" s="11" t="str"/>
+      <x:c r="E118" s="8" t="str"/>
+      <x:c r="F118" s="8" t="str"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B119" s="11" t="n">
+      <x:c r="A119" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B119" s="8" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C119" s="11" t="str">
+      <x:c r="C119" s="8" t="str">
         <x:v>INFORMS Journal on Computing</x:v>
       </x:c>
-      <x:c r="D119" s="11" t="str">
+      <x:c r="D119" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Computing</x:v>
       </x:c>
-      <x:c r="E119" s="11" t="str"/>
-      <x:c r="F119" s="11" t="str"/>
+      <x:c r="E119" s="8" t="str"/>
+      <x:c r="F119" s="8" t="str"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B120" s="11" t="n">
+      <x:c r="A120" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B120" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C120" s="11" t="str">
+      <x:c r="C120" s="8" t="str">
         <x:v>Information Systems Research</x:v>
       </x:c>
-      <x:c r="D120" s="11" t="str">
+      <x:c r="D120" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Information%20Systems%20Research</x:v>
       </x:c>
-      <x:c r="E120" s="11" t="str"/>
-      <x:c r="F120" s="11" t="str"/>
+      <x:c r="E120" s="8" t="str"/>
+      <x:c r="F120" s="8" t="str"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B121" s="11" t="n">
+      <x:c r="A121" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B121" s="8" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C121" s="11" t="str">
+      <x:c r="C121" s="8" t="str">
         <x:v>Manufacturing &amp; Service Operations Management</x:v>
       </x:c>
-      <x:c r="D121" s="11" t="str">
+      <x:c r="D121" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Manufacturing%20%26%20Service%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E121" s="11" t="str"/>
-      <x:c r="F121" s="11" t="str"/>
+      <x:c r="E121" s="8" t="str"/>
+      <x:c r="F121" s="8" t="str"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B122" s="11" t="n">
+      <x:c r="A122" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B122" s="8" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C122" s="11" t="str">
+      <x:c r="C122" s="8" t="str">
         <x:v>Decision Analysis</x:v>
       </x:c>
-      <x:c r="D122" s="11" t="str">
+      <x:c r="D122" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E122" s="11" t="str"/>
-      <x:c r="F122" s="11" t="str"/>
+      <x:c r="E122" s="8" t="str"/>
+      <x:c r="F122" s="8" t="str"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B123" s="11" t="n">
+      <x:c r="A123" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B123" s="8" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C123" s="11" t="str">
+      <x:c r="C123" s="8" t="str">
         <x:v>Production and Operations Management</x:v>
       </x:c>
-      <x:c r="D123" s="11" t="str">
+      <x:c r="D123" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Production%20and%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E123" s="11" t="str"/>
-      <x:c r="F123" s="11" t="str"/>
+      <x:c r="E123" s="8" t="str"/>
+      <x:c r="F123" s="8" t="str"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B124" s="11" t="n">
+      <x:c r="A124" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B124" s="8" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C124" s="11" t="str">
+      <x:c r="C124" s="8" t="str">
         <x:v>INFORMS Journal on Data Science</x:v>
       </x:c>
-      <x:c r="D124" s="11" t="str">
+      <x:c r="D124" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E124" s="11" t="str"/>
-      <x:c r="F124" s="11" t="str"/>
+      <x:c r="E124" s="8" t="str"/>
+      <x:c r="F124" s="8" t="str"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B125" s="11" t="n">
+      <x:c r="A125" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B125" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C125" s="11" t="str">
+      <x:c r="C125" s="8" t="str">
         <x:v>ACM Computing Surveys</x:v>
       </x:c>
-      <x:c r="D125" s="11" t="str">
+      <x:c r="D125" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Computing%20Surveys</x:v>
       </x:c>
-      <x:c r="E125" s="11" t="str"/>
-      <x:c r="F125" s="11" t="str"/>
+      <x:c r="E125" s="8" t="str"/>
+      <x:c r="F125" s="8" t="str"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B126" s="11" t="n">
+      <x:c r="A126" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B126" s="8" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C126" s="11" t="str">
+      <x:c r="C126" s="8" t="str">
         <x:v>ACM Transactions on Intelligent Systems and Technology</x:v>
       </x:c>
-      <x:c r="D126" s="11" t="str">
+      <x:c r="D126" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Intelligent%20Systems%20and%20Technology</x:v>
       </x:c>
-      <x:c r="E126" s="11" t="str"/>
-      <x:c r="F126" s="11" t="str"/>
+      <x:c r="E126" s="8" t="str"/>
+      <x:c r="F126" s="8" t="str"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B127" s="11" t="n">
+      <x:c r="A127" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B127" s="8" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C127" s="11" t="str">
+      <x:c r="C127" s="8" t="str">
         <x:v>ACM Transactions on Knowledge Discovery from Data</x:v>
       </x:c>
-      <x:c r="D127" s="11" t="str">
+      <x:c r="D127" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Knowledge%20Discovery%20from%20Data</x:v>
       </x:c>
-      <x:c r="E127" s="11" t="str"/>
-      <x:c r="F127" s="11" t="str"/>
+      <x:c r="E127" s="8" t="str"/>
+      <x:c r="F127" s="8" t="str"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B128" s="11" t="n">
+      <x:c r="A128" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B128" s="8" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C128" s="11" t="str">
+      <x:c r="C128" s="8" t="str">
         <x:v>ACM Transactions on Management Information Systems</x:v>
       </x:c>
-      <x:c r="D128" s="11" t="str">
+      <x:c r="D128" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Management%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E128" s="11" t="str"/>
-      <x:c r="F128" s="11" t="str"/>
+      <x:c r="E128" s="8" t="str"/>
+      <x:c r="F128" s="8" t="str"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B129" s="11" t="n">
+      <x:c r="A129" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B129" s="8" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C129" s="11" t="str">
+      <x:c r="C129" s="8" t="str">
         <x:v>ACM Transactions on Information Systems</x:v>
       </x:c>
-      <x:c r="D129" s="11" t="str">
+      <x:c r="D129" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E129" s="11" t="str"/>
-      <x:c r="F129" s="11" t="str"/>
+      <x:c r="E129" s="8" t="str"/>
+      <x:c r="F129" s="8" t="str"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B130" s="11" t="n">
+      <x:c r="A130" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B130" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C130" s="11" t="str">
+      <x:c r="C130" s="8" t="str">
         <x:v>ACM Transactions on Internet Technology</x:v>
       </x:c>
-      <x:c r="D130" s="11" t="str">
+      <x:c r="D130" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Internet%20Technology</x:v>
       </x:c>
-      <x:c r="E130" s="11" t="str"/>
-      <x:c r="F130" s="11" t="str"/>
+      <x:c r="E130" s="8" t="str"/>
+      <x:c r="F130" s="8" t="str"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B131" s="11" t="n">
+      <x:c r="A131" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B131" s="8" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C131" s="11" t="str">
+      <x:c r="C131" s="8" t="str">
         <x:v>ACM Transactions on Modeling and Computer Simulation</x:v>
       </x:c>
-      <x:c r="D131" s="11" t="str">
+      <x:c r="D131" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Modeling%20and%20Computer%20Simulation</x:v>
       </x:c>
-      <x:c r="E131" s="11" t="str"/>
-      <x:c r="F131" s="11" t="str"/>
+      <x:c r="E131" s="8" t="str"/>
+      <x:c r="F131" s="8" t="str"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B132" s="11" t="n">
+      <x:c r="A132" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B132" s="8" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C132" s="11" t="str">
+      <x:c r="C132" s="8" t="str">
         <x:v>ACM Transactions on Social Computing</x:v>
       </x:c>
-      <x:c r="D132" s="11" t="str">
+      <x:c r="D132" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Social%20Computing</x:v>
       </x:c>
-      <x:c r="E132" s="11" t="str"/>
-      <x:c r="F132" s="11" t="str"/>
+      <x:c r="E132" s="8" t="str"/>
+      <x:c r="F132" s="8" t="str"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B133" s="11" t="n">
+      <x:c r="A133" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B133" s="8" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C133" s="11" t="str">
+      <x:c r="C133" s="8" t="str">
         <x:v>ACM Transactions on the Web</x:v>
       </x:c>
-      <x:c r="D133" s="11" t="str">
+      <x:c r="D133" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20the%20Web</x:v>
       </x:c>
-      <x:c r="E133" s="11" t="str"/>
-      <x:c r="F133" s="11" t="str"/>
+      <x:c r="E133" s="8" t="str"/>
+      <x:c r="F133" s="8" t="str"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B134" s="11" t="n">
+      <x:c r="A134" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B134" s="8" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C134" s="11" t="str">
+      <x:c r="C134" s="8" t="str">
         <x:v>ACM Transactions on Recommender Systems</x:v>
       </x:c>
-      <x:c r="D134" s="11" t="str">
+      <x:c r="D134" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Recommender%20Systems</x:v>
       </x:c>
-      <x:c r="E134" s="11" t="str"/>
-      <x:c r="F134" s="11" t="str"/>
+      <x:c r="E134" s="8" t="str"/>
+      <x:c r="F134" s="8" t="str"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="11" t="str">
-        <x:v>IEEE/INFORMS/ACM</x:v>
-      </x:c>
-      <x:c r="B135" s="11" t="n">
+      <x:c r="A135" s="8" t="str">
+        <x:v>IEEE/INFORMS/ACM</x:v>
+      </x:c>
+      <x:c r="B135" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C135" s="11" t="str">
+      <x:c r="C135" s="8" t="str">
         <x:v>ACM/IMS Transactions on Data Science</x:v>
       </x:c>
-      <x:c r="D135" s="11" t="str">
+      <x:c r="D135" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM/IMS%20Transactions%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E135" s="11" t="str"/>
-      <x:c r="F135" s="11" t="str"/>
+      <x:c r="E135" s="8" t="str"/>
+      <x:c r="F135" s="8" t="str"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="11" t="str">
+      <x:c r="A136" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B136" s="11" t="n">
+      <x:c r="B136" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C136" s="11" t="str">
+      <x:c r="C136" s="8" t="str">
         <x:v>Journal of Forecasting</x:v>
       </x:c>
-      <x:c r="D136" s="11" t="str">
+      <x:c r="D136" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Forecasting</x:v>
       </x:c>
-      <x:c r="E136" s="11" t="str"/>
-      <x:c r="F136" s="11" t="str"/>
+      <x:c r="E136" s="8" t="str"/>
+      <x:c r="F136" s="8" t="str"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="11" t="str">
+      <x:c r="A137" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B137" s="11" t="n">
+      <x:c r="B137" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C137" s="11" t="str">
+      <x:c r="C137" s="8" t="str">
         <x:v>International Journal of Intelligent Systems</x:v>
       </x:c>
-      <x:c r="D137" s="11" t="str">
-        <x:v>https://www.hindawi.com</x:v>
-      </x:c>
-      <x:c r="E137" s="11" t="str"/>
-      <x:c r="F137" s="11" t="str"/>
+      <x:c r="D137" s="8" t="str">
+        <x:v>https://www.hindawi.com/search/all/International%20Journal%20of%20Intelligent%20Systems/</x:v>
+      </x:c>
+      <x:c r="E137" s="8" t="str">
+        <x:v>Hindawi|https://www.hindawi.com</x:v>
+      </x:c>
+      <x:c r="F137" s="8" t="str"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="11" t="str">
+      <x:c r="A138" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B138" s="11" t="n">
+      <x:c r="B138" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C138" s="11" t="str">
+      <x:c r="C138" s="8" t="str">
         <x:v>Expert Systems</x:v>
       </x:c>
-      <x:c r="D138" s="11" t="str">
+      <x:c r="D138" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Expert%20Systems</x:v>
       </x:c>
-      <x:c r="E138" s="11" t="str"/>
-      <x:c r="F138" s="11" t="str"/>
+      <x:c r="E138" s="8" t="str"/>
+      <x:c r="F138" s="8" t="str"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="11" t="str">
+      <x:c r="A139" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B139" s="11" t="n">
+      <x:c r="B139" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C139" s="11" t="str">
+      <x:c r="C139" s="8" t="str">
         <x:v>International Transactions in Operational Research</x:v>
       </x:c>
-      <x:c r="D139" s="11" t="str">
+      <x:c r="D139" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Transactions%20in%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E139" s="11" t="str"/>
-      <x:c r="F139" s="11" t="str"/>
+      <x:c r="E139" s="8" t="str"/>
+      <x:c r="F139" s="8" t="str"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="11" t="str">
+      <x:c r="A140" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B140" s="11" t="n">
+      <x:c r="B140" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C140" s="11" t="str">
+      <x:c r="C140" s="8" t="str">
         <x:v>Journal of Multi-Criteria Decision Analysis</x:v>
       </x:c>
-      <x:c r="D140" s="11" t="str">
+      <x:c r="D140" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Multi-Criteria%20Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E140" s="11" t="str"/>
-      <x:c r="F140" s="11" t="str"/>
+      <x:c r="E140" s="8" t="str"/>
+      <x:c r="F140" s="8" t="str"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="11" t="str">
+      <x:c r="A141" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B141" s="11" t="n">
+      <x:c r="B141" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C141" s="11" t="str">
+      <x:c r="C141" s="8" t="str">
         <x:v>Decision Sciences Journal</x:v>
       </x:c>
-      <x:c r="D141" s="11" t="str">
+      <x:c r="D141" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Decision%20Sciences%20Journal</x:v>
       </x:c>
-      <x:c r="E141" s="11" t="str"/>
-      <x:c r="F141" s="11" t="str"/>
+      <x:c r="E141" s="8" t="str"/>
+      <x:c r="F141" s="8" t="str"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="11" t="str">
+      <x:c r="A142" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B142" s="11" t="n">
+      <x:c r="B142" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C142" s="11" t="str">
+      <x:c r="C142" s="8" t="str">
         <x:v>Risk Analysis</x:v>
       </x:c>
-      <x:c r="D142" s="11" t="str">
+      <x:c r="D142" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Risk%20Analysis</x:v>
       </x:c>
-      <x:c r="E142" s="11" t="str"/>
-      <x:c r="F142" s="11" t="str"/>
+      <x:c r="E142" s="8" t="str"/>
+      <x:c r="F142" s="8" t="str"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="11" t="str">
+      <x:c r="A143" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B143" s="11" t="n">
+      <x:c r="B143" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C143" s="11" t="str">
+      <x:c r="C143" s="8" t="str">
         <x:v>International Journal of Finance &amp; Economics</x:v>
       </x:c>
-      <x:c r="D143" s="11" t="str">
+      <x:c r="D143" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Finance%20%26%20Economics</x:v>
       </x:c>
-      <x:c r="E143" s="11" t="str"/>
-      <x:c r="F143" s="11" t="str"/>
+      <x:c r="E143" s="8" t="str"/>
+      <x:c r="F143" s="8" t="str"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="11" t="str">
+      <x:c r="A144" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B144" s="11" t="n">
+      <x:c r="B144" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C144" s="11" t="str">
+      <x:c r="C144" s="8" t="str">
         <x:v>Quality and Reliability Engineering International</x:v>
       </x:c>
-      <x:c r="D144" s="11" t="str">
+      <x:c r="D144" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Quality%20and%20Reliability%20Engineering%20International</x:v>
       </x:c>
-      <x:c r="E144" s="11" t="str"/>
-      <x:c r="F144" s="11" t="str"/>
+      <x:c r="E144" s="8" t="str"/>
+      <x:c r="F144" s="8" t="str"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="11" t="str">
+      <x:c r="A145" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B145" s="11" t="n">
+      <x:c r="B145" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C145" s="11" t="str">
+      <x:c r="C145" s="8" t="str">
         <x:v>IISE Transactions</x:v>
       </x:c>
-      <x:c r="D145" s="11" t="str">
+      <x:c r="D145" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=IISE%20Transactions</x:v>
       </x:c>
-      <x:c r="E145" s="11" t="str"/>
-      <x:c r="F145" s="11" t="str"/>
+      <x:c r="E145" s="8" t="str"/>
+      <x:c r="F145" s="8" t="str"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="11" t="str">
+      <x:c r="A146" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B146" s="11" t="n">
+      <x:c r="B146" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C146" s="11" t="str">
+      <x:c r="C146" s="8" t="str">
         <x:v>Journal of the Operational Research Society</x:v>
       </x:c>
-      <x:c r="D146" s="11" t="str">
+      <x:c r="D146" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20the%20Operational%20Research%20Society</x:v>
       </x:c>
-      <x:c r="E146" s="11" t="str"/>
-      <x:c r="F146" s="11" t="str"/>
+      <x:c r="E146" s="8" t="str"/>
+      <x:c r="F146" s="8" t="str"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="11" t="str">
+      <x:c r="A147" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B147" s="11" t="n">
+      <x:c r="B147" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C147" s="11" t="str">
+      <x:c r="C147" s="8" t="str">
         <x:v>International Journal of Production Research</x:v>
       </x:c>
-      <x:c r="D147" s="11" t="str">
+      <x:c r="D147" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Production%20Research</x:v>
       </x:c>
-      <x:c r="E147" s="11" t="str"/>
-      <x:c r="F147" s="11" t="str"/>
+      <x:c r="E147" s="8" t="str"/>
+      <x:c r="F147" s="8" t="str"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="11" t="str">
+      <x:c r="A148" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B148" s="11" t="n">
+      <x:c r="B148" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C148" s="11" t="str">
+      <x:c r="C148" s="8" t="str">
         <x:v>International Journal of Systems Science</x:v>
       </x:c>
-      <x:c r="D148" s="11" t="str">
+      <x:c r="D148" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Systems%20Science</x:v>
       </x:c>
-      <x:c r="E148" s="11" t="str"/>
-      <x:c r="F148" s="11" t="str"/>
+      <x:c r="E148" s="8" t="str"/>
+      <x:c r="F148" s="8" t="str"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="11" t="str">
+      <x:c r="A149" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B149" s="11" t="n">
+      <x:c r="B149" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C149" s="11" t="str">
+      <x:c r="C149" s="8" t="str">
         <x:v>International Journal of General Systems</x:v>
       </x:c>
-      <x:c r="D149" s="11" t="str">
+      <x:c r="D149" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20General%20Systems</x:v>
       </x:c>
-      <x:c r="E149" s="11" t="str"/>
-      <x:c r="F149" s="11" t="str"/>
+      <x:c r="E149" s="8" t="str"/>
+      <x:c r="F149" s="8" t="str"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="11" t="str">
+      <x:c r="A150" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B150" s="11" t="n">
+      <x:c r="B150" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C150" s="11" t="str">
+      <x:c r="C150" s="8" t="str">
         <x:v>International Journal of Information Technology &amp; Decision Making</x:v>
       </x:c>
-      <x:c r="D150" s="11" t="str">
+      <x:c r="D150" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Information%20Technology%20%26%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E150" s="11" t="str"/>
-      <x:c r="F150" s="11" t="str"/>
+      <x:c r="E150" s="8" t="str"/>
+      <x:c r="F150" s="8" t="str"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="11" t="str">
+      <x:c r="A151" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B151" s="11" t="n">
+      <x:c r="B151" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C151" s="11" t="str">
+      <x:c r="C151" s="8" t="str">
         <x:v>International Journal of Uncertainty, Fuzziness and Knowledge-Based Systems</x:v>
       </x:c>
-      <x:c r="D151" s="11" t="str">
+      <x:c r="D151" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Uncertainty%2C%20Fuzziness%20and%20Knowledge-Based%20Systems</x:v>
       </x:c>
-      <x:c r="E151" s="11" t="str"/>
-      <x:c r="F151" s="11" t="str"/>
+      <x:c r="E151" s="8" t="str"/>
+      <x:c r="F151" s="8" t="str"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="11" t="str">
+      <x:c r="A152" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B152" s="11" t="n">
+      <x:c r="B152" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C152" s="11" t="str">
+      <x:c r="C152" s="8" t="str">
         <x:v>Asia-Pacific Journal of Operational Research</x:v>
       </x:c>
-      <x:c r="D152" s="11" t="str">
+      <x:c r="D152" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=Asia-Pacific%20Journal%20of%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E152" s="11" t="str"/>
-      <x:c r="F152" s="11" t="str"/>
+      <x:c r="E152" s="8" t="str"/>
+      <x:c r="F152" s="8" t="str"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="11" t="str">
+      <x:c r="A153" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B153" s="11" t="n">
+      <x:c r="B153" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C153" s="11" t="str">
+      <x:c r="C153" s="8" t="str">
         <x:v>Economic Research</x:v>
       </x:c>
-      <x:c r="D153" s="11" t="str">
+      <x:c r="D153" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Economic%20Research</x:v>
       </x:c>
-      <x:c r="E153" s="11" t="str"/>
-      <x:c r="F153" s="11" t="str"/>
+      <x:c r="E153" s="8" t="str"/>
+      <x:c r="F153" s="8" t="str"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="11" t="str">
+      <x:c r="A154" s="8" t="str">
         <x:v>Wiley/Taylor/WorldScientific</x:v>
       </x:c>
-      <x:c r="B154" s="11" t="n">
+      <x:c r="B154" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C154" s="11" t="str">
+      <x:c r="C154" s="8" t="str">
         <x:v>Journal of Management Analytics</x:v>
       </x:c>
-      <x:c r="D154" s="11" t="str">
+      <x:c r="D154" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Management%20Analytics</x:v>
       </x:c>
-      <x:c r="E154" s="11" t="str"/>
-      <x:c r="F154" s="11" t="str"/>
+      <x:c r="E154" s="8" t="str"/>
+      <x:c r="F154" s="8" t="str"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="11" t="str">
+      <x:c r="A155" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B155" s="11" t="n">
+      <x:c r="B155" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C155" s="11" t="str">
+      <x:c r="C155" s="8" t="str">
         <x:v>International Journal of Computational Intelligence Systems</x:v>
       </x:c>
-      <x:c r="D155" s="11" t="str">
+      <x:c r="D155" s="8" t="str">
         <x:v>https://www.springer.com/search?query=International%20Journal%20of%20Computational%20Intelligence%20Systems</x:v>
       </x:c>
-      <x:c r="E155" s="11" t="str"/>
-      <x:c r="F155" s="11" t="str"/>
+      <x:c r="E155" s="8" t="str"/>
+      <x:c r="F155" s="8" t="str"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="11" t="str">
+      <x:c r="A156" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B156" s="11" t="n">
+      <x:c r="B156" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C156" s="11" t="str">
+      <x:c r="C156" s="8" t="str">
         <x:v>Technological and Economic Development of Economy</x:v>
       </x:c>
-      <x:c r="D156" s="11" t="str">
-        <x:v>https://journals.vgtu.lt</x:v>
-      </x:c>
-      <x:c r="E156" s="11" t="str"/>
-      <x:c r="F156" s="11" t="str"/>
+      <x:c r="D156" s="8" t="str">
+        <x:v>https://journals.vilniustech.lt/index.php?search=Technological%20and%20Economic%20Development%20of%20Economy</x:v>
+      </x:c>
+      <x:c r="E156" s="8" t="str">
+        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
+      </x:c>
+      <x:c r="F156" s="8" t="str"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="11" t="str">
+      <x:c r="A157" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B157" s="11" t="n">
+      <x:c r="B157" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C157" s="11" t="str">
+      <x:c r="C157" s="8" t="str">
         <x:v>INFORMATICA</x:v>
       </x:c>
-      <x:c r="D157" s="11" t="str">
+      <x:c r="D157" s="8" t="str">
         <x:v>https://informatica.vu.lt</x:v>
       </x:c>
-      <x:c r="E157" s="11" t="str"/>
-      <x:c r="F157" s="11" t="str"/>
+      <x:c r="E157" s="8" t="str"/>
+      <x:c r="F157" s="8" t="str"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="11" t="str">
+      <x:c r="A158" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B158" s="11" t="n">
+      <x:c r="B158" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C158" s="11" t="str">
+      <x:c r="C158" s="8" t="str">
         <x:v>International Journal of Computers Communications &amp; Control</x:v>
       </x:c>
-      <x:c r="D158" s="11" t="str">
+      <x:c r="D158" s="8" t="str">
         <x:v>https://univagora.ro</x:v>
       </x:c>
-      <x:c r="E158" s="11" t="str"/>
-      <x:c r="F158" s="11" t="str"/>
+      <x:c r="E158" s="8" t="str"/>
+      <x:c r="F158" s="8" t="str"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="11" t="str">
+      <x:c r="A159" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B159" s="11" t="n">
+      <x:c r="B159" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C159" s="11" t="str">
+      <x:c r="C159" s="8" t="str">
         <x:v>International Journal of Strategic Property Management</x:v>
       </x:c>
-      <x:c r="D159" s="11" t="str">
-        <x:v>https://journals.vgtu.lt</x:v>
-      </x:c>
-      <x:c r="E159" s="11" t="str"/>
-      <x:c r="F159" s="11" t="str"/>
+      <x:c r="D159" s="8" t="str">
+        <x:v>https://journals.vilniustech.lt/index.php?search=International%20Journal%20of%20Strategic%20Property%20Management</x:v>
+      </x:c>
+      <x:c r="E159" s="8" t="str">
+        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
+      </x:c>
+      <x:c r="F159" s="8" t="str"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="11" t="str">
+      <x:c r="A160" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B160" s="11" t="n">
+      <x:c r="B160" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C160" s="11" t="str">
+      <x:c r="C160" s="8" t="str">
         <x:v>Transport</x:v>
       </x:c>
-      <x:c r="D160" s="11" t="str">
-        <x:v>https://journals.vgtu.lt</x:v>
-      </x:c>
-      <x:c r="E160" s="11" t="str"/>
-      <x:c r="F160" s="11" t="str"/>
+      <x:c r="D160" s="8" t="str">
+        <x:v>https://journals.vilniustech.lt/index.php?search=Transport</x:v>
+      </x:c>
+      <x:c r="E160" s="8" t="str">
+        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
+      </x:c>
+      <x:c r="F160" s="8" t="str"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="11" t="str">
+      <x:c r="A161" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B161" s="11" t="n">
+      <x:c r="B161" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C161" s="11" t="str">
+      <x:c r="C161" s="8" t="str">
         <x:v>Transformations in Business &amp; Economics</x:v>
       </x:c>
-      <x:c r="D161" s="11" t="str">
+      <x:c r="D161" s="8" t="str">
         <x:v>https://www.transformations.knf.vu.lt</x:v>
       </x:c>
-      <x:c r="E161" s="11" t="str"/>
-      <x:c r="F161" s="11" t="str"/>
+      <x:c r="E161" s="8" t="str"/>
+      <x:c r="F161" s="8" t="str"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="11" t="str">
+      <x:c r="A162" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B162" s="11" t="n">
+      <x:c r="B162" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C162" s="11" t="str">
+      <x:c r="C162" s="8" t="str">
         <x:v>Scientia Iranica</x:v>
       </x:c>
-      <x:c r="D162" s="11" t="str">
+      <x:c r="D162" s="8" t="str">
         <x:v>https://scientiairanica.sharif.edu</x:v>
       </x:c>
-      <x:c r="E162" s="11" t="str"/>
-      <x:c r="F162" s="11" t="str"/>
+      <x:c r="E162" s="8" t="str"/>
+      <x:c r="F162" s="8" t="str"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="11" t="str">
+      <x:c r="A163" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B163" s="11" t="n">
+      <x:c r="B163" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C163" s="11" t="str">
+      <x:c r="C163" s="8" t="str">
         <x:v>Iranian Journal of Fuzzy Systems</x:v>
       </x:c>
-      <x:c r="D163" s="11" t="str">
+      <x:c r="D163" s="8" t="str">
         <x:v>https://ijfs.usb.ac.ir</x:v>
       </x:c>
-      <x:c r="E163" s="11" t="str"/>
-      <x:c r="F163" s="11" t="str"/>
+      <x:c r="E163" s="8" t="str"/>
+      <x:c r="F163" s="8" t="str"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="11" t="str">
+      <x:c r="A164" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B164" s="11" t="n">
+      <x:c r="B164" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C164" s="11" t="str">
+      <x:c r="C164" s="8" t="str">
         <x:v>Kybernetes</x:v>
       </x:c>
-      <x:c r="D164" s="11" t="str">
+      <x:c r="D164" s="8" t="str">
         <x:v>https://www.emerald.com/insight/search?q=Kybernetes</x:v>
       </x:c>
-      <x:c r="E164" s="11" t="str"/>
-      <x:c r="F164" s="11" t="str"/>
+      <x:c r="E164" s="8" t="str"/>
+      <x:c r="F164" s="8" t="str"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="11" t="str">
+      <x:c r="A165" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B165" s="11" t="n">
+      <x:c r="B165" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C165" s="11" t="str">
+      <x:c r="C165" s="8" t="str">
         <x:v>Intelligent Decision Technologies</x:v>
       </x:c>
-      <x:c r="D165" s="11" t="str">
+      <x:c r="D165" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Decision%20Technologies</x:v>
       </x:c>
-      <x:c r="E165" s="11" t="str"/>
-      <x:c r="F165" s="11" t="str"/>
+      <x:c r="E165" s="8" t="str"/>
+      <x:c r="F165" s="8" t="str"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="11" t="str">
+      <x:c r="A166" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B166" s="11" t="n">
+      <x:c r="B166" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C166" s="11" t="str">
+      <x:c r="C166" s="8" t="str">
         <x:v>Fundamenta Informaticae</x:v>
       </x:c>
-      <x:c r="D166" s="11" t="str">
+      <x:c r="D166" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Fundamenta%20Informaticae</x:v>
       </x:c>
-      <x:c r="E166" s="11" t="str"/>
-      <x:c r="F166" s="11" t="str"/>
+      <x:c r="E166" s="8" t="str"/>
+      <x:c r="F166" s="8" t="str"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="11" t="str">
+      <x:c r="A167" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B167" s="11" t="n">
+      <x:c r="B167" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C167" s="11" t="str">
+      <x:c r="C167" s="8" t="str">
         <x:v>Intelligent Data Analysis</x:v>
       </x:c>
-      <x:c r="D167" s="11" t="str">
+      <x:c r="D167" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Data%20Analysis</x:v>
       </x:c>
-      <x:c r="E167" s="11" t="str"/>
-      <x:c r="F167" s="11" t="str"/>
+      <x:c r="E167" s="8" t="str"/>
+      <x:c r="F167" s="8" t="str"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="11" t="str">
+      <x:c r="A168" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B168" s="11" t="n">
+      <x:c r="B168" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C168" s="11" t="str">
+      <x:c r="C168" s="8" t="str">
         <x:v>Journal of Smart Environments and Green Computing</x:v>
       </x:c>
-      <x:c r="D168" s="11" t="str">
+      <x:c r="D168" s="8" t="str">
         <x:v>https://segcjournal.com</x:v>
       </x:c>
-      <x:c r="E168" s="11" t="str"/>
-      <x:c r="F168" s="11" t="str"/>
+      <x:c r="E168" s="8" t="str"/>
+      <x:c r="F168" s="8" t="str"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="11" t="str">
+      <x:c r="A169" s="8" t="str">
         <x:v>Others</x:v>
       </x:c>
-      <x:c r="B169" s="11" t="n">
+      <x:c r="B169" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C169" s="11" t="str">
+      <x:c r="C169" s="8" t="str">
         <x:v>Journal of Civil Engineering and Management</x:v>
       </x:c>
-      <x:c r="D169" s="11" t="str">
-        <x:v>https://journals.vgtu.lt</x:v>
-      </x:c>
-      <x:c r="E169" s="11" t="str"/>
-      <x:c r="F169" s="11" t="str"/>
+      <x:c r="D169" s="8" t="str">
+        <x:v>https://journals.vilniustech.lt/index.php?search=Journal%20of%20Civil%20Engineering%20and%20Management</x:v>
+      </x:c>
+      <x:c r="E169" s="8" t="str">
+        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
+      </x:c>
+      <x:c r="F169" s="8" t="str"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="11" t="str">
+      <x:c r="A170" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B170" s="11" t="n">
+      <x:c r="B170" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C170" s="11" t="str">
+      <x:c r="C170" s="8" t="str">
         <x:v>管理科学学报</x:v>
       </x:c>
-      <x:c r="D170" s="11" t="str">
+      <x:c r="D170" s="8" t="str">
         <x:v>http://jmsc.tju.edu.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E170" s="11" t="str">
+      <x:c r="E170" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8LJ05z2WKBaal83R1aZsKHhDdcfMpx3UBz-GfhJW-s7MsP1nXNGVxV1DUmvt3bqyaob8lhOefEDtskNzOE_2EpC2gCrA_8RJXiGWDTI_iUNA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F170" s="11" t="str"/>
+      <x:c r="F170" s="8" t="str"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="11" t="str">
+      <x:c r="A171" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B171" s="11" t="n">
+      <x:c r="B171" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C171" s="11" t="str">
+      <x:c r="C171" s="8" t="str">
         <x:v>系统工程理论与实践</x:v>
       </x:c>
-      <x:c r="D171" s="11" t="str">
+      <x:c r="D171" s="8" t="str">
         <x:v>http://www.sysengi.com/</x:v>
       </x:c>
-      <x:c r="E171" s="11" t="str">
+      <x:c r="E171" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=i3PX7_dq32X2Zk0vdxkR-ODkxN-nI3yF4njbEspRx73Nm7WAR7J-vcwM0_OoNx8FEvxGLJCXasn3KAcQ0RARebKAq4xD1pgviZ0U7vSuBvfNMhDxzEeSoA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F171" s="11" t="str"/>
+      <x:c r="F171" s="8" t="str"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="11" t="str">
+      <x:c r="A172" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B172" s="11" t="n">
+      <x:c r="B172" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C172" s="11" t="str">
+      <x:c r="C172" s="8" t="str">
         <x:v>管理世界</x:v>
       </x:c>
-      <x:c r="D172" s="11" t="str">
+      <x:c r="D172" s="8" t="str">
         <x:v>http://www.mwm.net.cn/web/</x:v>
       </x:c>
-      <x:c r="E172" s="11" t="str">
+      <x:c r="E172" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9bPeMF52gorOhVMoCTm_bP4JUtgupb_E88sMy-gsXzFr1P8lBB8uHZukD4Te4RdLMKnj45i1j1MNnPQo45WRUOuqkrMgwUszODdbOWIRUqkg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F172" s="11" t="str"/>
+      <x:c r="F172" s="8" t="str"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="11" t="str">
+      <x:c r="A173" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B173" s="11" t="n">
+      <x:c r="B173" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C173" s="11" t="str">
+      <x:c r="C173" s="8" t="str">
         <x:v>中国管理科学</x:v>
       </x:c>
-      <x:c r="D173" s="11" t="str">
+      <x:c r="D173" s="8" t="str">
         <x:v>http://www.zgglkx.com</x:v>
       </x:c>
-      <x:c r="E173" s="11" t="str">
+      <x:c r="E173" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-JU_du0-bK0lg27F1Oi8b1cNGusZwUOwac7P02Y1arLcSfkZu0L8ZB1IJhn7Fj80XDx2f9_sQ5r3G6IQgpyTe3Y_JDssEju9qAhMsGw3X0qw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F173" s="11" t="str"/>
+      <x:c r="F173" s="8" t="str"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="11" t="str">
+      <x:c r="A174" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B174" s="11" t="n">
+      <x:c r="B174" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C174" s="11" t="str">
+      <x:c r="C174" s="8" t="str">
         <x:v>系统工程学报</x:v>
       </x:c>
-      <x:c r="D174" s="11" t="str">
+      <x:c r="D174" s="8" t="str">
         <x:v>http://jse.tju.edu.cn</x:v>
       </x:c>
-      <x:c r="E174" s="11" t="str">
+      <x:c r="E174" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-NWam7tarWG4WxmWSs2_tcqdiLEz4i3KVdQbtnKLITej4vXhwHRR3aDau0yw8d_IavznXlO9dN3zYuKL_de5S7p2u36GqLdzMfHA3Wg9Wx0w==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F174" s="11" t="str"/>
+      <x:c r="F174" s="8" t="str"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="11" t="str">
+      <x:c r="A175" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B175" s="11" t="n">
+      <x:c r="B175" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C175" s="11" t="str">
+      <x:c r="C175" s="8" t="str">
         <x:v>系统管理学报</x:v>
       </x:c>
-      <x:c r="D175" s="11" t="str">
+      <x:c r="D175" s="8" t="str">
         <x:v>http://xtglxb.sjtu.edu.cn/</x:v>
       </x:c>
-      <x:c r="E175" s="11" t="str">
+      <x:c r="E175" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9URZHjnjpZNx894uUc8hEV_8y-XaWbYy_QQKZwrmUaOuHU_Ulmiyfu5w84oSoQ8OSwjHPBK4vEcFxdVksfIHxNuv4CL8S5HTYziOHdCIpK2w==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F175" s="11" t="str"/>
+      <x:c r="F175" s="8" t="str"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="11" t="str">
+      <x:c r="A176" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B176" s="11" t="n">
+      <x:c r="B176" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C176" s="11" t="str">
+      <x:c r="C176" s="8" t="str">
         <x:v>管理科学</x:v>
       </x:c>
-      <x:c r="D176" s="11" t="str">
+      <x:c r="D176" s="8" t="str">
         <x:v>http://glkx.hit.edu.cn/glkxcn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E176" s="11" t="str">
+      <x:c r="E176" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_ZE6E2FOt_BwppB5uBeXQErN0I5kVHOud5T_DbHM98apuHBLYdN4agXMpq5m9CZr4pnZE4hFnsyANk-8DWJ3fFUdWzB2oij7TzlVIKAxfF6A==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F176" s="11" t="str"/>
+      <x:c r="F176" s="8" t="str"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="11" t="str">
+      <x:c r="A177" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B177" s="11" t="n">
+      <x:c r="B177" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C177" s="11" t="str">
+      <x:c r="C177" s="8" t="str">
         <x:v>管理评论</x:v>
       </x:c>
-      <x:c r="D177" s="11" t="str">
+      <x:c r="D177" s="8" t="str">
         <x:v>http://www.glplzz.com/</x:v>
       </x:c>
-      <x:c r="E177" s="11" t="str">
+      <x:c r="E177" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-TCsOxvxdXdlSvw79gRfLC3Qs4Zx8pWINWUiL6dgoj_PFvNjjxeJ-IodjHg3dspx0OB_4yj_j_2YdtzhxiYvBKymQM3Mm052AZyEPIfen2cA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F177" s="11" t="str"/>
+      <x:c r="F177" s="8" t="str"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="11" t="str">
+      <x:c r="A178" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B178" s="11" t="n">
+      <x:c r="B178" s="8" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C178" s="11" t="str">
+      <x:c r="C178" s="8" t="str">
         <x:v>管理工程学报</x:v>
       </x:c>
-      <x:c r="D178" s="11" t="str">
+      <x:c r="D178" s="8" t="str">
         <x:v>http://glgcxb.zju.edu.cn/</x:v>
       </x:c>
-      <x:c r="E178" s="11" t="str">
+      <x:c r="E178" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</x:v>
       </x:c>
-      <x:c r="F178" s="11" t="str"/>
+      <x:c r="F178" s="8" t="str"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="11" t="str">
+      <x:c r="A179" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B179" s="11" t="n">
+      <x:c r="B179" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C179" s="11" t="str">
+      <x:c r="C179" s="8" t="str">
         <x:v>南开管理评论</x:v>
       </x:c>
-      <x:c r="D179" s="11" t="str">
+      <x:c r="D179" s="8" t="str">
         <x:v>http://www.nbronline.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E179" s="11" t="str">
+      <x:c r="E179" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F179" s="11" t="str"/>
+      <x:c r="F179" s="8" t="str"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="11" t="str">
+      <x:c r="A180" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B180" s="11" t="n">
+      <x:c r="B180" s="8" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C180" s="11" t="str">
+      <x:c r="C180" s="8" t="str">
         <x:v>科研管理</x:v>
       </x:c>
-      <x:c r="D180" s="11" t="str">
+      <x:c r="D180" s="8" t="str">
         <x:v>http://www.kygl.net.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E180" s="11" t="str">
+      <x:c r="E180" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F180" s="11" t="str"/>
+      <x:c r="F180" s="8" t="str"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="11" t="str">
+      <x:c r="A181" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B181" s="11" t="n">
+      <x:c r="B181" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C181" s="11" t="str">
+      <x:c r="C181" s="8" t="str">
         <x:v>情报学报</x:v>
       </x:c>
-      <x:c r="D181" s="11" t="str">
+      <x:c r="D181" s="8" t="str">
         <x:v>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</x:v>
       </x:c>
-      <x:c r="E181" s="11" t="str">
+      <x:c r="E181" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F181" s="11" t="str"/>
+      <x:c r="F181" s="8" t="str"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="11" t="str">
+      <x:c r="A182" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B182" s="11" t="n">
+      <x:c r="B182" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C182" s="11" t="str">
+      <x:c r="C182" s="8" t="str">
         <x:v>工程管理科技前沿</x:v>
       </x:c>
-      <x:c r="D182" s="11" t="str">
+      <x:c r="D182" s="8" t="str">
         <x:v>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="E182" s="11" t="str">
+      <x:c r="E182" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F182" s="11" t="str"/>
+      <x:c r="F182" s="8" t="str"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="11" t="str">
+      <x:c r="A183" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B183" s="11" t="n">
+      <x:c r="B183" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C183" s="11" t="str">
+      <x:c r="C183" s="8" t="str">
         <x:v>运筹与管理</x:v>
       </x:c>
-      <x:c r="D183" s="11" t="str">
+      <x:c r="D183" s="8" t="str">
         <x:v>http://www.jorms.net/CN/1007-3221/home.shtml</x:v>
       </x:c>
-      <x:c r="E183" s="11" t="str">
+      <x:c r="E183" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</x:v>
       </x:c>
-      <x:c r="F183" s="11" t="str"/>
+      <x:c r="F183" s="8" t="str"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="11" t="str">
+      <x:c r="A184" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B184" s="11" t="n">
+      <x:c r="B184" s="8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C184" s="11" t="str">
+      <x:c r="C184" s="8" t="str">
         <x:v>管理学报</x:v>
       </x:c>
-      <x:c r="D184" s="11" t="str">
+      <x:c r="D184" s="8" t="str">
         <x:v>http://manu68.magtech.com.cn/Jwk_glxb/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E184" s="11" t="str">
+      <x:c r="E184" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8PCnUrD8saRufeUaB7vvWh8ImJB4HeHNeLqW0ePwzGyEPNRCnQsHlbFXGOlO-wcTfqZgKY4hDwsLs-3Tn89zOBbGtw1AAMZyEw5PPM6laErQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F184" s="11" t="str"/>
+      <x:c r="F184" s="8" t="str"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="11" t="str">
+      <x:c r="A185" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B185" s="11" t="n">
+      <x:c r="B185" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C185" s="11" t="str">
+      <x:c r="C185" s="8" t="str">
         <x:v>工业工程与管理</x:v>
       </x:c>
-      <x:c r="D185" s="11" t="str">
+      <x:c r="D185" s="8" t="str">
         <x:v>https://gygc.cbpt.cnki.net/WKB2/WebPublication/index.aspx?mid=gygc</x:v>
       </x:c>
-      <x:c r="E185" s="11" t="str">
+      <x:c r="E185" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8br7MgEIcFYMQt_ZJBi4Gq5howJvAAN2q5Uw-jRJpkwA6seBfU1WclQ4xGDeYNZADI68ojMDuwRNLC-W9Dialui-wgcg5tuYIT8ESNZSpaSQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F185" s="11" t="str"/>
+      <x:c r="F185" s="8" t="str"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="11" t="str">
+      <x:c r="A186" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B186" s="11" t="n">
+      <x:c r="B186" s="8" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C186" s="11" t="str">
+      <x:c r="C186" s="8" t="str">
         <x:v>系统工程</x:v>
       </x:c>
-      <x:c r="D186" s="11" t="str">
+      <x:c r="D186" s="8" t="str">
         <x:v>http://www.xitonggongcheng.cn/</x:v>
       </x:c>
-      <x:c r="E186" s="11" t="str">
+      <x:c r="E186" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ521dERQpzlafVK7qGUOU45RpQBLI3a7dqVm6V_hSwqA5HQ==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F186" s="11" t="str"/>
+      <x:c r="F186" s="8" t="str"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="11" t="str">
+      <x:c r="A187" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B187" s="11" t="n">
+      <x:c r="B187" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C187" s="11" t="str">
+      <x:c r="C187" s="8" t="str">
         <x:v>控制与决策</x:v>
       </x:c>
-      <x:c r="D187" s="11" t="str">
+      <x:c r="D187" s="8" t="str">
         <x:v>http://kzyjc.alljournals.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E187" s="11" t="str">
+      <x:c r="E187" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9VMm0YxN4tX5yL-EVnsT6PAjZVl9XwIKssVo1NvBga91FGUvekhWuNlMQI0JER059BEkpPkSf2yKf-gU-zpBPmAP0aZmcjFXxTBOO3l4T0hA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F187" s="11" t="str"/>
+      <x:c r="F187" s="8" t="str"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="11" t="str">
+      <x:c r="A188" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B188" s="11" t="n">
+      <x:c r="B188" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C188" s="11" t="str">
+      <x:c r="C188" s="8" t="str">
         <x:v>系统工程与电子技术</x:v>
       </x:c>
-      <x:c r="D188" s="11" t="str">
+      <x:c r="D188" s="8" t="str">
         <x:v>http://www.sys-ele.com/CN/1001-506X/home.shtml</x:v>
       </x:c>
-      <x:c r="E188" s="11" t="str">
+      <x:c r="E188" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ522XKppJFMLpkDt0YeID7jzeew3YqHq1UltKzV8MACc98A==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F188" s="11" t="str"/>
+      <x:c r="F188" s="8" t="str"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="11" t="str">
+      <x:c r="A189" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B189" s="11" t="n">
+      <x:c r="B189" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C189" s="11" t="str">
+      <x:c r="C189" s="8" t="str">
         <x:v>中国软科学</x:v>
       </x:c>
-      <x:c r="D189" s="11" t="str">
+      <x:c r="D189" s="8" t="str">
         <x:v>http://www.cssm.com.cn/ch/index.aspx</x:v>
       </x:c>
-      <x:c r="E189" s="11" t="str">
+      <x:c r="E189" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8jySLJU_283KXns0m8yNk0Ce8rmtobTme-1MViCCKsbzSynAlfsvvxkGahZxy_URE-jKLwH5grOgRQ7kKV0KBnSC88LYojIfsOG5GxO7NKdg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F189" s="11" t="str"/>
+      <x:c r="F189" s="8" t="str"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="11" t="str">
+      <x:c r="A190" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B190" s="11" t="n">
+      <x:c r="B190" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C190" s="11" t="str">
+      <x:c r="C190" s="8" t="str">
         <x:v>系统科学与数学</x:v>
       </x:c>
-      <x:c r="D190" s="11" t="str">
+      <x:c r="D190" s="8" t="str">
         <x:v>http://sysmath.com/jweb_xtkxysx</x:v>
       </x:c>
-      <x:c r="E190" s="11" t="str">
+      <x:c r="E190" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-E-p5hVM-T-2-bewhhYzlPKidJWYOorDi1B-PITMAbOL0S7cekgijFCS0nSXq4XQNKt1GbaW3S6VWjdbpFqoGY_EIIuekH5mr8rxzI_HrR7g==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F190" s="11" t="str"/>
+      <x:c r="F190" s="8" t="str"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="11" t="str">
+      <x:c r="A191" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B191" s="11" t="n">
+      <x:c r="B191" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C191" s="11" t="str">
+      <x:c r="C191" s="8" t="str">
         <x:v>计量经济学报</x:v>
       </x:c>
-      <x:c r="D191" s="11" t="str">
+      <x:c r="D191" s="8" t="str">
         <x:v>http://www.cjoe.ac.cn/CN/2096-9732/home.shtml</x:v>
       </x:c>
-      <x:c r="E191" s="11" t="str">
+      <x:c r="E191" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9O7KTOAqVcVsRDT7MmQLR8XCOwVreqgSqoJ_mGw8hFdrvny_-zVG3nRwmEQnA8E_SpxQeLOkYd7CxfbKQuxDeda_UEYUS14oC9RQJGSD6dYg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F191" s="11" t="str"/>
+      <x:c r="F191" s="8" t="str"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="11" t="str">
+      <x:c r="A192" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B192" s="11" t="n">
+      <x:c r="B192" s="8" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C192" s="11" t="str">
+      <x:c r="C192" s="8" t="str">
         <x:v>自动化学报</x:v>
       </x:c>
-      <x:c r="D192" s="11" t="str">
+      <x:c r="D192" s="8" t="str">
         <x:v>http://www.aas.net.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E192" s="11" t="str">
+      <x:c r="E192" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_KyFB5Et1OillJwmuopCWBj5pdqWDmDRaudYAq4j6C1SQ8RskmxnZJipOZnXxhDK_wNDwDjzo_dILEkzq7JyCDiG26p2JrBu__1dKfqF0Hug==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F192" s="11" t="str"/>
+      <x:c r="F192" s="8" t="str"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="11" t="str">
+      <x:c r="A193" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B193" s="11" t="n">
+      <x:c r="B193" s="8" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C193" s="11" t="str">
+      <x:c r="C193" s="8" t="str">
         <x:v>计算机学报</x:v>
       </x:c>
-      <x:c r="D193" s="11" t="str">
+      <x:c r="D193" s="8" t="str">
         <x:v>http://cjc.ict.ac.cn/</x:v>
       </x:c>
-      <x:c r="E193" s="11" t="str">
+      <x:c r="E193" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9_vxQO77UEmThRI7mhs7_u-tPwE_PVKzc0Y8BhMYBHTzr98uiHz_J7VQEcj0zQgQD69gziJmOh-Y7_MS0eWzVrjAi2cxJHj4AyA5FLhECB7Q==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F193" s="11" t="str"/>
+      <x:c r="F193" s="8" t="str"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="11" t="str">
+      <x:c r="A194" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B194" s="11" t="n">
+      <x:c r="B194" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C194" s="11" t="str">
+      <x:c r="C194" s="8" t="str">
         <x:v>计算机研究与发展</x:v>
       </x:c>
-      <x:c r="D194" s="11" t="str">
+      <x:c r="D194" s="8" t="str">
         <x:v>http://crad.ict.ac.cn/</x:v>
       </x:c>
-      <x:c r="E194" s="11" t="str">
+      <x:c r="E194" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8lGm60BT1S32qMmgQriP9uZ2ShOTZe4_8yW-QQYDij87AjrNp9M_13YGgNGlrNwq-vJCQhJ1KyL0VCjz5laN36JY4u-_EtYQc2NFnjQlP6wg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F194" s="11" t="str"/>
+      <x:c r="F194" s="8" t="str"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="11" t="str">
+      <x:c r="A195" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B195" s="11" t="n">
+      <x:c r="B195" s="8" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C195" s="11" t="str">
+      <x:c r="C195" s="8" t="str">
         <x:v>电子学报</x:v>
       </x:c>
-      <x:c r="D195" s="11" t="str">
+      <x:c r="D195" s="8" t="str">
         <x:v>http://www.ejournal.org.cn/CN/volumn/current.shtml</x:v>
       </x:c>
-      <x:c r="E195" s="11" t="str">
+      <x:c r="E195" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/journals/DZXU/detail?uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F195" s="11" t="str"/>
+      <x:c r="F195" s="8" t="str"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="11" t="str">
+      <x:c r="A196" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B196" s="11" t="n">
+      <x:c r="B196" s="8" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C196" s="11" t="str">
+      <x:c r="C196" s="8" t="str">
         <x:v>软件学报</x:v>
       </x:c>
-      <x:c r="D196" s="11" t="str">
+      <x:c r="D196" s="8" t="str">
         <x:v>http://www.jos.org.cn/</x:v>
       </x:c>
-      <x:c r="E196" s="11" t="str">
+      <x:c r="E196" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-eSDBBKMj0vAeZF-smiUXPlDeISBrKFJZZ9arNvuLVDlcERM2YiZPI_j0aeLQpFlrUVoLG0JBQXMun-myIj8mt0fvZymwFzAizMqubrnbCDg==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F196" s="11" t="str"/>
+      <x:c r="F196" s="8" t="str"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="11" t="str">
+      <x:c r="A197" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B197" s="11" t="n">
+      <x:c r="B197" s="8" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C197" s="11" t="str">
+      <x:c r="C197" s="8" t="str">
         <x:v>中国科学: 信息科学</x:v>
       </x:c>
-      <x:c r="D197" s="11" t="str">
+      <x:c r="D197" s="8" t="str">
         <x:v>https://www.sciengine.com/publisher/scp/journal/SSI?slug=firstpublish</x:v>
       </x:c>
-      <x:c r="E197" s="11" t="str">
+      <x:c r="E197" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_wGZ_mUleWCYCON5LbBM4MWv3xigAWN4kttzDDJAGVBd7SeAnjCYVkCmhMZnWmK8p7oIeobAw_ntBHWA0d52ws1dPal6Yqvk_voRKDk5MihA==&amp;uniplatform=NZKPT</x:v>
       </x:c>
-      <x:c r="F197" s="11" t="str"/>
+      <x:c r="F197" s="8" t="str"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="11" t="str">
+      <x:c r="A198" s="8" t="str">
         <x:v>中文期刊</x:v>
       </x:c>
-      <x:c r="B198" s="11" t="n">
+      <x:c r="B198" s="8" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C198" s="11" t="str">
+      <x:c r="C198" s="8" t="str">
         <x:v>数据分析与知识发现</x:v>
       </x:c>
-      <x:c r="D198" s="11" t="str">
+      <x:c r="D198" s="8" t="str">
         <x:v>https://manu44.magtech.com.cn/Jwk_infotech_wk3/CN/2096-3467/home.shtml</x:v>
       </x:c>
-      <x:c r="E198" s="11" t="str">
+      <x:c r="E198" s="8" t="str">
         <x:v>CNKI|https://navi.cnki.net/knavi/journals/XDTQ/detail</x:v>
       </x:c>
-      <x:c r="F198" s="11" t="str"/>
+      <x:c r="F198" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e0fd1e74182431d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e8abb15b2f044f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3497,11 +3544,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="4" t="str">
         <x:v>Category</x:v>
       </x:c>
     </x:row>
@@ -3538,6 +3585,43 @@
     <x:row r="8">
       <x:c r="A8" t="str">
         <x:v>中文期刊</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="80" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>How to update</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>1. Edit the Journals sheet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>2. Keep the Extra Links format as: label|url; label|url</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>3. Run update_journals.bat to regenerate journals.json.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>4. Keep index.html and journals.json in the same folder.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/journal_new/journal_list.xlsx
+++ b/journal_new/journal_list.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Raf7068f8a086440a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="R8dafbf87a6d24777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1558fbe28ad948c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R25c3328df21b44a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" r:id="R49014a5409cb4165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R347ae10d58544aef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -277,7 +277,7 @@
       <x:c r="D2" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str"/>
+      <x:c r="E2" s="8"/>
       <x:c r="F2" s="8" t="str"/>
     </x:row>
     <x:row r="3">
@@ -293,7 +293,7 @@
       <x:c r="D3" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str"/>
+      <x:c r="E3" s="8"/>
       <x:c r="F3" s="8" t="str"/>
     </x:row>
     <x:row r="4">
@@ -309,7 +309,7 @@
       <x:c r="D4" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str"/>
+      <x:c r="E4" s="8"/>
       <x:c r="F4" s="8" t="str"/>
     </x:row>
     <x:row r="5">
@@ -325,7 +325,7 @@
       <x:c r="D5" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str"/>
+      <x:c r="E5" s="8"/>
       <x:c r="F5" s="8" t="str"/>
     </x:row>
     <x:row r="6">
@@ -341,7 +341,7 @@
       <x:c r="D6" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-j-of-operational-research</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str"/>
+      <x:c r="E6" s="8"/>
       <x:c r="F6" s="8" t="str"/>
     </x:row>
     <x:row r="7">
@@ -357,7 +357,7 @@
       <x:c r="D7" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str"/>
+      <x:c r="E7" s="8"/>
       <x:c r="F7" s="8" t="str"/>
     </x:row>
     <x:row r="8">
@@ -373,7 +373,7 @@
       <x:c r="D8" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str"/>
+      <x:c r="E8" s="8"/>
       <x:c r="F8" s="8" t="str"/>
     </x:row>
     <x:row r="9">
@@ -389,7 +389,7 @@
       <x:c r="D9" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str"/>
+      <x:c r="E9" s="8"/>
       <x:c r="F9" s="8" t="str"/>
     </x:row>
     <x:row r="10">
@@ -405,7 +405,7 @@
       <x:c r="D10" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str"/>
+      <x:c r="E10" s="8"/>
       <x:c r="F10" s="8" t="str"/>
     </x:row>
     <x:row r="11">
@@ -421,7 +421,7 @@
       <x:c r="D11" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-approximate-reasoning</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str"/>
+      <x:c r="E11" s="8"/>
       <x:c r="F11" s="8" t="str"/>
     </x:row>
     <x:row r="12">
@@ -437,7 +437,7 @@
       <x:c r="D12" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/int-j-of-production-economics</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="str"/>
+      <x:c r="E12" s="8"/>
       <x:c r="F12" s="8" t="str"/>
     </x:row>
     <x:row r="13">
@@ -453,7 +453,7 @@
       <x:c r="D13" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems</x:v>
       </x:c>
-      <x:c r="E13" s="8" t="str"/>
+      <x:c r="E13" s="8"/>
       <x:c r="F13" s="8" t="str"/>
     </x:row>
     <x:row r="14">
@@ -469,7 +469,7 @@
       <x:c r="D14" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega</x:v>
       </x:c>
-      <x:c r="E14" s="8" t="str"/>
+      <x:c r="E14" s="8"/>
       <x:c r="F14" s="8" t="str"/>
     </x:row>
     <x:row r="15">
@@ -485,7 +485,7 @@
       <x:c r="D15" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="str"/>
+      <x:c r="E15" s="8"/>
       <x:c r="F15" s="8" t="str"/>
     </x:row>
     <x:row r="16">
@@ -501,7 +501,7 @@
       <x:c r="D16" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="str"/>
+      <x:c r="E16" s="8"/>
       <x:c r="F16" s="8" t="str"/>
     </x:row>
     <x:row r="17">
@@ -517,7 +517,7 @@
       <x:c r="D17" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications</x:v>
       </x:c>
-      <x:c r="E17" s="8" t="str"/>
+      <x:c r="E17" s="8"/>
       <x:c r="F17" s="8" t="str"/>
     </x:row>
     <x:row r="18">
@@ -533,7 +533,7 @@
       <x:c r="D18" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting</x:v>
       </x:c>
-      <x:c r="E18" s="8" t="str"/>
+      <x:c r="E18" s="8"/>
       <x:c r="F18" s="8" t="str"/>
     </x:row>
     <x:row r="19">
@@ -549,7 +549,7 @@
       <x:c r="D19" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management</x:v>
       </x:c>
-      <x:c r="E19" s="8" t="str"/>
+      <x:c r="E19" s="8"/>
       <x:c r="F19" s="8" t="str"/>
     </x:row>
     <x:row r="20">
@@ -565,7 +565,7 @@
       <x:c r="D20" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems</x:v>
       </x:c>
-      <x:c r="E20" s="8" t="str"/>
+      <x:c r="E20" s="8"/>
       <x:c r="F20" s="8" t="str"/>
     </x:row>
     <x:row r="21">
@@ -581,7 +581,7 @@
       <x:c r="D21" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence</x:v>
       </x:c>
-      <x:c r="E21" s="8" t="str"/>
+      <x:c r="E21" s="8"/>
       <x:c r="F21" s="8" t="str"/>
     </x:row>
     <x:row r="22">
@@ -597,7 +597,7 @@
       <x:c r="D22" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition</x:v>
       </x:c>
-      <x:c r="E22" s="8" t="str"/>
+      <x:c r="E22" s="8"/>
       <x:c r="F22" s="8" t="str"/>
     </x:row>
     <x:row r="23">
@@ -613,7 +613,7 @@
       <x:c r="D23" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters</x:v>
       </x:c>
-      <x:c r="E23" s="8" t="str"/>
+      <x:c r="E23" s="8"/>
       <x:c r="F23" s="8" t="str"/>
     </x:row>
     <x:row r="24">
@@ -629,7 +629,7 @@
       <x:c r="D24" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing</x:v>
       </x:c>
-      <x:c r="E24" s="8" t="str"/>
+      <x:c r="E24" s="8"/>
       <x:c r="F24" s="8" t="str"/>
     </x:row>
     <x:row r="25">
@@ -645,7 +645,7 @@
       <x:c r="D25" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a</x:v>
       </x:c>
-      <x:c r="E25" s="8" t="str"/>
+      <x:c r="E25" s="8"/>
       <x:c r="F25" s="8" t="str"/>
     </x:row>
     <x:row r="26">
@@ -661,7 +661,7 @@
       <x:c r="D26" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-cleaner-production</x:v>
       </x:c>
-      <x:c r="E26" s="8" t="str"/>
+      <x:c r="E26" s="8"/>
       <x:c r="F26" s="8" t="str"/>
     </x:row>
     <x:row r="27">
@@ -677,7 +677,7 @@
       <x:c r="D27" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/energy</x:v>
       </x:c>
-      <x:c r="E27" s="8" t="str"/>
+      <x:c r="E27" s="8"/>
       <x:c r="F27" s="8" t="str"/>
     </x:row>
     <x:row r="28">
@@ -693,7 +693,7 @@
       <x:c r="D28" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety</x:v>
       </x:c>
-      <x:c r="E28" s="8" t="str"/>
+      <x:c r="E28" s="8"/>
       <x:c r="F28" s="8" t="str"/>
     </x:row>
     <x:row r="29">
@@ -709,7 +709,7 @@
       <x:c r="D29" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics</x:v>
       </x:c>
-      <x:c r="E29" s="8" t="str"/>
+      <x:c r="E29" s="8"/>
       <x:c r="F29" s="8" t="str"/>
     </x:row>
     <x:row r="30">
@@ -725,7 +725,7 @@
       <x:c r="D30" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open</x:v>
       </x:c>
-      <x:c r="E30" s="8" t="str"/>
+      <x:c r="E30" s="8"/>
       <x:c r="F30" s="8" t="str"/>
     </x:row>
     <x:row r="31">
@@ -741,7 +741,7 @@
       <x:c r="D31" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks</x:v>
       </x:c>
-      <x:c r="E31" s="8" t="str"/>
+      <x:c r="E31" s="8"/>
       <x:c r="F31" s="8" t="str"/>
     </x:row>
     <x:row r="32">
@@ -757,7 +757,7 @@
       <x:c r="D32" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
-      <x:c r="E32" s="8" t="str"/>
+      <x:c r="E32" s="8"/>
       <x:c r="F32" s="8" t="str"/>
     </x:row>
     <x:row r="33">
@@ -773,7 +773,7 @@
       <x:c r="D33" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry</x:v>
       </x:c>
-      <x:c r="E33" s="8" t="str"/>
+      <x:c r="E33" s="8"/>
       <x:c r="F33" s="8" t="str"/>
     </x:row>
     <x:row r="34">
@@ -789,7 +789,7 @@
       <x:c r="D34" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/chaos-solitons-and-fractals</x:v>
       </x:c>
-      <x:c r="E34" s="8" t="str"/>
+      <x:c r="E34" s="8"/>
       <x:c r="F34" s="8" t="str"/>
     </x:row>
     <x:row r="35">
@@ -805,7 +805,7 @@
       <x:c r="D35" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/safety-science</x:v>
       </x:c>
-      <x:c r="E35" s="8" t="str"/>
+      <x:c r="E35" s="8"/>
       <x:c r="F35" s="8" t="str"/>
     </x:row>
     <x:row r="36">
@@ -821,7 +821,7 @@
       <x:c r="D36" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change</x:v>
       </x:c>
-      <x:c r="E36" s="8" t="str"/>
+      <x:c r="E36" s="8"/>
       <x:c r="F36" s="8" t="str"/>
     </x:row>
     <x:row r="37">
@@ -837,7 +837,7 @@
       <x:c r="D37" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/automation-in-construction</x:v>
       </x:c>
-      <x:c r="E37" s="8" t="str"/>
+      <x:c r="E37" s="8"/>
       <x:c r="F37" s="8" t="str"/>
     </x:row>
     <x:row r="38">
@@ -853,7 +853,7 @@
       <x:c r="D38" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/annual-reviews-in-control</x:v>
       </x:c>
-      <x:c r="E38" s="8" t="str"/>
+      <x:c r="E38" s="8"/>
       <x:c r="F38" s="8" t="str"/>
     </x:row>
     <x:row r="39">
@@ -869,7 +869,7 @@
       <x:c r="D39" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-environmental-economics-and-management</x:v>
       </x:c>
-      <x:c r="E39" s="8" t="str"/>
+      <x:c r="E39" s="8"/>
       <x:c r="F39" s="8" t="str"/>
     </x:row>
     <x:row r="40">
@@ -885,7 +885,7 @@
       <x:c r="D40" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services</x:v>
       </x:c>
-      <x:c r="E40" s="8" t="str"/>
+      <x:c r="E40" s="8"/>
       <x:c r="F40" s="8" t="str"/>
     </x:row>
     <x:row r="41">
@@ -901,7 +901,7 @@
       <x:c r="D41" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-series-b-methodological</x:v>
       </x:c>
-      <x:c r="E41" s="8" t="str"/>
+      <x:c r="E41" s="8"/>
       <x:c r="F41" s="8" t="str"/>
     </x:row>
     <x:row r="42">
@@ -917,7 +917,7 @@
       <x:c r="D42" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
-      <x:c r="E42" s="8" t="str"/>
+      <x:c r="E42" s="8"/>
       <x:c r="F42" s="8" t="str"/>
     </x:row>
     <x:row r="43">
@@ -933,7 +933,7 @@
       <x:c r="D43" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
-      <x:c r="E43" s="8" t="str"/>
+      <x:c r="E43" s="8"/>
       <x:c r="F43" s="8" t="str"/>
     </x:row>
     <x:row r="44">
@@ -949,7 +949,7 @@
       <x:c r="D44" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes</x:v>
       </x:c>
-      <x:c r="E44" s="8" t="str"/>
+      <x:c r="E44" s="8"/>
       <x:c r="F44" s="8" t="str"/>
     </x:row>
     <x:row r="45">
@@ -965,7 +965,7 @@
       <x:c r="D45" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management</x:v>
       </x:c>
-      <x:c r="E45" s="8" t="str"/>
+      <x:c r="E45" s="8"/>
       <x:c r="F45" s="8" t="str"/>
     </x:row>
     <x:row r="46">
@@ -981,7 +981,7 @@
       <x:c r="D46" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research</x:v>
       </x:c>
-      <x:c r="E46" s="8" t="str"/>
+      <x:c r="E46" s="8"/>
       <x:c r="F46" s="8" t="str"/>
     </x:row>
     <x:row r="47">
@@ -997,7 +997,7 @@
       <x:c r="D47" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Travel%20Research</x:v>
       </x:c>
-      <x:c r="E47" s="8" t="str"/>
+      <x:c r="E47" s="8"/>
       <x:c r="F47" s="8" t="str"/>
     </x:row>
     <x:row r="48">
@@ -1013,7 +1013,7 @@
       <x:c r="D48" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Service%20Research</x:v>
       </x:c>
-      <x:c r="E48" s="8" t="str"/>
+      <x:c r="E48" s="8"/>
       <x:c r="F48" s="8" t="str"/>
     </x:row>
     <x:row r="49">
@@ -1029,7 +1029,7 @@
       <x:c r="D49" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-hospitality-management</x:v>
       </x:c>
-      <x:c r="E49" s="8" t="str"/>
+      <x:c r="E49" s="8"/>
       <x:c r="F49" s="8" t="str"/>
     </x:row>
     <x:row r="50">
@@ -1045,7 +1045,7 @@
       <x:c r="D50" s="8" t="str">
         <x:v>https://www.emerald.com/insight/search?q=International%20Journal%20of%20Contemporary%20Hospitality%20Management</x:v>
       </x:c>
-      <x:c r="E50" s="8" t="str"/>
+      <x:c r="E50" s="8"/>
       <x:c r="F50" s="8" t="str"/>
     </x:row>
     <x:row r="51">
@@ -1061,7 +1061,7 @@
       <x:c r="D51" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Sustainable%20Tourism</x:v>
       </x:c>
-      <x:c r="E51" s="8" t="str"/>
+      <x:c r="E51" s="8"/>
       <x:c r="F51" s="8" t="str"/>
     </x:row>
     <x:row r="52">
@@ -1077,7 +1077,7 @@
       <x:c r="D52" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management-perspectives</x:v>
       </x:c>
-      <x:c r="E52" s="8" t="str"/>
+      <x:c r="E52" s="8"/>
       <x:c r="F52" s="8" t="str"/>
     </x:row>
     <x:row r="53">
@@ -1093,7 +1093,7 @@
       <x:c r="D53" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Current%20Issues%20in%20Tourism</x:v>
       </x:c>
-      <x:c r="E53" s="8" t="str"/>
+      <x:c r="E53" s="8"/>
       <x:c r="F53" s="8" t="str"/>
     </x:row>
     <x:row r="54">
@@ -1109,7 +1109,7 @@
       <x:c r="D54" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E54" s="8" t="str"/>
+      <x:c r="E54" s="8"/>
       <x:c r="F54" s="8" t="str"/>
     </x:row>
     <x:row r="55">
@@ -1125,7 +1125,7 @@
       <x:c r="D55" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Tourism%20Planning%20and%20Development</x:v>
       </x:c>
-      <x:c r="E55" s="8" t="str"/>
+      <x:c r="E55" s="8"/>
       <x:c r="F55" s="8" t="str"/>
     </x:row>
     <x:row r="56">
@@ -1141,7 +1141,7 @@
       <x:c r="D56" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Journal%20of%20Hospitality%20%26%20Tourism%20Research</x:v>
       </x:c>
-      <x:c r="E56" s="8" t="str"/>
+      <x:c r="E56" s="8"/>
       <x:c r="F56" s="8" t="str"/>
     </x:row>
     <x:row r="57">
@@ -1157,7 +1157,7 @@
       <x:c r="D57" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20Economics</x:v>
       </x:c>
-      <x:c r="E57" s="8" t="str"/>
+      <x:c r="E57" s="8"/>
       <x:c r="F57" s="8" t="str"/>
     </x:row>
     <x:row r="58">
@@ -1173,7 +1173,7 @@
       <x:c r="D58" s="8" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-hospitality-and-tourism-management</x:v>
       </x:c>
-      <x:c r="E58" s="8" t="str"/>
+      <x:c r="E58" s="8"/>
       <x:c r="F58" s="8" t="str"/>
     </x:row>
     <x:row r="59">
@@ -1189,7 +1189,7 @@
       <x:c r="D59" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Tourism%20and%20Hospitality%20Research</x:v>
       </x:c>
-      <x:c r="E59" s="8" t="str"/>
+      <x:c r="E59" s="8"/>
       <x:c r="F59" s="8" t="str"/>
     </x:row>
     <x:row r="60">
@@ -1205,7 +1205,7 @@
       <x:c r="D60" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E60" s="8" t="str"/>
+      <x:c r="E60" s="8"/>
       <x:c r="F60" s="8" t="str"/>
     </x:row>
     <x:row r="61">
@@ -1221,7 +1221,7 @@
       <x:c r="D61" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Fuzzy%20Optimization%20and%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E61" s="8" t="str"/>
+      <x:c r="E61" s="8"/>
       <x:c r="F61" s="8" t="str"/>
     </x:row>
     <x:row r="62">
@@ -1237,7 +1237,7 @@
       <x:c r="D62" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Group%20Decision%20and%20Negotiation</x:v>
       </x:c>
-      <x:c r="E62" s="8" t="str"/>
+      <x:c r="E62" s="8"/>
       <x:c r="F62" s="8" t="str"/>
     </x:row>
     <x:row r="63">
@@ -1253,7 +1253,7 @@
       <x:c r="D63" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Soft%20Computing</x:v>
       </x:c>
-      <x:c r="E63" s="8" t="str"/>
+      <x:c r="E63" s="8"/>
       <x:c r="F63" s="8" t="str"/>
     </x:row>
     <x:row r="64">
@@ -1269,7 +1269,7 @@
       <x:c r="D64" s="8" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Machine%20Learning%20and%20Cybernetics</x:v>
       </x:c>
-      <x:c r="E64" s="8" t="str"/>
+      <x:c r="E64" s="8"/>
       <x:c r="F64" s="8" t="str"/>
     </x:row>
     <x:row r="65">
@@ -1285,7 +1285,7 @@
       <x:c r="D65" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Knowledge%20and%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E65" s="8" t="str"/>
+      <x:c r="E65" s="8"/>
       <x:c r="F65" s="8" t="str"/>
     </x:row>
     <x:row r="66">
@@ -1301,7 +1301,7 @@
       <x:c r="D66" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Neural%20Computing%20and%20Applications</x:v>
       </x:c>
-      <x:c r="E66" s="8" t="str"/>
+      <x:c r="E66" s="8"/>
       <x:c r="F66" s="8" t="str"/>
     </x:row>
     <x:row r="67">
@@ -1317,7 +1317,7 @@
       <x:c r="D67" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Applied%20Intelligence</x:v>
       </x:c>
-      <x:c r="E67" s="8" t="str"/>
+      <x:c r="E67" s="8"/>
       <x:c r="F67" s="8" t="str"/>
     </x:row>
     <x:row r="68">
@@ -1333,7 +1333,7 @@
       <x:c r="D68" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Cognitive%20Computation</x:v>
       </x:c>
-      <x:c r="E68" s="8" t="str"/>
+      <x:c r="E68" s="8"/>
       <x:c r="F68" s="8" t="str"/>
     </x:row>
     <x:row r="69">
@@ -1349,7 +1349,7 @@
       <x:c r="D69" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Complex%20%26%20Intelligent%20Systems</x:v>
       </x:c>
-      <x:c r="E69" s="8" t="str"/>
+      <x:c r="E69" s="8"/>
       <x:c r="F69" s="8" t="str"/>
     </x:row>
     <x:row r="70">
@@ -1365,7 +1365,7 @@
       <x:c r="D70" s="8" t="str">
         <x:v>https://link.springer.com/search?query=International%20Journal%20of%20Fuzzy%20Systems</x:v>
       </x:c>
-      <x:c r="E70" s="8" t="str"/>
+      <x:c r="E70" s="8"/>
       <x:c r="F70" s="8" t="str"/>
     </x:row>
     <x:row r="71">
@@ -1381,7 +1381,7 @@
       <x:c r="D71" s="8" t="str">
         <x:v>https://link.springer.com/search?query=OR%20Spectrum</x:v>
       </x:c>
-      <x:c r="E71" s="8" t="str"/>
+      <x:c r="E71" s="8"/>
       <x:c r="F71" s="8" t="str"/>
     </x:row>
     <x:row r="72">
@@ -1397,7 +1397,7 @@
       <x:c r="D72" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Artificial%20Intelligence%20Review</x:v>
       </x:c>
-      <x:c r="E72" s="8" t="str"/>
+      <x:c r="E72" s="8"/>
       <x:c r="F72" s="8" t="str"/>
     </x:row>
     <x:row r="73">
@@ -1413,7 +1413,7 @@
       <x:c r="D73" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Ambient%20Intelligence%20and%20Humanized%20Computing</x:v>
       </x:c>
-      <x:c r="E73" s="8" t="str"/>
+      <x:c r="E73" s="8"/>
       <x:c r="F73" s="8" t="str"/>
     </x:row>
     <x:row r="74">
@@ -1429,7 +1429,7 @@
       <x:c r="D74" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Frontiers%20of%20Engineering%20Management</x:v>
       </x:c>
-      <x:c r="E74" s="8" t="str"/>
+      <x:c r="E74" s="8"/>
       <x:c r="F74" s="8" t="str"/>
     </x:row>
     <x:row r="75">
@@ -1445,7 +1445,7 @@
       <x:c r="D75" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Data%2C%20Information%20and%20Management</x:v>
       </x:c>
-      <x:c r="E75" s="8" t="str"/>
+      <x:c r="E75" s="8"/>
       <x:c r="F75" s="8" t="str"/>
     </x:row>
     <x:row r="76">
@@ -1461,7 +1461,7 @@
       <x:c r="D76" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Systems%20Engineering</x:v>
       </x:c>
-      <x:c r="E76" s="8" t="str"/>
+      <x:c r="E76" s="8"/>
       <x:c r="F76" s="8" t="str"/>
     </x:row>
     <x:row r="77">
@@ -1477,7 +1477,7 @@
       <x:c r="D77" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Systems%20Science%20and%20Complexity</x:v>
       </x:c>
-      <x:c r="E77" s="8" t="str"/>
+      <x:c r="E77" s="8"/>
       <x:c r="F77" s="8" t="str"/>
     </x:row>
     <x:row r="78">
@@ -1493,7 +1493,7 @@
       <x:c r="D78" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Data%20Mining%20%26%20Knowledge%20Discovery</x:v>
       </x:c>
-      <x:c r="E78" s="8" t="str"/>
+      <x:c r="E78" s="8"/>
       <x:c r="F78" s="8" t="str"/>
     </x:row>
     <x:row r="79">
@@ -1509,7 +1509,7 @@
       <x:c r="D79" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Social%20Network%20Analysis%20and%20Mining</x:v>
       </x:c>
-      <x:c r="E79" s="8" t="str"/>
+      <x:c r="E79" s="8"/>
       <x:c r="F79" s="8" t="str"/>
     </x:row>
     <x:row r="80">
@@ -1525,7 +1525,7 @@
       <x:c r="D80" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Health%20Care%20Management%20Science</x:v>
       </x:c>
-      <x:c r="E80" s="8" t="str"/>
+      <x:c r="E80" s="8"/>
       <x:c r="F80" s="8" t="str"/>
     </x:row>
     <x:row r="81">
@@ -1541,7 +1541,7 @@
       <x:c r="D81" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Electronic%20Commerce%20Research</x:v>
       </x:c>
-      <x:c r="E81" s="8" t="str"/>
+      <x:c r="E81" s="8"/>
       <x:c r="F81" s="8" t="str"/>
     </x:row>
     <x:row r="82">
@@ -1557,7 +1557,7 @@
       <x:c r="D82" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Operational%20Research</x:v>
       </x:c>
-      <x:c r="E82" s="8" t="str"/>
+      <x:c r="E82" s="8"/>
       <x:c r="F82" s="8" t="str"/>
     </x:row>
     <x:row r="83">
@@ -1573,7 +1573,7 @@
       <x:c r="D83" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Information%20Technology%20%26%20Tourism</x:v>
       </x:c>
-      <x:c r="E83" s="8" t="str"/>
+      <x:c r="E83" s="8"/>
       <x:c r="F83" s="8" t="str"/>
     </x:row>
     <x:row r="84">
@@ -1589,7 +1589,7 @@
       <x:c r="D84" s="8" t="str">
         <x:v>https://link.springer.com/search?query=TOP</x:v>
       </x:c>
-      <x:c r="E84" s="8" t="str"/>
+      <x:c r="E84" s="8"/>
       <x:c r="F84" s="8" t="str"/>
     </x:row>
     <x:row r="85">
@@ -1605,7 +1605,7 @@
       <x:c r="D85" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Theory%20and%20Decision</x:v>
       </x:c>
-      <x:c r="E85" s="8" t="str"/>
+      <x:c r="E85" s="8"/>
       <x:c r="F85" s="8" t="str"/>
     </x:row>
     <x:row r="86">
@@ -1621,7 +1621,7 @@
       <x:c r="D86" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Annals%20of%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E86" s="8" t="str"/>
+      <x:c r="E86" s="8"/>
       <x:c r="F86" s="8" t="str"/>
     </x:row>
     <x:row r="87">
@@ -1637,7 +1637,7 @@
       <x:c r="D87" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Central%20European%20Journal%20of%20Operations%20Research</x:v>
       </x:c>
-      <x:c r="E87" s="8" t="str"/>
+      <x:c r="E87" s="8"/>
       <x:c r="F87" s="8" t="str"/>
     </x:row>
     <x:row r="88">
@@ -1653,9 +1653,7 @@
       <x:c r="D88" s="8" t="str">
         <x:v>https://www.sciengine.com/search?field=title&amp;query=SCIENCE%20CHINA%20Information%20Sciences</x:v>
       </x:c>
-      <x:c r="E88" s="8" t="str">
-        <x:v>SciEngine|https://www.sciengine.com</x:v>
-      </x:c>
+      <x:c r="E88" s="8"/>
       <x:c r="F88" s="8" t="str"/>
     </x:row>
     <x:row r="89">
@@ -1671,7 +1669,7 @@
       <x:c r="D89" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Progress%20in%20Artificial%20Intelligence</x:v>
       </x:c>
-      <x:c r="E89" s="8" t="str"/>
+      <x:c r="E89" s="8"/>
       <x:c r="F89" s="8" t="str"/>
     </x:row>
     <x:row r="90">
@@ -1687,7 +1685,7 @@
       <x:c r="D90" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Granular%20Computing</x:v>
       </x:c>
-      <x:c r="E90" s="8" t="str"/>
+      <x:c r="E90" s="8"/>
       <x:c r="F90" s="8" t="str"/>
     </x:row>
     <x:row r="91">
@@ -1703,7 +1701,7 @@
       <x:c r="D91" s="8" t="str">
         <x:v>https://link.springer.com/search?query=Journal%20of%20Intelligent%20Manufacturing</x:v>
       </x:c>
-      <x:c r="E91" s="8" t="str"/>
+      <x:c r="E91" s="8"/>
       <x:c r="F91" s="8" t="str"/>
     </x:row>
     <x:row r="92">
@@ -1719,9 +1717,7 @@
       <x:c r="D92" s="8" t="str">
         <x:v>https://www.nature.com/search?q=Nature%20Computational%20Science</x:v>
       </x:c>
-      <x:c r="E92" s="8" t="str">
-        <x:v>Nature|https://www.nature.com</x:v>
-      </x:c>
+      <x:c r="E92" s="8"/>
       <x:c r="F92" s="8" t="str"/>
     </x:row>
     <x:row r="93">
@@ -1737,9 +1733,7 @@
       <x:c r="D93" s="8" t="str">
         <x:v>https://www.nature.com/search?q=Nature%20Machine%20Intelligence</x:v>
       </x:c>
-      <x:c r="E93" s="8" t="str">
-        <x:v>Nature|https://www.nature.com</x:v>
-      </x:c>
+      <x:c r="E93" s="8"/>
       <x:c r="F93" s="8" t="str"/>
     </x:row>
     <x:row r="94">
@@ -1755,9 +1749,7 @@
       <x:c r="D94" s="8" t="str">
         <x:v>https://www.nature.com/search?q=npj%20Artificial%20Intelligence</x:v>
       </x:c>
-      <x:c r="E94" s="8" t="str">
-        <x:v>Nature|https://www.nature.com</x:v>
-      </x:c>
+      <x:c r="E94" s="8"/>
       <x:c r="F94" s="8" t="str"/>
     </x:row>
     <x:row r="95">
@@ -1773,9 +1765,7 @@
       <x:c r="D95" s="8" t="str">
         <x:v>https://www.nature.com/search?q=Nature%20Communications</x:v>
       </x:c>
-      <x:c r="E95" s="8" t="str">
-        <x:v>Nature|https://www.nature.com</x:v>
-      </x:c>
+      <x:c r="E95" s="8"/>
       <x:c r="F95" s="8" t="str"/>
     </x:row>
     <x:row r="96">
@@ -1791,9 +1781,7 @@
       <x:c r="D96" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Systems%2C%20Man%2C%20and%20Cybernetics%3A%20Systems</x:v>
       </x:c>
-      <x:c r="E96" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E96" s="8"/>
       <x:c r="F96" s="8" t="str"/>
     </x:row>
     <x:row r="97">
@@ -1809,9 +1797,7 @@
       <x:c r="D97" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Cybernetics</x:v>
       </x:c>
-      <x:c r="E97" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E97" s="8"/>
       <x:c r="F97" s="8" t="str"/>
     </x:row>
     <x:row r="98">
@@ -1827,9 +1813,7 @@
       <x:c r="D98" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Computational%20Social%20Systems</x:v>
       </x:c>
-      <x:c r="E98" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E98" s="8"/>
       <x:c r="F98" s="8" t="str"/>
     </x:row>
     <x:row r="99">
@@ -1845,9 +1829,7 @@
       <x:c r="D99" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Fuzzy%20Systems</x:v>
       </x:c>
-      <x:c r="E99" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E99" s="8"/>
       <x:c r="F99" s="8" t="str"/>
     </x:row>
     <x:row r="100">
@@ -1863,9 +1845,7 @@
       <x:c r="D100" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Reliability</x:v>
       </x:c>
-      <x:c r="E100" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E100" s="8"/>
       <x:c r="F100" s="8" t="str"/>
     </x:row>
     <x:row r="101">
@@ -1881,9 +1861,7 @@
       <x:c r="D101" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Engineering%20Management</x:v>
       </x:c>
-      <x:c r="E101" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E101" s="8"/>
       <x:c r="F101" s="8" t="str"/>
     </x:row>
     <x:row r="102">
@@ -1899,9 +1877,7 @@
       <x:c r="D102" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Artificial%20Intelligence</x:v>
       </x:c>
-      <x:c r="E102" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E102" s="8"/>
       <x:c r="F102" s="8" t="str"/>
     </x:row>
     <x:row r="103">
@@ -1917,9 +1893,7 @@
       <x:c r="D103" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Knowledge%20and%20Data%20Engineering</x:v>
       </x:c>
-      <x:c r="E103" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E103" s="8"/>
       <x:c r="F103" s="8" t="str"/>
     </x:row>
     <x:row r="104">
@@ -1935,9 +1909,7 @@
       <x:c r="D104" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Evolutionary%20Computation</x:v>
       </x:c>
-      <x:c r="E104" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E104" s="8"/>
       <x:c r="F104" s="8" t="str"/>
     </x:row>
     <x:row r="105">
@@ -1953,9 +1925,7 @@
       <x:c r="D105" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Neural%20Networks%20and%20Learning%20Systems</x:v>
       </x:c>
-      <x:c r="E105" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E105" s="8"/>
       <x:c r="F105" s="8" t="str"/>
     </x:row>
     <x:row r="106">
@@ -1971,9 +1941,7 @@
       <x:c r="D106" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Pattern%20Analysis%20and%20Machine%20Intelligence</x:v>
       </x:c>
-      <x:c r="E106" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E106" s="8"/>
       <x:c r="F106" s="8" t="str"/>
     </x:row>
     <x:row r="107">
@@ -1989,9 +1957,7 @@
       <x:c r="D107" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Big%20Data</x:v>
       </x:c>
-      <x:c r="E107" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E107" s="8"/>
       <x:c r="F107" s="8" t="str"/>
     </x:row>
     <x:row r="108">
@@ -2007,9 +1973,7 @@
       <x:c r="D108" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Network%20Science%20and%20Engineering</x:v>
       </x:c>
-      <x:c r="E108" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E108" s="8"/>
       <x:c r="F108" s="8" t="str"/>
     </x:row>
     <x:row r="109">
@@ -2025,7 +1989,7 @@
       <x:c r="D109" s="8" t="str">
         <x:v>https://www.ieee-jas.net</x:v>
       </x:c>
-      <x:c r="E109" s="8" t="str"/>
+      <x:c r="E109" s="8"/>
       <x:c r="F109" s="8" t="str"/>
     </x:row>
     <x:row r="110">
@@ -2041,9 +2005,7 @@
       <x:c r="D110" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Cognitive%20and%20Developmental%20Systems</x:v>
       </x:c>
-      <x:c r="E110" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E110" s="8"/>
       <x:c r="F110" s="8" t="str"/>
     </x:row>
     <x:row r="111">
@@ -2059,9 +2021,7 @@
       <x:c r="D111" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Emerging%20Topics%20in%20Computational%20Intelligence</x:v>
       </x:c>
-      <x:c r="E111" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E111" s="8"/>
       <x:c r="F111" s="8" t="str"/>
     </x:row>
     <x:row r="112">
@@ -2077,9 +2037,7 @@
       <x:c r="D112" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Systems%20Journal</x:v>
       </x:c>
-      <x:c r="E112" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E112" s="8"/>
       <x:c r="F112" s="8" t="str"/>
     </x:row>
     <x:row r="113">
@@ -2095,9 +2053,7 @@
       <x:c r="D113" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Intelligent%20Systems</x:v>
       </x:c>
-      <x:c r="E113" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E113" s="8"/>
       <x:c r="F113" s="8" t="str"/>
     </x:row>
     <x:row r="114">
@@ -2113,7 +2069,7 @@
       <x:c r="D114" s="8" t="str">
         <x:v>https://www.jseepub.com</x:v>
       </x:c>
-      <x:c r="E114" s="8" t="str"/>
+      <x:c r="E114" s="8"/>
       <x:c r="F114" s="8" t="str"/>
     </x:row>
     <x:row r="115">
@@ -2129,9 +2085,7 @@
       <x:c r="D115" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Automation%20Science%20and%20Engineering</x:v>
       </x:c>
-      <x:c r="E115" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E115" s="8"/>
       <x:c r="F115" s="8" t="str"/>
     </x:row>
     <x:row r="116">
@@ -2147,9 +2101,7 @@
       <x:c r="D116" s="8" t="str">
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?queryText=IEEE%20Transactions%20on%20Automatic%20Control</x:v>
       </x:c>
-      <x:c r="E116" s="8" t="str">
-        <x:v>IEEE Xplore|https://ieeexplore.ieee.org</x:v>
-      </x:c>
+      <x:c r="E116" s="8"/>
       <x:c r="F116" s="8" t="str"/>
     </x:row>
     <x:row r="117">
@@ -2165,7 +2117,7 @@
       <x:c r="D117" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Management%20Science</x:v>
       </x:c>
-      <x:c r="E117" s="8" t="str"/>
+      <x:c r="E117" s="8"/>
       <x:c r="F117" s="8" t="str"/>
     </x:row>
     <x:row r="118">
@@ -2181,7 +2133,7 @@
       <x:c r="D118" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Operations%20Research</x:v>
       </x:c>
-      <x:c r="E118" s="8" t="str"/>
+      <x:c r="E118" s="8"/>
       <x:c r="F118" s="8" t="str"/>
     </x:row>
     <x:row r="119">
@@ -2197,7 +2149,7 @@
       <x:c r="D119" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Computing</x:v>
       </x:c>
-      <x:c r="E119" s="8" t="str"/>
+      <x:c r="E119" s="8"/>
       <x:c r="F119" s="8" t="str"/>
     </x:row>
     <x:row r="120">
@@ -2213,7 +2165,7 @@
       <x:c r="D120" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Information%20Systems%20Research</x:v>
       </x:c>
-      <x:c r="E120" s="8" t="str"/>
+      <x:c r="E120" s="8"/>
       <x:c r="F120" s="8" t="str"/>
     </x:row>
     <x:row r="121">
@@ -2229,7 +2181,7 @@
       <x:c r="D121" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Manufacturing%20%26%20Service%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E121" s="8" t="str"/>
+      <x:c r="E121" s="8"/>
       <x:c r="F121" s="8" t="str"/>
     </x:row>
     <x:row r="122">
@@ -2245,7 +2197,7 @@
       <x:c r="D122" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E122" s="8" t="str"/>
+      <x:c r="E122" s="8"/>
       <x:c r="F122" s="8" t="str"/>
     </x:row>
     <x:row r="123">
@@ -2261,7 +2213,7 @@
       <x:c r="D123" s="8" t="str">
         <x:v>https://journals.sagepub.com/action/doSearch?AllField=Production%20and%20Operations%20Management</x:v>
       </x:c>
-      <x:c r="E123" s="8" t="str"/>
+      <x:c r="E123" s="8"/>
       <x:c r="F123" s="8" t="str"/>
     </x:row>
     <x:row r="124">
@@ -2277,7 +2229,7 @@
       <x:c r="D124" s="8" t="str">
         <x:v>https://pubsonline.informs.org/action/doSearch?AllField=INFORMS%20Journal%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E124" s="8" t="str"/>
+      <x:c r="E124" s="8"/>
       <x:c r="F124" s="8" t="str"/>
     </x:row>
     <x:row r="125">
@@ -2293,7 +2245,7 @@
       <x:c r="D125" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Computing%20Surveys</x:v>
       </x:c>
-      <x:c r="E125" s="8" t="str"/>
+      <x:c r="E125" s="8"/>
       <x:c r="F125" s="8" t="str"/>
     </x:row>
     <x:row r="126">
@@ -2309,7 +2261,7 @@
       <x:c r="D126" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Intelligent%20Systems%20and%20Technology</x:v>
       </x:c>
-      <x:c r="E126" s="8" t="str"/>
+      <x:c r="E126" s="8"/>
       <x:c r="F126" s="8" t="str"/>
     </x:row>
     <x:row r="127">
@@ -2325,7 +2277,7 @@
       <x:c r="D127" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Knowledge%20Discovery%20from%20Data</x:v>
       </x:c>
-      <x:c r="E127" s="8" t="str"/>
+      <x:c r="E127" s="8"/>
       <x:c r="F127" s="8" t="str"/>
     </x:row>
     <x:row r="128">
@@ -2341,7 +2293,7 @@
       <x:c r="D128" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Management%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E128" s="8" t="str"/>
+      <x:c r="E128" s="8"/>
       <x:c r="F128" s="8" t="str"/>
     </x:row>
     <x:row r="129">
@@ -2357,7 +2309,7 @@
       <x:c r="D129" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Information%20Systems</x:v>
       </x:c>
-      <x:c r="E129" s="8" t="str"/>
+      <x:c r="E129" s="8"/>
       <x:c r="F129" s="8" t="str"/>
     </x:row>
     <x:row r="130">
@@ -2373,7 +2325,7 @@
       <x:c r="D130" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Internet%20Technology</x:v>
       </x:c>
-      <x:c r="E130" s="8" t="str"/>
+      <x:c r="E130" s="8"/>
       <x:c r="F130" s="8" t="str"/>
     </x:row>
     <x:row r="131">
@@ -2389,7 +2341,7 @@
       <x:c r="D131" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Modeling%20and%20Computer%20Simulation</x:v>
       </x:c>
-      <x:c r="E131" s="8" t="str"/>
+      <x:c r="E131" s="8"/>
       <x:c r="F131" s="8" t="str"/>
     </x:row>
     <x:row r="132">
@@ -2405,7 +2357,7 @@
       <x:c r="D132" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Social%20Computing</x:v>
       </x:c>
-      <x:c r="E132" s="8" t="str"/>
+      <x:c r="E132" s="8"/>
       <x:c r="F132" s="8" t="str"/>
     </x:row>
     <x:row r="133">
@@ -2421,7 +2373,7 @@
       <x:c r="D133" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20the%20Web</x:v>
       </x:c>
-      <x:c r="E133" s="8" t="str"/>
+      <x:c r="E133" s="8"/>
       <x:c r="F133" s="8" t="str"/>
     </x:row>
     <x:row r="134">
@@ -2437,7 +2389,7 @@
       <x:c r="D134" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM%20Transactions%20on%20Recommender%20Systems</x:v>
       </x:c>
-      <x:c r="E134" s="8" t="str"/>
+      <x:c r="E134" s="8"/>
       <x:c r="F134" s="8" t="str"/>
     </x:row>
     <x:row r="135">
@@ -2453,7 +2405,7 @@
       <x:c r="D135" s="8" t="str">
         <x:v>https://dl.acm.org/action/doSearch?AllField=ACM/IMS%20Transactions%20on%20Data%20Science</x:v>
       </x:c>
-      <x:c r="E135" s="8" t="str"/>
+      <x:c r="E135" s="8"/>
       <x:c r="F135" s="8" t="str"/>
     </x:row>
     <x:row r="136">
@@ -2469,7 +2421,7 @@
       <x:c r="D136" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Forecasting</x:v>
       </x:c>
-      <x:c r="E136" s="8" t="str"/>
+      <x:c r="E136" s="8"/>
       <x:c r="F136" s="8" t="str"/>
     </x:row>
     <x:row r="137">
@@ -2503,7 +2455,7 @@
       <x:c r="D138" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Expert%20Systems</x:v>
       </x:c>
-      <x:c r="E138" s="8" t="str"/>
+      <x:c r="E138" s="8"/>
       <x:c r="F138" s="8" t="str"/>
     </x:row>
     <x:row r="139">
@@ -2519,7 +2471,7 @@
       <x:c r="D139" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Transactions%20in%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E139" s="8" t="str"/>
+      <x:c r="E139" s="8"/>
       <x:c r="F139" s="8" t="str"/>
     </x:row>
     <x:row r="140">
@@ -2535,7 +2487,7 @@
       <x:c r="D140" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Journal%20of%20Multi-Criteria%20Decision%20Analysis</x:v>
       </x:c>
-      <x:c r="E140" s="8" t="str"/>
+      <x:c r="E140" s="8"/>
       <x:c r="F140" s="8" t="str"/>
     </x:row>
     <x:row r="141">
@@ -2551,7 +2503,7 @@
       <x:c r="D141" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Decision%20Sciences%20Journal</x:v>
       </x:c>
-      <x:c r="E141" s="8" t="str"/>
+      <x:c r="E141" s="8"/>
       <x:c r="F141" s="8" t="str"/>
     </x:row>
     <x:row r="142">
@@ -2567,7 +2519,7 @@
       <x:c r="D142" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Risk%20Analysis</x:v>
       </x:c>
-      <x:c r="E142" s="8" t="str"/>
+      <x:c r="E142" s="8"/>
       <x:c r="F142" s="8" t="str"/>
     </x:row>
     <x:row r="143">
@@ -2583,7 +2535,7 @@
       <x:c r="D143" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=International%20Journal%20of%20Finance%20%26%20Economics</x:v>
       </x:c>
-      <x:c r="E143" s="8" t="str"/>
+      <x:c r="E143" s="8"/>
       <x:c r="F143" s="8" t="str"/>
     </x:row>
     <x:row r="144">
@@ -2599,7 +2551,7 @@
       <x:c r="D144" s="8" t="str">
         <x:v>https://onlinelibrary.wiley.com/action/doSearch?AllField=Quality%20and%20Reliability%20Engineering%20International</x:v>
       </x:c>
-      <x:c r="E144" s="8" t="str"/>
+      <x:c r="E144" s="8"/>
       <x:c r="F144" s="8" t="str"/>
     </x:row>
     <x:row r="145">
@@ -2615,7 +2567,7 @@
       <x:c r="D145" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=IISE%20Transactions</x:v>
       </x:c>
-      <x:c r="E145" s="8" t="str"/>
+      <x:c r="E145" s="8"/>
       <x:c r="F145" s="8" t="str"/>
     </x:row>
     <x:row r="146">
@@ -2631,7 +2583,7 @@
       <x:c r="D146" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20the%20Operational%20Research%20Society</x:v>
       </x:c>
-      <x:c r="E146" s="8" t="str"/>
+      <x:c r="E146" s="8"/>
       <x:c r="F146" s="8" t="str"/>
     </x:row>
     <x:row r="147">
@@ -2647,7 +2599,7 @@
       <x:c r="D147" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Production%20Research</x:v>
       </x:c>
-      <x:c r="E147" s="8" t="str"/>
+      <x:c r="E147" s="8"/>
       <x:c r="F147" s="8" t="str"/>
     </x:row>
     <x:row r="148">
@@ -2663,7 +2615,7 @@
       <x:c r="D148" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20Systems%20Science</x:v>
       </x:c>
-      <x:c r="E148" s="8" t="str"/>
+      <x:c r="E148" s="8"/>
       <x:c r="F148" s="8" t="str"/>
     </x:row>
     <x:row r="149">
@@ -2679,7 +2631,7 @@
       <x:c r="D149" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=International%20Journal%20of%20General%20Systems</x:v>
       </x:c>
-      <x:c r="E149" s="8" t="str"/>
+      <x:c r="E149" s="8"/>
       <x:c r="F149" s="8" t="str"/>
     </x:row>
     <x:row r="150">
@@ -2695,7 +2647,7 @@
       <x:c r="D150" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Information%20Technology%20%26%20Decision%20Making</x:v>
       </x:c>
-      <x:c r="E150" s="8" t="str"/>
+      <x:c r="E150" s="8"/>
       <x:c r="F150" s="8" t="str"/>
     </x:row>
     <x:row r="151">
@@ -2711,7 +2663,7 @@
       <x:c r="D151" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=International%20Journal%20of%20Uncertainty%2C%20Fuzziness%20and%20Knowledge-Based%20Systems</x:v>
       </x:c>
-      <x:c r="E151" s="8" t="str"/>
+      <x:c r="E151" s="8"/>
       <x:c r="F151" s="8" t="str"/>
     </x:row>
     <x:row r="152">
@@ -2727,7 +2679,7 @@
       <x:c r="D152" s="8" t="str">
         <x:v>https://www.worldscientific.com/action/doSearch?AllField=Asia-Pacific%20Journal%20of%20Operational%20Research</x:v>
       </x:c>
-      <x:c r="E152" s="8" t="str"/>
+      <x:c r="E152" s="8"/>
       <x:c r="F152" s="8" t="str"/>
     </x:row>
     <x:row r="153">
@@ -2743,7 +2695,7 @@
       <x:c r="D153" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Economic%20Research</x:v>
       </x:c>
-      <x:c r="E153" s="8" t="str"/>
+      <x:c r="E153" s="8"/>
       <x:c r="F153" s="8" t="str"/>
     </x:row>
     <x:row r="154">
@@ -2759,7 +2711,7 @@
       <x:c r="D154" s="8" t="str">
         <x:v>https://www.tandfonline.com/action/doSearch?AllField=Journal%20of%20Management%20Analytics</x:v>
       </x:c>
-      <x:c r="E154" s="8" t="str"/>
+      <x:c r="E154" s="8"/>
       <x:c r="F154" s="8" t="str"/>
     </x:row>
     <x:row r="155">
@@ -2775,7 +2727,7 @@
       <x:c r="D155" s="8" t="str">
         <x:v>https://www.springer.com/search?query=International%20Journal%20of%20Computational%20Intelligence%20Systems</x:v>
       </x:c>
-      <x:c r="E155" s="8" t="str"/>
+      <x:c r="E155" s="8"/>
       <x:c r="F155" s="8" t="str"/>
     </x:row>
     <x:row r="156">
@@ -2791,9 +2743,7 @@
       <x:c r="D156" s="8" t="str">
         <x:v>https://journals.vilniustech.lt/index.php?search=Technological%20and%20Economic%20Development%20of%20Economy</x:v>
       </x:c>
-      <x:c r="E156" s="8" t="str">
-        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
-      </x:c>
+      <x:c r="E156" s="8"/>
       <x:c r="F156" s="8" t="str"/>
     </x:row>
     <x:row r="157">
@@ -2809,7 +2759,7 @@
       <x:c r="D157" s="8" t="str">
         <x:v>https://informatica.vu.lt</x:v>
       </x:c>
-      <x:c r="E157" s="8" t="str"/>
+      <x:c r="E157" s="8"/>
       <x:c r="F157" s="8" t="str"/>
     </x:row>
     <x:row r="158">
@@ -2825,7 +2775,7 @@
       <x:c r="D158" s="8" t="str">
         <x:v>https://univagora.ro</x:v>
       </x:c>
-      <x:c r="E158" s="8" t="str"/>
+      <x:c r="E158" s="8"/>
       <x:c r="F158" s="8" t="str"/>
     </x:row>
     <x:row r="159">
@@ -2841,9 +2791,7 @@
       <x:c r="D159" s="8" t="str">
         <x:v>https://journals.vilniustech.lt/index.php?search=International%20Journal%20of%20Strategic%20Property%20Management</x:v>
       </x:c>
-      <x:c r="E159" s="8" t="str">
-        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
-      </x:c>
+      <x:c r="E159" s="8"/>
       <x:c r="F159" s="8" t="str"/>
     </x:row>
     <x:row r="160">
@@ -2859,9 +2807,7 @@
       <x:c r="D160" s="8" t="str">
         <x:v>https://journals.vilniustech.lt/index.php?search=Transport</x:v>
       </x:c>
-      <x:c r="E160" s="8" t="str">
-        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
-      </x:c>
+      <x:c r="E160" s="8"/>
       <x:c r="F160" s="8" t="str"/>
     </x:row>
     <x:row r="161">
@@ -2877,7 +2823,7 @@
       <x:c r="D161" s="8" t="str">
         <x:v>https://www.transformations.knf.vu.lt</x:v>
       </x:c>
-      <x:c r="E161" s="8" t="str"/>
+      <x:c r="E161" s="8"/>
       <x:c r="F161" s="8" t="str"/>
     </x:row>
     <x:row r="162">
@@ -2893,7 +2839,7 @@
       <x:c r="D162" s="8" t="str">
         <x:v>https://scientiairanica.sharif.edu</x:v>
       </x:c>
-      <x:c r="E162" s="8" t="str"/>
+      <x:c r="E162" s="8"/>
       <x:c r="F162" s="8" t="str"/>
     </x:row>
     <x:row r="163">
@@ -2909,7 +2855,7 @@
       <x:c r="D163" s="8" t="str">
         <x:v>https://ijfs.usb.ac.ir</x:v>
       </x:c>
-      <x:c r="E163" s="8" t="str"/>
+      <x:c r="E163" s="8"/>
       <x:c r="F163" s="8" t="str"/>
     </x:row>
     <x:row r="164">
@@ -2925,7 +2871,7 @@
       <x:c r="D164" s="8" t="str">
         <x:v>https://www.emerald.com/insight/search?q=Kybernetes</x:v>
       </x:c>
-      <x:c r="E164" s="8" t="str"/>
+      <x:c r="E164" s="8"/>
       <x:c r="F164" s="8" t="str"/>
     </x:row>
     <x:row r="165">
@@ -2941,7 +2887,7 @@
       <x:c r="D165" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Decision%20Technologies</x:v>
       </x:c>
-      <x:c r="E165" s="8" t="str"/>
+      <x:c r="E165" s="8"/>
       <x:c r="F165" s="8" t="str"/>
     </x:row>
     <x:row r="166">
@@ -2957,7 +2903,7 @@
       <x:c r="D166" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Fundamenta%20Informaticae</x:v>
       </x:c>
-      <x:c r="E166" s="8" t="str"/>
+      <x:c r="E166" s="8"/>
       <x:c r="F166" s="8" t="str"/>
     </x:row>
     <x:row r="167">
@@ -2973,7 +2919,7 @@
       <x:c r="D167" s="8" t="str">
         <x:v>https://content.iospress.com/search?q=Intelligent%20Data%20Analysis</x:v>
       </x:c>
-      <x:c r="E167" s="8" t="str"/>
+      <x:c r="E167" s="8"/>
       <x:c r="F167" s="8" t="str"/>
     </x:row>
     <x:row r="168">
@@ -2989,7 +2935,7 @@
       <x:c r="D168" s="8" t="str">
         <x:v>https://segcjournal.com</x:v>
       </x:c>
-      <x:c r="E168" s="8" t="str"/>
+      <x:c r="E168" s="8"/>
       <x:c r="F168" s="8" t="str"/>
     </x:row>
     <x:row r="169">
@@ -3005,9 +2951,7 @@
       <x:c r="D169" s="8" t="str">
         <x:v>https://journals.vilniustech.lt/index.php?search=Journal%20of%20Civil%20Engineering%20and%20Management</x:v>
       </x:c>
-      <x:c r="E169" s="8" t="str">
-        <x:v>VILNIUS TECH Journals|https://journals.vilniustech.lt</x:v>
-      </x:c>
+      <x:c r="E169" s="8"/>
       <x:c r="F169" s="8" t="str"/>
     </x:row>
     <x:row r="170">
@@ -3535,7 +3479,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e8abb15b2f044f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra53375365bdf415e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
